--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Útok" sheetId="1" r:id="Rf008dd197f774763"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obrana" sheetId="2" r:id="Rf3a0ebd0224b4608"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="3" r:id="R25d17a7a2a984214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Útok" sheetId="1" r:id="Rc99f640131614f96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obrana" sheetId="2" r:id="Rdf26b9dc650f4d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="3" r:id="Rc491ba76c66d48e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3196,10 +3196,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="2" t="str">
-        <x:v>Do konce svého příštího tahu nemůžeš používat reakce ani provádět akci Pomoc.</x:v>
+        <x:v>Do konce svého příštího tahu nemůžeš používat reakce ani bonusové akce.</x:v>
       </x:c>
       <x:c r="C38" s="2" t="str">
-        <x:v>Nepovedená obrana tě zaměstná natolik, že nezvládneš pohotově reagovat ani pomáhat.</x:v>
+        <x:v>Nezvládnutá obrana tě rozhodí a připraví o pohotové reakce i další manévry.</x:v>
       </x:c>
       <x:c r="D38"/>
       <x:c r="E38">
@@ -3731,10 +3731,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D8" s="2" t="str">
-        <x:v>Při příštím ověření Síly nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Síly má postih −1d4.</x:v>
       </x:c>
       <x:c r="E8" s="2" t="str">
-        <x:v>Vlastní záběr špatně odhadneš a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Vlastní záběr špatně odhadneš a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F8"/>
       <x:c r="G8">
@@ -3752,10 +3752,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
-        <x:v>Snažíš se vyniknout razancí a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Snažíš se vyniknout razancí a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F9"/>
       <x:c r="G9">
@@ -3836,10 +3836,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="2" t="str">
-        <x:v>Příští ověření Síly má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Síly má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E13" s="2" t="str">
-        <x:v>Provedení obětuješ velkému záběru a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Provedení obětuješ velkému záběru a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F13"/>
       <x:c r="G13">
@@ -3983,10 +3983,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D20" s="2" t="str">
-        <x:v>Příští dvě ověření Síly mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření Síly mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E20" s="2" t="str">
-        <x:v>Přidáš důraz ve špatnou chvíli a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš důraz ve špatnou chvíli a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F20"/>
       <x:c r="G20">
@@ -4130,10 +4130,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D27" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření Síly má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Síly má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E27" s="2" t="str">
-        <x:v>Pokusíš se všechno přetlačit a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Pokusíš se všechno přetlačit a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F27"/>
       <x:c r="G27">
@@ -4151,10 +4151,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D28" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Síly má postih −2.</x:v>
+        <x:v>Příští ověření Síly má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E28" s="2" t="str">
-        <x:v>Vlastní záběr špatně odhadneš a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Vlastní záběr špatně odhadneš a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F28"/>
       <x:c r="G28">
@@ -4403,10 +4403,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D40" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření Síly mají postih −3.</x:v>
+        <x:v>Příští dvě ověření Síly mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E40" s="2" t="str">
-        <x:v>Přidáš důraz ve špatnou chvíli a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš důraz ve špatnou chvíli a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F40"/>
       <x:c r="G40">
@@ -4550,10 +4550,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D47" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření Síly mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E47" s="2" t="str">
-        <x:v>Pokusíš se všechno přetlačit a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Pokusíš se všechno přetlačit a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F47"/>
       <x:c r="G47">
@@ -4571,10 +4571,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D48" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Síly mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E48" s="2" t="str">
-        <x:v>Vlastní záběr špatně odhadneš a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Vlastní záběr špatně odhadneš a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F48"/>
       <x:c r="G48">
@@ -4697,10 +4697,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D54" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E54" s="2" t="str">
-        <x:v>Zbytečně se předem vyčerpáš a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Zbytečně se předem vyčerpáš a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F54"/>
       <x:c r="G54">
@@ -4739,10 +4739,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D56" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E56" s="2" t="str">
-        <x:v>Přepneš síly při napravování a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Přepneš síly při napravování a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F56"/>
       <x:c r="G56">
@@ -4823,10 +4823,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D60" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E60" s="2" t="str">
-        <x:v>Přidáš důraz ve špatnou chvíli a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš důraz ve špatnou chvíli a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F60"/>
       <x:c r="G60">
@@ -4991,10 +4991,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D68" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Athletics nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Athletics má postih −1d4.</x:v>
       </x:c>
       <x:c r="E68" s="2" t="str">
-        <x:v>Rozvrhneš si námahu špatně a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Rozvrhneš si námahu špatně a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F68"/>
       <x:c r="G68">
@@ -5012,10 +5012,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D69" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E69" s="2" t="str">
-        <x:v>Sáhneš po zbytečně náročném provedení a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Sáhneš po zbytečně náročném provedení a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F69"/>
       <x:c r="G69">
@@ -5096,10 +5096,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D73" s="2" t="str">
-        <x:v>Příští ověření dovednosti Athletics má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Athletics má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E73" s="2" t="str">
-        <x:v>Ztratíš správný rytmus záběru a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Ztratíš správný rytmus záběru a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F73"/>
       <x:c r="G73">
@@ -5243,10 +5243,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D80" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Athletics mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Athletics mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E80" s="2" t="str">
-        <x:v>Přetáhneš potřebný záběr a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přetáhneš potřebný záběr a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F80"/>
       <x:c r="G80">
@@ -5390,10 +5390,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D87" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Athletics má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Athletics má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E87" s="2" t="str">
-        <x:v>Záběr uspěcháš před srovnáním a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Záběr uspěcháš před srovnáním a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F87"/>
       <x:c r="G87">
@@ -5411,10 +5411,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D88" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Síly má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Athletics má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E88" s="2" t="str">
-        <x:v>Rozvrhneš si námahu špatně a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Rozvrhneš si námahu špatně a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F88"/>
       <x:c r="G88">
@@ -5663,10 +5663,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D100" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Athletics mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Athletics mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E100" s="2" t="str">
-        <x:v>Přetáhneš potřebný záběr a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přetáhneš potřebný záběr a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F100"/>
       <x:c r="G100">
@@ -5810,10 +5810,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D107" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Athletics mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E107" s="2" t="str">
-        <x:v>Záběr uspěcháš před srovnáním a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Záběr uspěcháš před srovnáním a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F107"/>
       <x:c r="G107">
@@ -5831,10 +5831,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D108" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Síly mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E108" s="2" t="str">
-        <x:v>Rozvrhneš si námahu špatně a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Rozvrhneš si námahu špatně a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F108"/>
       <x:c r="G108">
@@ -5957,10 +5957,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D114" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E114" s="2" t="str">
-        <x:v>Vlastní rezervu odhadneš velkoryse a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Vlastní rezervu odhadneš velkoryse a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F114"/>
       <x:c r="G114">
@@ -5999,10 +5999,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D116" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E116" s="2" t="str">
-        <x:v>Snažíš se chybu přetlačit a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Snažíš se chybu přetlačit a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F116"/>
       <x:c r="G116">
@@ -6083,10 +6083,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D120" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E120" s="2" t="str">
-        <x:v>Přetáhneš potřebný záběr a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přetáhneš potřebný záběr a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F120"/>
       <x:c r="G120">
@@ -6251,10 +6251,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D128" s="2" t="str">
-        <x:v>Při příštím ověření Obratnosti nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Obratnosti má postih −1d4.</x:v>
       </x:c>
       <x:c r="E128" s="2" t="str">
-        <x:v>Opravu začneš příliš brzy a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Opravu začneš příliš brzy a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F128"/>
       <x:c r="G128">
@@ -6272,10 +6272,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D129" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E129" s="2" t="str">
-        <x:v>Snažíš se předběhnout vlastní rytmus a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Snažíš se předběhnout vlastní rytmus a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F129"/>
       <x:c r="G129">
@@ -6356,10 +6356,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D133" s="2" t="str">
-        <x:v>Příští ověření Obratnosti má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Obratnosti má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E133" s="2" t="str">
-        <x:v>Jemnost nahradíš prudkým provedením a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Jemnost nahradíš prudkým provedením a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F133"/>
       <x:c r="G133">
@@ -6503,10 +6503,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D140" s="2" t="str">
-        <x:v>Příští dvě ověření Obratnosti mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření Obratnosti mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E140" s="2" t="str">
-        <x:v>Okázale opravuješ špatné načasování a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Okázale opravuješ špatné načasování a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F140"/>
       <x:c r="G140">
@@ -6650,10 +6650,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D147" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření Obratnosti má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Obratnosti má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E147" s="2" t="str">
-        <x:v>Vlastní pohyb zbytečně komplikuješ a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Vlastní pohyb zbytečně komplikuješ a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F147"/>
       <x:c r="G147">
@@ -6671,10 +6671,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D148" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Obratnosti má postih −2.</x:v>
+        <x:v>Příští ověření Obratnosti má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E148" s="2" t="str">
-        <x:v>Opravu začneš příliš brzy a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Opravu začneš příliš brzy a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F148"/>
       <x:c r="G148">
@@ -6923,10 +6923,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D160" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření Obratnosti mají postih −3.</x:v>
+        <x:v>Příští dvě ověření Obratnosti mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E160" s="2" t="str">
-        <x:v>Okázale opravuješ špatné načasování a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Okázale opravuješ špatné načasování a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F160"/>
       <x:c r="G160">
@@ -7070,10 +7070,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D167" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření Obratnosti mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E167" s="2" t="str">
-        <x:v>Vlastní pohyb zbytečně komplikuješ a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Vlastní pohyb zbytečně komplikuješ a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F167"/>
       <x:c r="G167">
@@ -7091,10 +7091,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D168" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Obratnosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E168" s="2" t="str">
-        <x:v>Opravu začneš příliš brzy a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Opravu začneš příliš brzy a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F168"/>
       <x:c r="G168">
@@ -7217,10 +7217,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D174" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E174" s="2" t="str">
-        <x:v>Opravu načasuješ ještě hůř a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Opravu načasuješ ještě hůř a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F174"/>
       <x:c r="G174">
@@ -7259,10 +7259,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D176" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E176" s="2" t="str">
-        <x:v>Přesnost hlídáš až křečovitě a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Přesnost hlídáš až křečovitě a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F176"/>
       <x:c r="G176">
@@ -7343,10 +7343,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D180" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E180" s="2" t="str">
-        <x:v>Okázale opravuješ špatné načasování a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Okázale opravuješ špatné načasování a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F180"/>
       <x:c r="G180">
@@ -7511,10 +7511,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D188" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Acrobatics nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Acrobatics má postih −1d4.</x:v>
       </x:c>
       <x:c r="E188" s="2" t="str">
-        <x:v>Srovnání uspěcháš před odhadem a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Srovnání uspěcháš před odhadem a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F188"/>
       <x:c r="G188">
@@ -7532,10 +7532,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D189" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E189" s="2" t="str">
-        <x:v>Přidáš zbytečně okázalý pohyb a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš zbytečně okázalý pohyb a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F189"/>
       <x:c r="G189">
@@ -7616,10 +7616,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D193" s="2" t="str">
-        <x:v>Příští ověření dovednosti Acrobatics má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Acrobatics má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E193" s="2" t="str">
-        <x:v>Složitým provedením ztratíš jistotu a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Složitým provedením ztratíš jistotu a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F193"/>
       <x:c r="G193">
@@ -7763,10 +7763,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D200" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Acrobatics mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Acrobatics mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E200" s="2" t="str">
-        <x:v>Správný rytmus překryješ horlivostí a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Správný rytmus překryješ horlivostí a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F200"/>
       <x:c r="G200">
@@ -7910,10 +7910,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D207" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Acrobatics má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Acrobatics má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E207" s="2" t="str">
-        <x:v>Rovnováhu hlídáš až křečovitě a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Rovnováhu hlídáš až křečovitě a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F207"/>
       <x:c r="G207">
@@ -7931,10 +7931,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D208" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Obratnosti má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Acrobatics má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E208" s="2" t="str">
-        <x:v>Srovnání uspěcháš před odhadem a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Srovnání uspěcháš před odhadem a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F208"/>
       <x:c r="G208">
@@ -8183,10 +8183,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D220" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Acrobatics mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Acrobatics mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E220" s="2" t="str">
-        <x:v>Správný rytmus překryješ horlivostí a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Správný rytmus překryješ horlivostí a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F220"/>
       <x:c r="G220">
@@ -8330,10 +8330,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D227" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Acrobatics mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E227" s="2" t="str">
-        <x:v>Rovnováhu hlídáš až křečovitě a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Rovnováhu hlídáš až křečovitě a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F227"/>
       <x:c r="G227">
@@ -8351,10 +8351,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D228" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Obratnosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E228" s="2" t="str">
-        <x:v>Srovnání uspěcháš před odhadem a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Srovnání uspěcháš před odhadem a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F228"/>
       <x:c r="G228">
@@ -8477,10 +8477,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D234" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E234" s="2" t="str">
-        <x:v>Přeženeš opravu drobného zaváhání a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Přeženeš opravu drobného zaváhání a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F234"/>
       <x:c r="G234">
@@ -8519,10 +8519,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D236" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E236" s="2" t="str">
-        <x:v>Přidáš ladnost na úkor jistoty a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Přidáš ladnost na úkor jistoty a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F236"/>
       <x:c r="G236">
@@ -8603,10 +8603,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D240" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E240" s="2" t="str">
-        <x:v>Správný rytmus překryješ horlivostí a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Správný rytmus překryješ horlivostí a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F240"/>
       <x:c r="G240">
@@ -8771,10 +8771,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D248" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Sleight of Hand nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Sleight of Hand má postih −1d4.</x:v>
       </x:c>
       <x:c r="E248" s="2" t="str">
-        <x:v>Sled pohybů zbytečně komplikuješ a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Sled pohybů zbytečně komplikuješ a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F248"/>
       <x:c r="G248">
@@ -8792,10 +8792,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D249" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E249" s="2" t="str">
-        <x:v>Přidáš zcela nepotřebnou finesu a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš zcela nepotřebnou finesu a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F249"/>
       <x:c r="G249">
@@ -8876,10 +8876,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D253" s="2" t="str">
-        <x:v>Příští ověření dovednosti Sleight of Hand má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Sleight of Hand má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E253" s="2" t="str">
-        <x:v>Provedení sevřeš přehnanou pečlivostí a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Provedení sevřeš přehnanou pečlivostí a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F253"/>
       <x:c r="G253">
@@ -9023,10 +9023,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D260" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Sleight of Hand mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Sleight of Hand mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E260" s="2" t="str">
-        <x:v>Pokus zpestříš nepotřebným pohybem a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Pokus zpestříš nepotřebným pohybem a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F260"/>
       <x:c r="G260">
@@ -9170,10 +9170,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D267" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Sleight of Hand má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Sleight of Hand má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E267" s="2" t="str">
-        <x:v>Opravu drobnosti příliš zvýrazníš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Opravu drobnosti příliš zvýrazníš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F267"/>
       <x:c r="G267">
@@ -9191,10 +9191,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D268" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Obratnosti má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Sleight of Hand má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E268" s="2" t="str">
-        <x:v>Sled pohybů zbytečně komplikuješ a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Sled pohybů zbytečně komplikuješ a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F268"/>
       <x:c r="G268">
@@ -9443,10 +9443,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D280" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Sleight of Hand mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Sleight of Hand mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E280" s="2" t="str">
-        <x:v>Pokus zpestříš nepotřebným pohybem a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Pokus zpestříš nepotřebným pohybem a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F280"/>
       <x:c r="G280">
@@ -9590,10 +9590,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D287" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Sleight of Hand mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E287" s="2" t="str">
-        <x:v>Opravu drobnosti příliš zvýrazníš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Opravu drobnosti příliš zvýrazníš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F287"/>
       <x:c r="G287">
@@ -9611,10 +9611,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D288" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Obratnosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E288" s="2" t="str">
-        <x:v>Sled pohybů zbytečně komplikuješ a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Sled pohybů zbytečně komplikuješ a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F288"/>
       <x:c r="G288">
@@ -9737,10 +9737,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D294" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E294" s="2" t="str">
-        <x:v>Zbytečně opravuješ správnou část a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Zbytečně opravuješ správnou část a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F294"/>
       <x:c r="G294">
@@ -9779,10 +9779,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D296" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E296" s="2" t="str">
-        <x:v>Jemné načasování zbytečně rozhodíš a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jemné načasování zbytečně rozhodíš a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F296"/>
       <x:c r="G296">
@@ -9863,10 +9863,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D300" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E300" s="2" t="str">
-        <x:v>Pokus zpestříš nepotřebným pohybem a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Pokus zpestříš nepotřebným pohybem a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F300"/>
       <x:c r="G300">
@@ -10031,10 +10031,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D308" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Stealth nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Stealth má postih −1d4.</x:v>
       </x:c>
       <x:c r="E308" s="2" t="str">
-        <x:v>Zvolíš přehnaně složitý postup a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Zvolíš přehnaně složitý postup a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F308"/>
       <x:c r="G308">
@@ -10052,10 +10052,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D309" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E309" s="2" t="str">
-        <x:v>Zbytečně se snažíš zmizet dokonale a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Zbytečně se snažíš zmizet dokonale a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F309"/>
       <x:c r="G309">
@@ -10136,10 +10136,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D313" s="2" t="str">
-        <x:v>Příští ověření dovednosti Stealth má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Stealth má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E313" s="2" t="str">
-        <x:v>Ztratíš přirozený rytmus skrývání a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Ztratíš přirozený rytmus skrývání a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F313"/>
       <x:c r="G313">
@@ -10283,10 +10283,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D320" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Stealth mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Stealth mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E320" s="2" t="str">
-        <x:v>Křečovitě opravuješ své tempo a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Křečovitě opravuješ své tempo a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F320"/>
       <x:c r="G320">
@@ -10430,10 +10430,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D327" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Stealth má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Stealth má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E327" s="2" t="str">
-        <x:v>Opravu načasování zbytečně zvýrazníš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Opravu načasování zbytečně zvýrazníš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F327"/>
       <x:c r="G327">
@@ -10451,10 +10451,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D328" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Obratnosti má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Stealth má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E328" s="2" t="str">
-        <x:v>Zvolíš přehnaně složitý postup a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Zvolíš přehnaně složitý postup a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F328"/>
       <x:c r="G328">
@@ -10703,10 +10703,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D340" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Stealth mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Stealth mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E340" s="2" t="str">
-        <x:v>Křečovitě opravuješ své tempo a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Křečovitě opravuješ své tempo a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F340"/>
       <x:c r="G340">
@@ -10850,10 +10850,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D347" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Stealth mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E347" s="2" t="str">
-        <x:v>Opravu načasování zbytečně zvýrazníš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Opravu načasování zbytečně zvýrazníš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F347"/>
       <x:c r="G347">
@@ -10871,10 +10871,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D348" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Obratnosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E348" s="2" t="str">
-        <x:v>Zvolíš přehnaně složitý postup a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Zvolíš přehnaně složitý postup a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F348"/>
       <x:c r="G348">
@@ -10997,10 +10997,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D354" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E354" s="2" t="str">
-        <x:v>Pokusíš se nenápadnost uspěchat a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Pokusíš se nenápadnost uspěchat a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F354"/>
       <x:c r="G354">
@@ -11039,10 +11039,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D356" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E356" s="2" t="str">
-        <x:v>Přehnaně hlídáš každé zaváhání a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Přehnaně hlídáš každé zaváhání a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F356"/>
       <x:c r="G356">
@@ -11123,10 +11123,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D360" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E360" s="2" t="str">
-        <x:v>Křečovitě opravuješ své tempo a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Křečovitě opravuješ své tempo a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F360"/>
       <x:c r="G360">
@@ -11291,10 +11291,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D368" s="2" t="str">
-        <x:v>Při příštím ověření Inteligence nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Inteligence má postih −1d4.</x:v>
       </x:c>
       <x:c r="E368" s="2" t="str">
-        <x:v>Rozbor zatížíš zbytečnou odbočkou a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Rozbor zatížíš zbytečnou odbočkou a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F368"/>
       <x:c r="G368">
@@ -11312,10 +11312,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D369" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E369" s="2" t="str">
-        <x:v>Vlastní teorii rozvineš přespříliš a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Vlastní teorii rozvineš přespříliš a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F369"/>
       <x:c r="G369">
@@ -11396,10 +11396,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D373" s="2" t="str">
-        <x:v>Příští ověření Inteligence má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Inteligence má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E373" s="2" t="str">
-        <x:v>Spleteš si příčinu s následkem a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Spleteš si příčinu s následkem a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F373"/>
       <x:c r="G373">
@@ -11543,10 +11543,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D380" s="2" t="str">
-        <x:v>Příští dvě ověření Inteligence mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření Inteligence mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E380" s="2" t="str">
-        <x:v>Přidáš zbytečnou myšlenkovou okliku a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš zbytečnou myšlenkovou okliku a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F380"/>
       <x:c r="G380">
@@ -11690,10 +11690,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D387" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření Inteligence má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Inteligence má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E387" s="2" t="str">
-        <x:v>Souvislost si zbytečně domyslíš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Souvislost si zbytečně domyslíš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F387"/>
       <x:c r="G387">
@@ -11711,10 +11711,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D388" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Inteligence má postih −2.</x:v>
+        <x:v>Příští ověření Inteligence má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E388" s="2" t="str">
-        <x:v>Rozbor zatížíš zbytečnou odbočkou a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Rozbor zatížíš zbytečnou odbočkou a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F388"/>
       <x:c r="G388">
@@ -11963,10 +11963,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D400" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření Inteligence mají postih −3.</x:v>
+        <x:v>Příští dvě ověření Inteligence mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E400" s="2" t="str">
-        <x:v>Přidáš zbytečnou myšlenkovou okliku a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš zbytečnou myšlenkovou okliku a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F400"/>
       <x:c r="G400">
@@ -12110,10 +12110,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D407" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření Inteligence mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E407" s="2" t="str">
-        <x:v>Souvislost si zbytečně domyslíš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Souvislost si zbytečně domyslíš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F407"/>
       <x:c r="G407">
@@ -12131,10 +12131,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D408" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Inteligence mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E408" s="2" t="str">
-        <x:v>Rozbor zatížíš zbytečnou odbočkou a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Rozbor zatížíš zbytečnou odbočkou a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F408"/>
       <x:c r="G408">
@@ -12257,10 +12257,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D414" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E414" s="2" t="str">
-        <x:v>Zbytečně rozebereš správnou část a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Zbytečně rozebereš správnou část a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F414"/>
       <x:c r="G414">
@@ -12299,10 +12299,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D416" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E416" s="2" t="str">
-        <x:v>Jistotu hledáš v komplikacích a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jistotu hledáš v komplikacích a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F416"/>
       <x:c r="G416">
@@ -12383,10 +12383,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D420" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E420" s="2" t="str">
-        <x:v>Přidáš zbytečnou myšlenkovou okliku a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš zbytečnou myšlenkovou okliku a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F420"/>
       <x:c r="G420">
@@ -12551,10 +12551,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D428" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Arcana nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Arcana má postih −1d4.</x:v>
       </x:c>
       <x:c r="E428" s="2" t="str">
-        <x:v>Rozbor zatížíš nepotřebnou teorií a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Rozbor zatížíš nepotřebnou teorií a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F428"/>
       <x:c r="G428">
@@ -12572,10 +12572,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D429" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E429" s="2" t="str">
-        <x:v>Přidáš příliš učenou odbočku a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš příliš učenou odbočku a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F429"/>
       <x:c r="G429">
@@ -12656,10 +12656,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D433" s="2" t="str">
-        <x:v>Příští ověření dovednosti Arcana má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Arcana má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E433" s="2" t="str">
-        <x:v>Spleteš si dvě magické poučky a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Spleteš si dvě magické poučky a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F433"/>
       <x:c r="G433">
@@ -12803,10 +12803,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D440" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Arcana mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Arcana mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E440" s="2" t="str">
-        <x:v>Přidáš magii zbytečnou složitost a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš magii zbytečnou složitost a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F440"/>
       <x:c r="G440">
@@ -12950,10 +12950,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D447" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Arcana má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Arcana má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E447" s="2" t="str">
-        <x:v>Magickou souvislost si domyslíš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Magickou souvislost si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F447"/>
       <x:c r="G447">
@@ -12971,10 +12971,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D448" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Inteligence má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Arcana má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E448" s="2" t="str">
-        <x:v>Rozbor zatížíš nepotřebnou teorií a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Rozbor zatížíš nepotřebnou teorií a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F448"/>
       <x:c r="G448">
@@ -13223,10 +13223,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D460" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Arcana mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Arcana mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E460" s="2" t="str">
-        <x:v>Přidáš magii zbytečnou složitost a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš magii zbytečnou složitost a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F460"/>
       <x:c r="G460">
@@ -13370,10 +13370,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D467" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Arcana mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E467" s="2" t="str">
-        <x:v>Magickou souvislost si domyslíš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Magickou souvislost si domyslíš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F467"/>
       <x:c r="G467">
@@ -13391,10 +13391,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D468" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Inteligence mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E468" s="2" t="str">
-        <x:v>Rozbor zatížíš nepotřebnou teorií a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Rozbor zatížíš nepotřebnou teorií a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F468"/>
       <x:c r="G468">
@@ -13517,10 +13517,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D474" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E474" s="2" t="str">
-        <x:v>Správnou znalost opravíš k horšímu a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správnou znalost opravíš k horšímu a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F474"/>
       <x:c r="G474">
@@ -13559,10 +13559,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D476" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E476" s="2" t="str">
-        <x:v>Magický princip zbytečně překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Magický princip zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F476"/>
       <x:c r="G476">
@@ -13643,10 +13643,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D480" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E480" s="2" t="str">
-        <x:v>Přidáš magii zbytečnou složitost a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš magii zbytečnou složitost a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F480"/>
       <x:c r="G480">
@@ -13811,10 +13811,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D488" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti History nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti History má postih −1d4.</x:v>
       </x:c>
       <x:c r="E488" s="2" t="str">
-        <x:v>Výklad zatížíš zbytečnou odbočkou a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Výklad zatížíš zbytečnou odbočkou a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F488"/>
       <x:c r="G488">
@@ -13832,10 +13832,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D489" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E489" s="2" t="str">
-        <x:v>Zbytečně předvedeš rozsah znalostí a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Zbytečně předvedeš rozsah znalostí a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F489"/>
       <x:c r="G489">
@@ -13916,10 +13916,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D493" s="2" t="str">
-        <x:v>Příští ověření dovednosti History má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti History má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E493" s="2" t="str">
-        <x:v>Zaměníš pořadí známých událostí a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš pořadí známých událostí a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F493"/>
       <x:c r="G493">
@@ -14063,10 +14063,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D500" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti History mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti History mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E500" s="2" t="str">
-        <x:v>Zbytečně rozvětvíš vlastní výklad a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Zbytečně rozvětvíš vlastní výklad a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F500"/>
       <x:c r="G500">
@@ -14210,10 +14210,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D507" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti History má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti History má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E507" s="2" t="str">
-        <x:v>Chybějící souvislost si domyslíš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Chybějící souvislost si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F507"/>
       <x:c r="G507">
@@ -14231,10 +14231,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D508" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Inteligence má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti History má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E508" s="2" t="str">
-        <x:v>Výklad zatížíš zbytečnou odbočkou a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Výklad zatížíš zbytečnou odbočkou a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F508"/>
       <x:c r="G508">
@@ -14483,10 +14483,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D520" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti History mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti History mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E520" s="2" t="str">
-        <x:v>Zbytečně rozvětvíš vlastní výklad a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Zbytečně rozvětvíš vlastní výklad a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F520"/>
       <x:c r="G520">
@@ -14630,10 +14630,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D527" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti History mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E527" s="2" t="str">
-        <x:v>Chybějící souvislost si domyslíš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Chybějící souvislost si domyslíš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F527"/>
       <x:c r="G527">
@@ -14651,10 +14651,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D528" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Inteligence mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E528" s="2" t="str">
-        <x:v>Výklad zatížíš zbytečnou odbočkou a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Výklad zatížíš zbytečnou odbočkou a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F528"/>
       <x:c r="G528">
@@ -14777,10 +14777,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D534" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E534" s="2" t="str">
-        <x:v>Správnou vzpomínku překryješ dohadem a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správnou vzpomínku překryješ dohadem a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F534"/>
       <x:c r="G534">
@@ -14819,10 +14819,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D536" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E536" s="2" t="str">
-        <x:v>Jednoduchou souvislost překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jednoduchou souvislost překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F536"/>
       <x:c r="G536">
@@ -14903,10 +14903,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D540" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E540" s="2" t="str">
-        <x:v>Zbytečně rozvětvíš vlastní výklad a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Zbytečně rozvětvíš vlastní výklad a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F540"/>
       <x:c r="G540">
@@ -15071,10 +15071,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D548" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Investigation nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Investigation má postih −1d4.</x:v>
       </x:c>
       <x:c r="E548" s="2" t="str">
-        <x:v>Rozbor zatížíš zbytečnou stopou a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Rozbor zatížíš zbytečnou stopou a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F548"/>
       <x:c r="G548">
@@ -15092,10 +15092,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D549" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E549" s="2" t="str">
-        <x:v>Vlastní teorii rozkošatíš přespříliš a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Vlastní teorii rozkošatíš přespříliš a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F549"/>
       <x:c r="G549">
@@ -15176,10 +15176,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D553" s="2" t="str">
-        <x:v>Příští ověření dovednosti Investigation má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Investigation má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E553" s="2" t="str">
-        <x:v>Zaměníš následek za příčinu a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš následek za příčinu a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F553"/>
       <x:c r="G553">
@@ -15323,10 +15323,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D560" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Investigation mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Investigation mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E560" s="2" t="str">
-        <x:v>Přidáš zbytečnou vyšetřovací okliku a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš zbytečnou vyšetřovací okliku a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F560"/>
       <x:c r="G560">
@@ -15470,10 +15470,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D567" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Investigation má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Investigation má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E567" s="2" t="str">
-        <x:v>Chybějící článek si domyslíš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Chybějící článek si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F567"/>
       <x:c r="G567">
@@ -15491,10 +15491,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D568" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Inteligence má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Investigation má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E568" s="2" t="str">
-        <x:v>Rozbor zatížíš zbytečnou stopou a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Rozbor zatížíš zbytečnou stopou a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F568"/>
       <x:c r="G568">
@@ -15743,10 +15743,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D580" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Investigation mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Investigation mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E580" s="2" t="str">
-        <x:v>Přidáš zbytečnou vyšetřovací okliku a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš zbytečnou vyšetřovací okliku a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F580"/>
       <x:c r="G580">
@@ -15890,10 +15890,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D587" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Investigation mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E587" s="2" t="str">
-        <x:v>Chybějící článek si domyslíš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Chybějící článek si domyslíš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F587"/>
       <x:c r="G587">
@@ -15911,10 +15911,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D588" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Inteligence mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E588" s="2" t="str">
-        <x:v>Rozbor zatížíš zbytečnou stopou a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Rozbor zatížíš zbytečnou stopou a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F588"/>
       <x:c r="G588">
@@ -16037,10 +16037,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D594" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E594" s="2" t="str">
-        <x:v>Správný závěr překryješ opravou a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správný závěr překryješ opravou a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F594"/>
       <x:c r="G594">
@@ -16079,10 +16079,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D596" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E596" s="2" t="str">
-        <x:v>Pátrání zbytečně překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Pátrání zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F596"/>
       <x:c r="G596">
@@ -16163,10 +16163,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D600" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E600" s="2" t="str">
-        <x:v>Přidáš zbytečnou vyšetřovací okliku a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš zbytečnou vyšetřovací okliku a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F600"/>
       <x:c r="G600">
@@ -16331,10 +16331,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D608" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Nature nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Nature má postih −1d4.</x:v>
       </x:c>
       <x:c r="E608" s="2" t="str">
-        <x:v>Výklad zatížíš zbytečnou výjimkou a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Výklad zatížíš zbytečnou výjimkou a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F608"/>
       <x:c r="G608">
@@ -16352,10 +16352,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D609" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E609" s="2" t="str">
-        <x:v>Zbytečně předvedeš učenou odbočku a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Zbytečně předvedeš učenou odbočku a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F609"/>
       <x:c r="G609">
@@ -16436,10 +16436,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D613" s="2" t="str">
-        <x:v>Příští ověření dovednosti Nature má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Nature má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E613" s="2" t="str">
-        <x:v>Zaměníš dvě přírodní zákonitosti a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš dvě přírodní zákonitosti a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F613"/>
       <x:c r="G613">
@@ -16583,10 +16583,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D620" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Nature mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Nature mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E620" s="2" t="str">
-        <x:v>Přírodu zbytečně vysvětluješ oklikou a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přírodu zbytečně vysvětluješ oklikou a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F620"/>
       <x:c r="G620">
@@ -16730,10 +16730,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D627" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Nature má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Nature má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E627" s="2" t="str">
-        <x:v>Přírodní souvislost si domyslíš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Přírodní souvislost si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F627"/>
       <x:c r="G627">
@@ -16751,10 +16751,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D628" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Inteligence má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Nature má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E628" s="2" t="str">
-        <x:v>Výklad zatížíš zbytečnou výjimkou a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Výklad zatížíš zbytečnou výjimkou a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F628"/>
       <x:c r="G628">
@@ -17003,10 +17003,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D640" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Nature mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Nature mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E640" s="2" t="str">
-        <x:v>Přírodu zbytečně vysvětluješ oklikou a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přírodu zbytečně vysvětluješ oklikou a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F640"/>
       <x:c r="G640">
@@ -17150,10 +17150,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D647" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Nature mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E647" s="2" t="str">
-        <x:v>Přírodní souvislost si domyslíš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Přírodní souvislost si domyslíš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F647"/>
       <x:c r="G647">
@@ -17171,10 +17171,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D648" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Inteligence mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E648" s="2" t="str">
-        <x:v>Výklad zatížíš zbytečnou výjimkou a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Výklad zatížíš zbytečnou výjimkou a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F648"/>
       <x:c r="G648">
@@ -17297,10 +17297,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D654" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E654" s="2" t="str">
-        <x:v>Správnou znalost překryješ dohadem a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správnou znalost překryješ dohadem a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F654"/>
       <x:c r="G654">
@@ -17339,10 +17339,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D656" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E656" s="2" t="str">
-        <x:v>Jednoduchý princip zbytečně rozebereš a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jednoduchý princip zbytečně rozebereš a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F656"/>
       <x:c r="G656">
@@ -17423,10 +17423,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D660" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E660" s="2" t="str">
-        <x:v>Přírodu zbytečně vysvětluješ oklikou a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přírodu zbytečně vysvětluješ oklikou a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F660"/>
       <x:c r="G660">
@@ -17591,10 +17591,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D668" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Religion nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Religion má postih −1d4.</x:v>
       </x:c>
       <x:c r="E668" s="2" t="str">
-        <x:v>Rozbor zatížíš učenou odbočkou a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Rozbor zatížíš učenou odbočkou a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F668"/>
       <x:c r="G668">
@@ -17612,10 +17612,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D669" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E669" s="2" t="str">
-        <x:v>Přidáš zbytečně slavnostní výklad a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš zbytečně slavnostní výklad a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F669"/>
       <x:c r="G669">
@@ -17696,10 +17696,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D673" s="2" t="str">
-        <x:v>Příští ověření dovednosti Religion má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Religion má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E673" s="2" t="str">
-        <x:v>Zaměníš dvě známá učení a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš dvě známá učení a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F673"/>
       <x:c r="G673">
@@ -17843,10 +17843,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D680" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Religion mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Religion mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E680" s="2" t="str">
-        <x:v>Přidáš zbytečnou věroučnou okliku a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš zbytečnou věroučnou okliku a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F680"/>
       <x:c r="G680">
@@ -17990,10 +17990,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D687" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Religion má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Religion má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E687" s="2" t="str">
-        <x:v>Náboženskou souvislost si domyslíš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Náboženskou souvislost si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F687"/>
       <x:c r="G687">
@@ -18011,10 +18011,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D688" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Inteligence má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Religion má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E688" s="2" t="str">
-        <x:v>Rozbor zatížíš učenou odbočkou a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Rozbor zatížíš učenou odbočkou a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F688"/>
       <x:c r="G688">
@@ -18263,10 +18263,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D700" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Religion mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Religion mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E700" s="2" t="str">
-        <x:v>Přidáš zbytečnou věroučnou okliku a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš zbytečnou věroučnou okliku a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F700"/>
       <x:c r="G700">
@@ -18410,10 +18410,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D707" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Religion mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E707" s="2" t="str">
-        <x:v>Náboženskou souvislost si domyslíš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Náboženskou souvislost si domyslíš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F707"/>
       <x:c r="G707">
@@ -18431,10 +18431,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D708" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Inteligence mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E708" s="2" t="str">
-        <x:v>Rozbor zatížíš učenou odbočkou a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Rozbor zatížíš učenou odbočkou a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F708"/>
       <x:c r="G708">
@@ -18557,10 +18557,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D714" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E714" s="2" t="str">
-        <x:v>Správnou vzpomínku překryješ výkladem a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správnou vzpomínku překryješ výkladem a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F714"/>
       <x:c r="G714">
@@ -18599,10 +18599,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D716" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E716" s="2" t="str">
-        <x:v>Jednoduchou poučku překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jednoduchou poučku překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F716"/>
       <x:c r="G716">
@@ -18683,10 +18683,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D720" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E720" s="2" t="str">
-        <x:v>Přidáš zbytečnou věroučnou okliku a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš zbytečnou věroučnou okliku a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F720"/>
       <x:c r="G720">
@@ -18851,10 +18851,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D728" s="2" t="str">
-        <x:v>Při příštím ověření Moudrosti nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Moudrosti má postih −1d4.</x:v>
       </x:c>
       <x:c r="E728" s="2" t="str">
-        <x:v>Rozhodování zatížíš zbytečnou pochybností a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Rozhodování zatížíš zbytečnou pochybností a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F728"/>
       <x:c r="G728">
@@ -18872,10 +18872,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D729" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E729" s="2" t="str">
-        <x:v>Zbytečně rozvíjíš vlastní předtuchu a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Zbytečně rozvíjíš vlastní předtuchu a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F729"/>
       <x:c r="G729">
@@ -18956,10 +18956,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D733" s="2" t="str">
-        <x:v>Příští ověření Moudrosti má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Moudrosti má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E733" s="2" t="str">
-        <x:v>Zaměníš přání za skutečný odhad a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš přání za skutečný odhad a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F733"/>
       <x:c r="G733">
@@ -19103,10 +19103,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D740" s="2" t="str">
-        <x:v>Příští dvě ověření Moudrosti mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření Moudrosti mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E740" s="2" t="str">
-        <x:v>Přidáš zbytečnou rozhodovací okliku a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš zbytečnou rozhodovací okliku a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F740"/>
       <x:c r="G740">
@@ -19250,10 +19250,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D747" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření Moudrosti má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Moudrosti má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E747" s="2" t="str">
-        <x:v>Chybějící jistotu nahradíš domněnkou a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Chybějící jistotu nahradíš domněnkou a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F747"/>
       <x:c r="G747">
@@ -19271,10 +19271,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D748" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Moudrosti má postih −2.</x:v>
+        <x:v>Příští ověření Moudrosti má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E748" s="2" t="str">
-        <x:v>Rozhodování zatížíš zbytečnou pochybností a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Rozhodování zatížíš zbytečnou pochybností a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F748"/>
       <x:c r="G748">
@@ -19523,10 +19523,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D760" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření Moudrosti mají postih −3.</x:v>
+        <x:v>Příští dvě ověření Moudrosti mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E760" s="2" t="str">
-        <x:v>Přidáš zbytečnou rozhodovací okliku a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš zbytečnou rozhodovací okliku a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F760"/>
       <x:c r="G760">
@@ -19670,10 +19670,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D767" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření Moudrosti mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E767" s="2" t="str">
-        <x:v>Chybějící jistotu nahradíš domněnkou a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Chybějící jistotu nahradíš domněnkou a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F767"/>
       <x:c r="G767">
@@ -19691,10 +19691,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D768" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Moudrosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E768" s="2" t="str">
-        <x:v>Rozhodování zatížíš zbytečnou pochybností a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Rozhodování zatížíš zbytečnou pochybností a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F768"/>
       <x:c r="G768">
@@ -19817,10 +19817,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D774" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E774" s="2" t="str">
-        <x:v>Správný pocit překryješ pochybností a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správný pocit překryješ pochybností a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F774"/>
       <x:c r="G774">
@@ -19859,10 +19859,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D776" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E776" s="2" t="str">
-        <x:v>Prostý úsudek zbytečně překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Prostý úsudek zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F776"/>
       <x:c r="G776">
@@ -19943,10 +19943,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D780" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E780" s="2" t="str">
-        <x:v>Přidáš zbytečnou rozhodovací okliku a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš zbytečnou rozhodovací okliku a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F780"/>
       <x:c r="G780">
@@ -20111,10 +20111,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D788" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Animal Handling nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Animal Handling má postih −1d4.</x:v>
       </x:c>
       <x:c r="E788" s="2" t="str">
-        <x:v>Přístup zatížíš zbytečným váháním a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Přístup zatížíš zbytečným váháním a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F788"/>
       <x:c r="G788">
@@ -20132,10 +20132,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D789" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E789" s="2" t="str">
-        <x:v>Vlastní klid předvádíš přespříliš a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Vlastní klid předvádíš přespříliš a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F789"/>
       <x:c r="G789">
@@ -20216,10 +20216,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D793" s="2" t="str">
-        <x:v>Příští ověření dovednosti Animal Handling má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Animal Handling má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E793" s="2" t="str">
-        <x:v>Zaměníš očekávání za pochopení a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš očekávání za pochopení a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F793"/>
       <x:c r="G793">
@@ -20363,10 +20363,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D800" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Animal Handling mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Animal Handling mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E800" s="2" t="str">
-        <x:v>Zbytečně zkomplikuješ vlastní přístup a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Zbytečně zkomplikuješ vlastní přístup a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F800"/>
       <x:c r="G800">
@@ -20510,10 +20510,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D807" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Animal Handling má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Animal Handling má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E807" s="2" t="str">
-        <x:v>Chování si doplníš domněnkou a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Chování si doplníš domněnkou a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F807"/>
       <x:c r="G807">
@@ -20531,10 +20531,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D808" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Moudrosti má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Animal Handling má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E808" s="2" t="str">
-        <x:v>Přístup zatížíš zbytečným váháním a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Přístup zatížíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F808"/>
       <x:c r="G808">
@@ -20783,10 +20783,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D820" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Animal Handling mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Animal Handling mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E820" s="2" t="str">
-        <x:v>Zbytečně zkomplikuješ vlastní přístup a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Zbytečně zkomplikuješ vlastní přístup a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F820"/>
       <x:c r="G820">
@@ -20930,10 +20930,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D827" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Animal Handling mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E827" s="2" t="str">
-        <x:v>Chování si doplníš domněnkou a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Chování si doplníš domněnkou a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F827"/>
       <x:c r="G827">
@@ -20951,10 +20951,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D828" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Moudrosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E828" s="2" t="str">
-        <x:v>Přístup zatížíš zbytečným váháním a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Přístup zatížíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F828"/>
       <x:c r="G828">
@@ -21077,10 +21077,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D834" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E834" s="2" t="str">
-        <x:v>Správný přístup opravíš přehnaně a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správný přístup opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F834"/>
       <x:c r="G834">
@@ -21119,10 +21119,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D836" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E836" s="2" t="str">
-        <x:v>Jednoduché chování zbytečně překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jednoduché chování zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F836"/>
       <x:c r="G836">
@@ -21203,10 +21203,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D840" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E840" s="2" t="str">
-        <x:v>Zbytečně zkomplikuješ vlastní přístup a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Zbytečně zkomplikuješ vlastní přístup a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F840"/>
       <x:c r="G840">
@@ -21371,10 +21371,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D848" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Insight nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Insight má postih −1d4.</x:v>
       </x:c>
       <x:c r="E848" s="2" t="str">
-        <x:v>Odhad zatížíš zbytečnou pochybností a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Odhad zatížíš zbytečnou pochybností a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F848"/>
       <x:c r="G848">
@@ -21392,10 +21392,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D849" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E849" s="2" t="str">
-        <x:v>Přidáš příliš důmyslné vysvětlení a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš příliš důmyslné vysvětlení a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F849"/>
       <x:c r="G849">
@@ -21476,10 +21476,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D853" s="2" t="str">
-        <x:v>Příští ověření dovednosti Insight má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Insight má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E853" s="2" t="str">
-        <x:v>Zaměníš obavu za skutečný úmysl a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš obavu za skutečný úmysl a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F853"/>
       <x:c r="G853">
@@ -21623,10 +21623,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D860" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Insight mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Insight mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E860" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v úsudku a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš zbytečnou okliku v úsudku a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F860"/>
       <x:c r="G860">
@@ -21770,10 +21770,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D867" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Insight má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Insight má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E867" s="2" t="str">
-        <x:v>Cizí úmysl si domyslíš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Cizí úmysl si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F867"/>
       <x:c r="G867">
@@ -21791,10 +21791,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D868" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Moudrosti má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Insight má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E868" s="2" t="str">
-        <x:v>Odhad zatížíš zbytečnou pochybností a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Odhad zatížíš zbytečnou pochybností a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F868"/>
       <x:c r="G868">
@@ -22043,10 +22043,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D880" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Insight mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Insight mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E880" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v úsudku a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš zbytečnou okliku v úsudku a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F880"/>
       <x:c r="G880">
@@ -22190,10 +22190,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D887" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Insight mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E887" s="2" t="str">
-        <x:v>Cizí úmysl si domyslíš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Cizí úmysl si domyslíš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F887"/>
       <x:c r="G887">
@@ -22211,10 +22211,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D888" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Moudrosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E888" s="2" t="str">
-        <x:v>Odhad zatížíš zbytečnou pochybností a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Odhad zatížíš zbytečnou pochybností a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F888"/>
       <x:c r="G888">
@@ -22337,10 +22337,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D894" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E894" s="2" t="str">
-        <x:v>Správný dojem překryješ podezřením a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správný dojem překryješ podezřením a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F894"/>
       <x:c r="G894">
@@ -22379,10 +22379,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D896" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E896" s="2" t="str">
-        <x:v>Prosté jednání zbytečně překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Prosté jednání zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F896"/>
       <x:c r="G896">
@@ -22463,10 +22463,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D900" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E900" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v úsudku a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš zbytečnou okliku v úsudku a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F900"/>
       <x:c r="G900">
@@ -22631,10 +22631,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D908" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Medicine nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Medicine má postih −1d4.</x:v>
       </x:c>
       <x:c r="E908" s="2" t="str">
-        <x:v>Postup zatížíš zbytečným váháním a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Postup zatížíš zbytečným váháním a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F908"/>
       <x:c r="G908">
@@ -22652,10 +22652,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D909" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E909" s="2" t="str">
-        <x:v>Přidáš nepotřebnou odbornou odbočku a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš nepotřebnou odbornou odbočku a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F909"/>
       <x:c r="G909">
@@ -22736,10 +22736,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D913" s="2" t="str">
-        <x:v>Příští ověření dovednosti Medicine má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Medicine má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E913" s="2" t="str">
-        <x:v>Zaměníš podobnost za vysvětlení a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš podobnost za vysvětlení a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F913"/>
       <x:c r="G913">
@@ -22883,10 +22883,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D920" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Medicine mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Medicine mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E920" s="2" t="str">
-        <x:v>Přidáš zbytečnou diagnostickou okliku a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš zbytečnou diagnostickou okliku a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F920"/>
       <x:c r="G920">
@@ -23030,10 +23030,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D927" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Medicine má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Medicine má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E927" s="2" t="str">
-        <x:v>Chybějící poznatek si domyslíš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Chybějící poznatek si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F927"/>
       <x:c r="G927">
@@ -23051,10 +23051,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D928" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Moudrosti má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Medicine má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E928" s="2" t="str">
-        <x:v>Postup zatížíš zbytečným váháním a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Postup zatížíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F928"/>
       <x:c r="G928">
@@ -23303,10 +23303,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D940" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Medicine mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Medicine mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E940" s="2" t="str">
-        <x:v>Přidáš zbytečnou diagnostickou okliku a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš zbytečnou diagnostickou okliku a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F940"/>
       <x:c r="G940">
@@ -23450,10 +23450,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D947" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Medicine mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E947" s="2" t="str">
-        <x:v>Chybějící poznatek si domyslíš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Chybějící poznatek si domyslíš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F947"/>
       <x:c r="G947">
@@ -23471,10 +23471,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D948" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Moudrosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E948" s="2" t="str">
-        <x:v>Postup zatížíš zbytečným váháním a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Postup zatížíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F948"/>
       <x:c r="G948">
@@ -23597,10 +23597,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D954" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E954" s="2" t="str">
-        <x:v>Správný postup opravíš přehnaně a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správný postup opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F954"/>
       <x:c r="G954">
@@ -23639,10 +23639,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D956" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E956" s="2" t="str">
-        <x:v>Jednoduché posouzení překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jednoduché posouzení překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F956"/>
       <x:c r="G956">
@@ -23723,10 +23723,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D960" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E960" s="2" t="str">
-        <x:v>Přidáš zbytečnou diagnostickou okliku a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš zbytečnou diagnostickou okliku a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F960"/>
       <x:c r="G960">
@@ -23891,10 +23891,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D968" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Perception nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Perception má postih −1d4.</x:v>
       </x:c>
       <x:c r="E968" s="2" t="str">
-        <x:v>Pozorování zatížíš zbytečnou pochybností a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Pozorování zatížíš zbytečnou pochybností a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F968"/>
       <x:c r="G968">
@@ -23912,10 +23912,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D969" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E969" s="2" t="str">
-        <x:v>Zbytečně se soustředíš na maličkost a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Zbytečně se soustředíš na maličkost a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F969"/>
       <x:c r="G969">
@@ -23996,10 +23996,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D973" s="2" t="str">
-        <x:v>Příští ověření dovednosti Perception má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Perception má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E973" s="2" t="str">
-        <x:v>Zaměníš očekávání za skutečný vjem a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš očekávání za skutečný vjem a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F973"/>
       <x:c r="G973">
@@ -24143,10 +24143,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D980" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Perception mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Perception mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E980" s="2" t="str">
-        <x:v>Zbytečně si roztříštíš vlastní pozornost a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Zbytečně si roztříštíš vlastní pozornost a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F980"/>
       <x:c r="G980">
@@ -24290,10 +24290,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D987" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Perception má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Perception má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E987" s="2" t="str">
-        <x:v>Chybějící detail si domyslíš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Chybějící detail si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F987"/>
       <x:c r="G987" t="n">
@@ -24311,10 +24311,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D988" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Moudrosti má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Perception má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E988" s="2" t="str">
-        <x:v>Pozorování zatížíš zbytečnou pochybností a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Pozorování zatížíš zbytečnou pochybností a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F988"/>
       <x:c r="G988" t="n">
@@ -24563,10 +24563,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D1000" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Perception mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Perception mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E1000" s="2" t="str">
-        <x:v>Zbytečně si roztříštíš vlastní pozornost a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Zbytečně si roztříštíš vlastní pozornost a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1000"/>
       <x:c r="G1000" t="n">
@@ -24710,10 +24710,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1007" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Perception mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E1007" s="2" t="str">
-        <x:v>Chybějící detail si domyslíš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Chybějící detail si domyslíš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1007"/>
       <x:c r="G1007">
@@ -24731,10 +24731,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1008" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Moudrosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E1008" s="2" t="str">
-        <x:v>Pozorování zatížíš zbytečnou pochybností a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Pozorování zatížíš zbytečnou pochybností a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1008"/>
       <x:c r="G1008">
@@ -24857,10 +24857,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1014" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Perception mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Perception mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E1014" s="2" t="str">
-        <x:v>Správný postřeh překryješ dohadem a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správný postřeh překryješ dohadem a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1014"/>
       <x:c r="G1014">
@@ -24899,10 +24899,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1016" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1016" s="2" t="str">
-        <x:v>Soustředění zbytečně překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Soustředění zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1016"/>
       <x:c r="G1016">
@@ -24983,10 +24983,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1020" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1020" s="2" t="str">
-        <x:v>Zbytečně si roztříštíš vlastní pozornost a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Zbytečně si roztříštíš vlastní pozornost a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F1020"/>
       <x:c r="G1020">
@@ -25151,10 +25151,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1028" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Survival nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Survival má postih −1d4.</x:v>
       </x:c>
       <x:c r="E1028" s="2" t="str">
-        <x:v>Přípravu zatížíš zbytečným váháním a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Přípravu zatížíš zbytečným váháním a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1028"/>
       <x:c r="G1028">
@@ -25172,10 +25172,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1029" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1029" s="2" t="str">
-        <x:v>Přidáš nepotřebně důmyslný postup a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš nepotřebně důmyslný postup a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F1029"/>
       <x:c r="G1029">
@@ -25256,10 +25256,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1033" s="2" t="str">
-        <x:v>Příští ověření dovednosti Survival má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Survival má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1033" s="2" t="str">
-        <x:v>Zaměníš zkušenost za platné pravidlo a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš zkušenost za platné pravidlo a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1033"/>
       <x:c r="G1033">
@@ -25403,10 +25403,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1040" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Survival mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Survival mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E1040" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v postupu a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš zbytečnou okliku v postupu a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F1040"/>
       <x:c r="G1040">
@@ -25550,10 +25550,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1047" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Survival má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Survival má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E1047" s="2" t="str">
-        <x:v>Chybějící souvislost doplníš odhadem a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Chybějící souvislost doplníš odhadem a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F1047"/>
       <x:c r="G1047">
@@ -25571,10 +25571,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1048" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Moudrosti má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Survival má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E1048" s="2" t="str">
-        <x:v>Přípravu zatížíš zbytečným váháním a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Přípravu zatížíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1048"/>
       <x:c r="G1048">
@@ -25823,10 +25823,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1060" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Survival mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Survival mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E1060" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v postupu a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš zbytečnou okliku v postupu a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1060"/>
       <x:c r="G1060">
@@ -25970,10 +25970,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1067" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Survival mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E1067" s="2" t="str">
-        <x:v>Chybějící souvislost doplníš odhadem a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Chybějící souvislost doplníš odhadem a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1067"/>
       <x:c r="G1067">
@@ -25991,10 +25991,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1068" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Moudrosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E1068" s="2" t="str">
-        <x:v>Přípravu zatížíš zbytečným váháním a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Přípravu zatížíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1068"/>
       <x:c r="G1068">
@@ -26117,10 +26117,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1074" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E1074" s="2" t="str">
-        <x:v>Správný odhad opravíš přehnaně a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Správný odhad opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1074"/>
       <x:c r="G1074">
@@ -26159,10 +26159,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1076" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1076" s="2" t="str">
-        <x:v>Jednoduché řešení překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jednoduché řešení překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1076"/>
       <x:c r="G1076">
@@ -26243,10 +26243,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1080" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1080" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v postupu a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš zbytečnou okliku v postupu a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F1080"/>
       <x:c r="G1080">
@@ -26411,10 +26411,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1088" s="2" t="str">
-        <x:v>Při příštím ověření Charismatu nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Charismatu má postih −1d4.</x:v>
       </x:c>
       <x:c r="E1088" s="2" t="str">
-        <x:v>Projev zatížíš zbytečným váháním a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Projev zatížíš zbytečným váháním a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1088"/>
       <x:c r="G1088">
@@ -26432,10 +26432,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1089" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1089" s="2" t="str">
-        <x:v>Přidáš příliš okázalou jistotu a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš příliš okázalou jistotu a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F1089"/>
       <x:c r="G1089">
@@ -26516,10 +26516,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1093" s="2" t="str">
-        <x:v>Příští ověření Charismatu má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Charismatu má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1093" s="2" t="str">
-        <x:v>Zaměníš důraz za přirozenost a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš důraz za přirozenost a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1093"/>
       <x:c r="G1093">
@@ -26663,10 +26663,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1100" s="2" t="str">
-        <x:v>Příští dvě ověření Charismatu mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření Charismatu mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E1100" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu projevu a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš nepotřebnou změnu projevu a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F1100"/>
       <x:c r="G1100">
@@ -26810,10 +26810,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1107" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření Charismatu má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Charismatu má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E1107" s="2" t="str">
-        <x:v>Vlastní vystupování zbytečně přeženeš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Vlastní vystupování zbytečně přeženeš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F1107"/>
       <x:c r="G1107">
@@ -26831,10 +26831,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1108" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Charismatu má postih −2.</x:v>
+        <x:v>Příští ověření Charismatu má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E1108" s="2" t="str">
-        <x:v>Projev zatížíš zbytečným váháním a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Projev zatížíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1108"/>
       <x:c r="G1108">
@@ -27083,10 +27083,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1120" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření Charismatu mají postih −3.</x:v>
+        <x:v>Příští dvě ověření Charismatu mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E1120" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu projevu a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš nepotřebnou změnu projevu a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1120"/>
       <x:c r="G1120">
@@ -27230,10 +27230,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1127" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření Charismatu mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E1127" s="2" t="str">
-        <x:v>Vlastní vystupování zbytečně přeženeš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Vlastní vystupování zbytečně přeženeš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1127"/>
       <x:c r="G1127">
@@ -27251,10 +27251,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1128" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Charismatu mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E1128" s="2" t="str">
-        <x:v>Projev zatížíš zbytečným váháním a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Projev zatížíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1128"/>
       <x:c r="G1128">
@@ -27377,10 +27377,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1134" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E1134" s="2" t="str">
-        <x:v>Přirozený dojem opravíš přehnaně a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Přirozený dojem opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1134"/>
       <x:c r="G1134">
@@ -27419,10 +27419,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1136" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1136" s="2" t="str">
-        <x:v>Prosté vystupování zbytečně překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Prosté vystupování zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1136"/>
       <x:c r="G1136">
@@ -27503,10 +27503,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1140" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1140" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu projevu a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš nepotřebnou změnu projevu a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F1140"/>
       <x:c r="G1140">
@@ -27671,10 +27671,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1148" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Deception nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Deception má postih −1d4.</x:v>
       </x:c>
       <x:c r="E1148" s="2" t="str">
-        <x:v>Krytí zatížíš zbytečným váháním a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Krytí zatížíš zbytečným váháním a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1148"/>
       <x:c r="G1148">
@@ -27692,10 +27692,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1149" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1149" s="2" t="str">
-        <x:v>Přidáš nepotřebně složité vysvětlení a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš nepotřebně složité vysvětlení a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F1149"/>
       <x:c r="G1149">
@@ -27776,10 +27776,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1153" s="2" t="str">
-        <x:v>Příští ověření dovednosti Deception má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Deception má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1153" s="2" t="str">
-        <x:v>Zaměníš přehánění za přesvědčivost a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš přehánění za přesvědčivost a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1153"/>
       <x:c r="G1153">
@@ -27923,10 +27923,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1160" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Deception mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Deception mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E1160" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu verze a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš zbytečnou změnu verze a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F1160"/>
       <x:c r="G1160">
@@ -28070,10 +28070,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1167" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Deception má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Deception má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E1167" s="2" t="str">
-        <x:v>Maskování pravdy zbytečně přeženeš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Maskování pravdy zbytečně přeženeš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F1167"/>
       <x:c r="G1167">
@@ -28091,10 +28091,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1168" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Charismatu má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Deception má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E1168" s="2" t="str">
-        <x:v>Krytí zatížíš zbytečným váháním a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Krytí zatížíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1168"/>
       <x:c r="G1168">
@@ -28343,10 +28343,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1180" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Deception mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Deception mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E1180" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu verze a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš zbytečnou změnu verze a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1180"/>
       <x:c r="G1180">
@@ -28490,10 +28490,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1187" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Deception mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E1187" s="2" t="str">
-        <x:v>Maskování pravdy zbytečně přeženeš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Maskování pravdy zbytečně přeženeš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1187"/>
       <x:c r="G1187">
@@ -28511,10 +28511,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1188" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Charismatu mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E1188" s="2" t="str">
-        <x:v>Krytí zatížíš zbytečným váháním a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Krytí zatížíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1188"/>
       <x:c r="G1188">
@@ -28637,10 +28637,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1194" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E1194" s="2" t="str">
-        <x:v>Uváděnou verzi opravíš přehnaně a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Uváděnou verzi opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1194"/>
       <x:c r="G1194">
@@ -28679,10 +28679,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1196" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1196" s="2" t="str">
-        <x:v>Jednoduché krytí zbytečně překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jednoduché krytí zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1196"/>
       <x:c r="G1196">
@@ -28763,10 +28763,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1200" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1200" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu verze a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš zbytečnou změnu verze a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F1200"/>
       <x:c r="G1200">
@@ -28931,10 +28931,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1208" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Intimidation nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Intimidation má postih −1d4.</x:v>
       </x:c>
       <x:c r="E1208" s="2" t="str">
-        <x:v>Rozhodnost narušíš vlastním váháním a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Rozhodnost narušíš vlastním váháním a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1208"/>
       <x:c r="G1208">
@@ -28952,10 +28952,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1209" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1209" s="2" t="str">
-        <x:v>Přidáš nepotřebnou dramatickou vrstvu a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš nepotřebnou dramatickou vrstvu a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F1209"/>
       <x:c r="G1209">
@@ -29036,10 +29036,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1213" s="2" t="str">
-        <x:v>Příští ověření dovednosti Intimidation má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Intimidation má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1213" s="2" t="str">
-        <x:v>Zaměníš naléhavost za autoritu a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš naléhavost za autoritu a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1213"/>
       <x:c r="G1213">
@@ -29183,10 +29183,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1220" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Intimidation mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Intimidation mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E1220" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu důrazu a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš zbytečnou změnu důrazu a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F1220"/>
       <x:c r="G1220">
@@ -29330,10 +29330,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1227" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Intimidation má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Intimidation má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E1227" s="2" t="str">
-        <x:v>Výhrůžný dojem zbytečně přeženeš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Výhrůžný dojem zbytečně přeženeš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F1227"/>
       <x:c r="G1227">
@@ -29351,10 +29351,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1228" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Charismatu má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Intimidation má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E1228" s="2" t="str">
-        <x:v>Rozhodnost narušíš vlastním váháním a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Rozhodnost narušíš vlastním váháním a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1228"/>
       <x:c r="G1228">
@@ -29603,10 +29603,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1240" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Intimidation mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Intimidation mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E1240" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu důrazu a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš zbytečnou změnu důrazu a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1240"/>
       <x:c r="G1240">
@@ -29750,10 +29750,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1247" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Intimidation mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E1247" s="2" t="str">
-        <x:v>Výhrůžný dojem zbytečně přeženeš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Výhrůžný dojem zbytečně přeženeš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1247"/>
       <x:c r="G1247">
@@ -29771,10 +29771,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1248" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Charismatu mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E1248" s="2" t="str">
-        <x:v>Rozhodnost narušíš vlastním váháním a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Rozhodnost narušíš vlastním váháním a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1248"/>
       <x:c r="G1248">
@@ -29897,10 +29897,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1254" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E1254" s="2" t="str">
-        <x:v>Přirozený důraz opravíš přehnaně a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Přirozený důraz opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1254"/>
       <x:c r="G1254">
@@ -29939,10 +29939,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1256" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1256" s="2" t="str">
-        <x:v>Jednoduchý nátlak překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jednoduchý nátlak překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1256"/>
       <x:c r="G1256">
@@ -30023,10 +30023,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1260" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1260" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu důrazu a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš zbytečnou změnu důrazu a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F1260"/>
       <x:c r="G1260">
@@ -30191,10 +30191,10 @@
         <x:v>Sranda</x:v>
       </x:c>
       <x:c r="D1268" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Performance nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Performance má postih −1d4.</x:v>
       </x:c>
       <x:c r="E1268" s="2" t="str">
-        <x:v>Provedení narušíš zbytečným váháním a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Provedení narušíš zbytečným váháním a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1268"/>
       <x:c r="G1268" t="n">
@@ -30212,10 +30212,10 @@
         <x:v>Sranda</x:v>
       </x:c>
       <x:c r="D1269" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1269" s="2" t="str">
-        <x:v>Přidáš nepotřebnou efektní vsuvku a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš nepotřebnou efektní vsuvku a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F1269"/>
       <x:c r="G1269" t="n">
@@ -30296,10 +30296,10 @@
         <x:v>Sranda</x:v>
       </x:c>
       <x:c r="D1273" s="2" t="str">
-        <x:v>Příští ověření dovednosti Performance má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Performance má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1273" s="2" t="str">
-        <x:v>Zaměníš složitost za působivost a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš složitost za působivost a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1273"/>
       <x:c r="G1273" t="n">
@@ -30443,10 +30443,10 @@
         <x:v>Sranda</x:v>
       </x:c>
       <x:c r="D1280" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Performance mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Performance mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E1280" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu tempa a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš nepotřebnou změnu tempa a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F1280"/>
       <x:c r="G1280" t="n">
@@ -30590,10 +30590,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1287" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Performance má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Performance má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E1287" s="2" t="str">
-        <x:v>Podání svého výkonu přeženeš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Podání svého výkonu přeženeš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F1287"/>
       <x:c r="G1287">
@@ -30611,10 +30611,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1288" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Charismatu má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Performance má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E1288" s="2" t="str">
-        <x:v>Provedení narušíš zbytečným váháním a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Provedení narušíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1288"/>
       <x:c r="G1288">
@@ -30863,10 +30863,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1300" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Performance mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Performance mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E1300" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu tempa a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš nepotřebnou změnu tempa a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1300"/>
       <x:c r="G1300">
@@ -31010,10 +31010,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1307" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Performance mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E1307" s="2" t="str">
-        <x:v>Podání svého výkonu přeženeš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Podání svého výkonu přeženeš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1307"/>
       <x:c r="G1307">
@@ -31031,10 +31031,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1308" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Charismatu mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E1308" s="2" t="str">
-        <x:v>Provedení narušíš zbytečným váháním a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Provedení narušíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1308"/>
       <x:c r="G1308">
@@ -31157,10 +31157,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1314" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E1314" s="2" t="str">
-        <x:v>Přirozený výkon opravíš přehnaně a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Přirozený výkon opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1314"/>
       <x:c r="G1314">
@@ -31199,10 +31199,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1316" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1316" s="2" t="str">
-        <x:v>Jednoduché provedení zbytečně překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Jednoduché provedení zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1316"/>
       <x:c r="G1316">
@@ -31283,10 +31283,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1320" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1320" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu tempa a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš nepotřebnou změnu tempa a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F1320"/>
       <x:c r="G1320">
@@ -31451,10 +31451,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1328" s="2" t="str">
-        <x:v>Při příštím ověření dovednosti Persuasion nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Persuasion má postih −1d4.</x:v>
       </x:c>
       <x:c r="E1328" s="2" t="str">
-        <x:v>Vlastní postup zatížíš váháním a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Vlastní postup zatížíš váháním a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1328"/>
       <x:c r="G1328">
@@ -31472,10 +31472,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1329" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1329" s="2" t="str">
-        <x:v>Přidáš nepotřebné velkolepé zdůvodnění a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Přidáš nepotřebné velkolepé zdůvodnění a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F1329"/>
       <x:c r="G1329">
@@ -31556,10 +31556,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1333" s="2" t="str">
-        <x:v>Příští ověření dovednosti Persuasion má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření dovednosti Persuasion má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1333" s="2" t="str">
-        <x:v>Zaměníš opakování za přesvědčivost a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš opakování za přesvědčivost a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1333"/>
       <x:c r="G1333">
@@ -31703,10 +31703,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1340" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Persuasion mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření dovednosti Persuasion mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E1340" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu přístupu a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš nepotřebnou změnu přístupu a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F1340"/>
       <x:c r="G1340">
@@ -31850,10 +31850,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D1347" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření dovednosti Persuasion má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Persuasion má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E1347" s="2" t="str">
-        <x:v>Snaze přesvědčit příliš podlehneš a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Snaze přesvědčit příliš podlehneš a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F1347"/>
       <x:c r="G1347" t="n">
@@ -31871,10 +31871,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D1348" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Charismatu má postih −2.</x:v>
+        <x:v>Příští ověření dovednosti Persuasion má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E1348" s="2" t="str">
-        <x:v>Vlastní postup zatížíš váháním a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Vlastní postup zatížíš váháním a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1348"/>
       <x:c r="G1348" t="n">
@@ -32123,10 +32123,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D1360" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření dovednosti Persuasion mají postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Persuasion mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E1360" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu přístupu a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš nepotřebnou změnu přístupu a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1360"/>
       <x:c r="G1360" t="n">
@@ -32270,10 +32270,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1367" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření dovednosti Persuasion mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E1367" s="2" t="str">
-        <x:v>Snaze přesvědčit příliš podlehneš a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Snaze přesvědčit příliš podlehneš a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1367"/>
       <x:c r="G1367">
@@ -32291,10 +32291,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1368" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Charismatu mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E1368" s="2" t="str">
-        <x:v>Vlastní postup zatížíš váháním a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Vlastní postup zatížíš váháním a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1368"/>
       <x:c r="G1368">
@@ -32417,10 +32417,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1374" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E1374" s="2" t="str">
-        <x:v>Srozumitelný důvod opravíš přehnaně a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Srozumitelný důvod opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1374"/>
       <x:c r="G1374">
@@ -32459,10 +32459,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1376" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1376" s="2" t="str">
-        <x:v>Prosté zdůvodnění zbytečně překombinuješ a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Prosté zdůvodnění zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1376"/>
       <x:c r="G1376">
@@ -32543,10 +32543,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1380" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1380" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu přístupu a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš nepotřebnou změnu přístupu a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F1380"/>
       <x:c r="G1380">
@@ -32711,10 +32711,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1388" s="2" t="str">
-        <x:v>Při příštím ověření Odolnosti nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Odolnosti má postih −1d4.</x:v>
       </x:c>
       <x:c r="E1388" s="2" t="str">
-        <x:v>Námahu rozvrhneš příliš lehkovážně a dobře míněná pomoc tě jen mate.</x:v>
+        <x:v>Námahu rozvrhneš příliš lehkovážně a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1388"/>
       <x:c r="G1388">
@@ -32732,10 +32732,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1389" s="2" t="str">
-        <x:v>Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1389" s="2" t="str">
-        <x:v>Vlastní odolnost zbytečně testuješ a další pomocí bys přidal jen zmatek.</x:v>
+        <x:v>Vlastní odolnost zbytečně testuješ a při nebezpečí zbytečně zaváháš.</x:v>
       </x:c>
       <x:c r="F1389"/>
       <x:c r="G1389">
@@ -32816,10 +32816,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1393" s="2" t="str">
-        <x:v>Příští ověření Odolnosti má postih −1 a nemůže získat výhodu z akce Pomoc.</x:v>
+        <x:v>Příští ověření Odolnosti má postih −1. Příští záchranný hod má postih −1.</x:v>
       </x:c>
       <x:c r="E1393" s="2" t="str">
-        <x:v>Zaměníš napětí za skutečnou výdrž a další pokus si tvrdohlavě zkomplikuješ sám.</x:v>
+        <x:v>Zaměníš napětí za skutečnou výdrž a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1393"/>
       <x:c r="G1393">
@@ -32963,10 +32963,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1400" s="2" t="str">
-        <x:v>Příští dvě ověření Odolnosti mají postih −1. Do vyhodnocení tvého příštího ověření vlastnosti nemůžeš provádět akci Pomoc.</x:v>
+        <x:v>Příští dvě ověření Odolnosti mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
       </x:c>
       <x:c r="E1400" s="2" t="str">
-        <x:v>Přidáš námahu ve špatnou chvíli a dalších pár pokusů přehnaně hlídáš.</x:v>
+        <x:v>Přidáš námahu ve špatnou chvíli a opatrnost zpomalí další pokusy i reakce.</x:v>
       </x:c>
       <x:c r="F1400"/>
       <x:c r="G1400">
@@ -33110,10 +33110,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1407" s="2" t="str">
-        <x:v>Při příštích dvou ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští ověření Odolnosti má postih −2.</x:v>
+        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Odolnosti má navíc postih −2.</x:v>
       </x:c>
       <x:c r="E1407" s="2" t="str">
-        <x:v>Pokusíš se všechno přestát silou a cizí pomoc přes vlastní zmatek nevyužiješ.</x:v>
+        <x:v>Pokusíš se všechno přestát silou a zmatek přeneseš i do dalších činností.</x:v>
       </x:c>
       <x:c r="F1407"/>
       <x:c r="G1407">
@@ -33131,10 +33131,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1408" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští ověření Odolnosti má postih −2.</x:v>
+        <x:v>Příští ověření Odolnosti má postih −2. Příští záchranný hod má postih −2.</x:v>
       </x:c>
       <x:c r="E1408" s="2" t="str">
-        <x:v>Námahu rozvrhneš příliš lehkovážně a kvůli nejistotě nedokážeš nikoho podpořit.</x:v>
+        <x:v>Námahu rozvrhneš příliš lehkovážně a nejistota ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1408"/>
       <x:c r="G1408">
@@ -33383,10 +33383,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1420" s="2" t="str">
-        <x:v>Do vyhodnocení tvých příštích dvou ověření vlastností nemůžeš provádět akci Pomoc. Příští dvě ověření Odolnosti mají postih −3.</x:v>
+        <x:v>Příští dvě ověření Odolnosti mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
       </x:c>
       <x:c r="E1420" s="2" t="str">
-        <x:v>Přidáš námahu ve špatnou chvíli a další pokusy ti zkomplikuje vlastní nerozhodnost.</x:v>
+        <x:v>Přidáš námahu ve špatnou chvíli a zmatek ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1420"/>
       <x:c r="G1420">
@@ -33530,10 +33530,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1427" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc. Příští tři ověření Odolnosti mají postih −5.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
       </x:c>
       <x:c r="E1427" s="2" t="str">
-        <x:v>Pokusíš se všechno přestát silou a bolest nepřebije ani dobře míněná pomoc.</x:v>
+        <x:v>Pokusíš se všechno přestát silou a bolest ti naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1427"/>
       <x:c r="G1427">
@@ -33551,10 +33551,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1428" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření Odolnosti mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
       </x:c>
       <x:c r="E1428" s="2" t="str">
-        <x:v>Námahu rozvrhneš příliš lehkovážně a bolest ti znemožní spolehlivě podpořit ostatní.</x:v>
+        <x:v>Námahu rozvrhneš příliš lehkovážně a bolest ti ztíží výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1428"/>
       <x:c r="G1428">
@@ -33677,10 +33677,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1434" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
       </x:c>
       <x:c r="E1434" s="2" t="str">
-        <x:v>Drobnou slabost překryješ přepětím a další pokusy ti ztíží prudká bolest.</x:v>
+        <x:v>Drobnou slabost překryješ přepětím a prudká bolest naruší výkon i obranu.</x:v>
       </x:c>
       <x:c r="F1434"/>
       <x:c r="G1434">
@@ -33719,10 +33719,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1436" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu. Při příštích třech ověřeních vlastností nemůžeš získat výhodu z akce Pomoc.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1436" s="2" t="str">
-        <x:v>Přirozenou výdrž zbytečně přepínáš a bolest ti naruší další samostatný výkon.</x:v>
+        <x:v>Přirozenou výdrž zbytečně přepínáš a otřes ti naruší výkon i pohotovost.</x:v>
       </x:c>
       <x:c r="F1436"/>
       <x:c r="G1436">
@@ -33803,10 +33803,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1440" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do vyhodnocení tvých příštích tří ověření vlastností nemůžeš provádět akci Pomoc. Příští tři ověření vlastností mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
       </x:c>
       <x:c r="E1440" s="2" t="str">
-        <x:v>Přidáš námahu ve špatnou chvíli a bolest ti rozbije výkon i spolupráci.</x:v>
+        <x:v>Přidáš námahu ve špatnou chvíli a bolest ti rozbije soustředění i obranu.</x:v>
       </x:c>
       <x:c r="F1440"/>
       <x:c r="G1440">

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Útok" sheetId="1" r:id="Rc99f640131614f96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obrana" sheetId="2" r:id="Rdf26b9dc650f4d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="3" r:id="Rc491ba76c66d48e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Útok" sheetId="1" r:id="Ra5157a2018464642"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obrana" sheetId="2" r:id="R2d5f63b255234005"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="3" r:id="R85383b2b64994222"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1165,10 +1165,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C41" s="2" t="str">
-        <x:v>Do začátku svého příštího tahu nemůžeš používat reakce; příští útok na dálku do konce svého příštího tahu má −1 k hodu na zásah.</x:v>
+        <x:v>Tvé příští dva útoky na dálku do konce tvého příštího tahu mají −2 k hodu na zásah.</x:v>
       </x:c>
       <x:c r="D41" s="2" t="str">
-        <x:v>Než znovu získáš přehled, nedokážeš pohotově reagovat ani přesně navázat útokem.</x:v>
+        <x:v>Nezvládnutý útok tě rozhodí a při dalších pokusech ztratíš potřebnou jistotu.</x:v>
       </x:c>
       <x:c r="E41"/>
       <x:c r="F41">
@@ -1183,10 +1183,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C42" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu nemůžeš provádět útoky na dálku ani používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu nemůžeš provádět útoky na dálku.</x:v>
       </x:c>
       <x:c r="D42" s="2" t="str">
-        <x:v>Bolestivě se přetížíš a dočasně nedokážeš mířit ani pohotově reagovat.</x:v>
+        <x:v>Selhání ti rozbije provedení a další útoky nedokážeš dokončit.</x:v>
       </x:c>
       <x:c r="E42"/>
       <x:c r="F42">
@@ -1201,10 +1201,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C43" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Ve svém příštím tahu nemůžeš provádět akce ani bonusové akce.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="D43" s="2" t="str">
-        <x:v>Selhání tě zasáhne prudkým šokem a další okamžik nezvládneš soustředěně jednat.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="E43"/>
       <x:c r="F43">
@@ -1219,10 +1219,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C44" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu mají všechny tvé útoky nevýhodu a nemůžeš používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu mají všechny tvé útoky nevýhodu.</x:v>
       </x:c>
       <x:c r="D44" s="2" t="str">
-        <x:v>Silný otřes ti naruší všechny další útoky a připraví tě o pohotové reakce.</x:v>
+        <x:v>Selhání tě rozhodí a další útoky nedokážeš správně načasovat.</x:v>
       </x:c>
       <x:c r="E44"/>
       <x:c r="F44">
@@ -1255,10 +1255,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C46" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého příštího tahu mají všechny tvé hody na útok a záchranné hody postih −4.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého příštího tahu mají všechny tvé hody na útok postih −4.</x:v>
       </x:c>
       <x:c r="D46" s="2" t="str">
-        <x:v>Prudký psychický otřes ti výrazně zhorší přesnost útoků i schopnost odvracet nebezpečí.</x:v>
+        <x:v>Soustředění se ti rozpadne a další útoky provádíš s velkou nejistotou.</x:v>
       </x:c>
       <x:c r="E46"/>
       <x:c r="F46">
@@ -1273,10 +1273,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C47" s="2" t="str">
-        <x:v>Ve svém příštím tahu nemůžeš provádět akce. Do konce svého druhého následujícího tahu nemůžeš používat reakce.</x:v>
+        <x:v>Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="D47" s="2" t="str">
-        <x:v>Ztratíš kontrolu nad dalším postupem a delší chvíli nedokážeš pohotově reagovat.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="E47"/>
       <x:c r="F47">
@@ -1309,10 +1309,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C49" s="2" t="str">
-        <x:v>Do konce svého druhého následujícího tahu nemůžeš používat bonusové akce ani reakce a všechny tvé útoky mají nevýhodu.</x:v>
+        <x:v>Do konce svého druhého následujícího tahu mají všechny tvé útoky nevýhodu.</x:v>
       </x:c>
       <x:c r="D49" s="2" t="str">
-        <x:v>Nezdar ti rozbije rytmus, zhorší další útoky a znemožní rychlé navázání i reakce.</x:v>
+        <x:v>Selhání tě rozhodí a další útoky nedokážeš správně načasovat.</x:v>
       </x:c>
       <x:c r="E49"/>
       <x:c r="F49">
@@ -1327,10 +1327,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C50" s="2" t="str">
-        <x:v>Do konce svého příštího tahu nemůžeš útočit, provádět akce, bonusové akce ani používat reakce.</x:v>
+        <x:v>Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="D50" s="2" t="str">
-        <x:v>Úplně ztratíš přehled a chvíli se nedokážeš zmoci na útok, jednání ani reakci.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="E50"/>
       <x:c r="F50">
@@ -1345,10 +1345,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C51" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu máš −3 k AC a nevýhodu na všechny záchranné hody.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu máš −3 k AC.</x:v>
       </x:c>
       <x:c r="D51" s="2" t="str">
-        <x:v>Prudký otřes tě zasáhne natolik, že se delší chvíli nedokážeš účinně chránit.</x:v>
+        <x:v>Selhání ti rozbije obranu a nedokážeš se pořádně krýt.</x:v>
       </x:c>
       <x:c r="E51"/>
       <x:c r="F51">
@@ -1363,10 +1363,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C52" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Ve svém příštím tahu máš −3 ke všem hodům na útok a můžeš využít jen polovinu pohybu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Ve svém příštím tahu máš −3 ke všem hodům na útok.</x:v>
       </x:c>
       <x:c r="D52" s="2" t="str">
-        <x:v>Bolestivé přetížení ti výrazně omezí další přesun i přesnost útoků.</x:v>
+        <x:v>Útok tě rozhodí a další zásahy zkoušíš bez potřebné jistoty.</x:v>
       </x:c>
       <x:c r="E52"/>
       <x:c r="F52">
@@ -1381,10 +1381,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C53" s="2" t="str">
-        <x:v>Do konce svého příštího tahu mají všechny útoky nepřátel proti tobě výhodu. Do konce svého druhého následujícího tahu nemůžeš používat reakce.</x:v>
+        <x:v>Do konce svého příštího tahu mají všechny útoky nepřátel proti tobě výhodu.</x:v>
       </x:c>
       <x:c r="D53" s="2" t="str">
-        <x:v>Po selhání zůstaneš nebezpečně odkrytý a nezvládneš pohotově reagovat na okolí.</x:v>
+        <x:v>Zcela odkryješ svou obranu a soupeřům nabídneš snadný cíl.</x:v>
       </x:c>
       <x:c r="E53"/>
       <x:c r="F53">
@@ -1435,10 +1435,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C56" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Ve svém příštím tahu nemůžeš provádět akce ani bonusové akce a do konce svého příštího tahu nemůžeš používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="D56" s="2" t="str">
-        <x:v>Silné přetížení tě zraní a na chvíli připraví o jednání i pohotové reakce.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="E56"/>
       <x:c r="F56">
@@ -1453,10 +1453,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C57" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu máš −3 k AC a nemůžeš používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu máš −3 k AC.</x:v>
       </x:c>
       <x:c r="D57" s="2" t="str">
-        <x:v>Následky zranění ti rozvrátí obranu a znemožní pohotově reagovat.</x:v>
+        <x:v>Selhání ti rozbije obranu a nedokážeš se pořádně krýt.</x:v>
       </x:c>
       <x:c r="E57"/>
       <x:c r="F57">
@@ -1471,10 +1471,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C58" s="2" t="str">
-        <x:v>Do konce svého druhého následujícího tahu nemůžeš provádět útoky na dálku. Ve svém příštím tahu nemůžeš používat bonusovou akci.</x:v>
+        <x:v>Do konce svého druhého následujícího tahu nemůžeš provádět útoky na dálku.</x:v>
       </x:c>
       <x:c r="D58" s="2" t="str">
-        <x:v>Zcela ztratíš kontrolu nad mířením a náprava tě připraví o rychlé navázání.</x:v>
+        <x:v>Selhání ti rozbije provedení a další útoky nedokážeš dokončit.</x:v>
       </x:c>
       <x:c r="E58"/>
       <x:c r="F58">
@@ -1489,10 +1489,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C59" s="2" t="str">
-        <x:v>Ve svém příštím tahu nemůžeš provádět akce ani bonusové akce. Do konce svého příštího tahu máš −3 k AC.</x:v>
+        <x:v>Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="D59" s="2" t="str">
-        <x:v>Nezvládnutý pokus tě úplně rozhodí a při vzpamatovávání zůstaneš nebezpečně odkrytý.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="E59"/>
       <x:c r="F59">
@@ -1507,10 +1507,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C60" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu mají všechny tvé záchranné hody nevýhodu a nemůžeš používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu mají všechny tvé záchranné hody nevýhodu.</x:v>
       </x:c>
       <x:c r="D60" s="2" t="str">
-        <x:v>Bolestivý šok ti naruší pohotovost a delší chvíli nedokážeš účinně odvracet nebezpečí.</x:v>
+        <x:v>Otřes tě připraví o jistotu a dalším hrozbám odoláváš jen obtížně.</x:v>
       </x:c>
       <x:c r="E60"/>
       <x:c r="F60">
@@ -2245,10 +2245,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C101" s="2" t="str">
-        <x:v>Do začátku svého příštího tahu nemůžeš používat reakce; příští útok na blízko do konce svého příštího tahu má −1 k hodu na zásah.</x:v>
+        <x:v>Tvé příští dva útoky na blízko do konce tvého příštího tahu mají −2 k hodu na zásah.</x:v>
       </x:c>
       <x:c r="D101" s="2" t="str">
-        <x:v>Zaváhání ti rozhodí pozornost i přesnost a chvíli nedokážeš pohotově reagovat.</x:v>
+        <x:v>Nezvládnutý útok tě rozhodí a při dalších pokusech ztratíš potřebnou jistotu.</x:v>
       </x:c>
       <x:c r="E101"/>
       <x:c r="F101">
@@ -2263,10 +2263,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C102" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Ve svém příštím tahu nemůžeš provádět akce ani bonusové akce a do konce svého příštího tahu nemůžeš používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="D102" s="2" t="str">
-        <x:v>Bolestivý otřes tě na chvíli připraví o schopnost jednat i pohotově reagovat.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="E102"/>
       <x:c r="F102">
@@ -2281,10 +2281,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C103" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu nemůžeš provádět útoky na blízko ani používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu nemůžeš provádět útoky na blízko.</x:v>
       </x:c>
       <x:c r="D103" s="2" t="str">
-        <x:v>Nezvládnutý útok tě zraní a na čas znemožní další boj zblízka i reakce.</x:v>
+        <x:v>Selhání ti rozbije provedení a další útoky nedokážeš dokončit.</x:v>
       </x:c>
       <x:c r="E103"/>
       <x:c r="F103">
@@ -2299,10 +2299,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C104" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Ve svém příštím tahu nemůžeš provádět akce ani bonusové akce.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="D104" s="2" t="str">
-        <x:v>Prudký šok tě bolestivě zasáhne a na další okamžik přeruší tvoje soustředěné jednání.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="E104"/>
       <x:c r="F104">
@@ -2317,10 +2317,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C105" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu mají všechny tvé útoky nevýhodu a nemůžeš používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu mají všechny tvé útoky nevýhodu.</x:v>
       </x:c>
       <x:c r="D105" s="2" t="str">
-        <x:v>Otřes po selhání ti rozvrátí další útoky a znemožní rychle reagovat.</x:v>
+        <x:v>Selhání tě rozhodí a další útoky nedokážeš správně načasovat.</x:v>
       </x:c>
       <x:c r="E105"/>
       <x:c r="F105">
@@ -2353,10 +2353,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C107" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého příštího tahu mají všechny tvé hody na útok a záchranné hody postih −4.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého příštího tahu mají všechny tvé hody na útok postih −4.</x:v>
       </x:c>
       <x:c r="D107" s="2" t="str">
-        <x:v>Bolestivý psychický otřes ti výrazně naruší útoky i obranu před nebezpečím.</x:v>
+        <x:v>Soustředění se ti rozpadne a další útoky provádíš s velkou nejistotou.</x:v>
       </x:c>
       <x:c r="E107"/>
       <x:c r="F107">
@@ -2371,10 +2371,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C108" s="2" t="str">
-        <x:v>Ve svém příštím tahu nemůžeš provádět akce. Do konce svého druhého následujícího tahu nemůžeš používat reakce.</x:v>
+        <x:v>Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="D108" s="2" t="str">
-        <x:v>Po selhání nedokážeš navázat dalším jednáním a ztracené reakce se vracejí pomalu.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="E108"/>
       <x:c r="F108">
@@ -2407,10 +2407,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C110" s="2" t="str">
-        <x:v>Do konce svého druhého následujícího tahu nemůžeš používat bonusové akce ani reakce a všechny tvé útoky mají nevýhodu.</x:v>
+        <x:v>Do konce svého druhého následujícího tahu mají všechny tvé útoky nevýhodu.</x:v>
       </x:c>
       <x:c r="D110" s="2" t="str">
-        <x:v>Selhání ti rozvrátí bojové tempo a připraví tě o rychlé jednání i reakce.</x:v>
+        <x:v>Selhání tě rozhodí a další útoky nedokážeš správně načasovat.</x:v>
       </x:c>
       <x:c r="E110"/>
       <x:c r="F110">
@@ -2425,10 +2425,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C111" s="2" t="str">
-        <x:v>Do konce svého příštího tahu nemůžeš útočit, provádět akce, bonusové akce ani používat reakce.</x:v>
+        <x:v>Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="D111" s="2" t="str">
-        <x:v>Následky nezdaru tě úplně ochromí a na chvíli znemožní útok, jednání i reakce.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="E111"/>
       <x:c r="F111">
@@ -2443,10 +2443,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C112" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu máš −3 k AC a nevýhodu na všechny záchranné hody.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu máš −3 k AC.</x:v>
       </x:c>
       <x:c r="D112" s="2" t="str">
-        <x:v>Silný otřes tě připraví o jistotu v obraně a schopnost dobře odvracet nebezpečí.</x:v>
+        <x:v>Selhání ti rozbije obranu a nedokážeš se pořádně krýt.</x:v>
       </x:c>
       <x:c r="E112"/>
       <x:c r="F112">
@@ -2461,10 +2461,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C113" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Ve svém příštím tahu máš −3 ke všem hodům na útok a můžeš využít jen polovinu pohybu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Ve svém příštím tahu máš −3 ke všem hodům na útok.</x:v>
       </x:c>
       <x:c r="D113" s="2" t="str">
-        <x:v>Bolestivě se přetížíš a další útoky i přesun zvládáš jen s výraznými obtížemi.</x:v>
+        <x:v>Útok tě rozhodí a další zásahy zkoušíš bez potřebné jistoty.</x:v>
       </x:c>
       <x:c r="E113"/>
       <x:c r="F113">
@@ -2479,10 +2479,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C114" s="2" t="str">
-        <x:v>Do konce svého příštího tahu mají všechny útoky nepřátel proti tobě výhodu. Do konce svého druhého následujícího tahu nemůžeš používat reakce.</x:v>
+        <x:v>Do konce svého příštího tahu mají všechny útoky nepřátel proti tobě výhodu.</x:v>
       </x:c>
       <x:c r="D114" s="2" t="str">
-        <x:v>Po nezvládnutém útoku zůstaneš výrazně zranitelný a nestihneš pohotově reagovat.</x:v>
+        <x:v>Zcela odkryješ svou obranu a soupeřům nabídneš snadný cíl.</x:v>
       </x:c>
       <x:c r="E114"/>
       <x:c r="F114">
@@ -2533,10 +2533,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C117" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu máš −3 k AC a nemůžeš používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu máš −3 k AC.</x:v>
       </x:c>
       <x:c r="D117" s="2" t="str">
-        <x:v>Bolestivé zranění ti zhorší obranu a na delší chvíli vyřadí tvoje reakce.</x:v>
+        <x:v>Selhání ti rozbije obranu a nedokážeš se pořádně krýt.</x:v>
       </x:c>
       <x:c r="E117"/>
       <x:c r="F117">
@@ -2551,10 +2551,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C118" s="2" t="str">
-        <x:v>Do konce svého druhého následujícího tahu nemůžeš provádět útoky na blízko. Ve svém příštím tahu nemůžeš používat bonusovou akci.</x:v>
+        <x:v>Do konce svého druhého následujícího tahu nemůžeš provádět útoky na blízko.</x:v>
       </x:c>
       <x:c r="D118" s="2" t="str">
-        <x:v>Ztratíš kontrolu nad bojem zblízka a náprava ti vezme čas k rychlému jednání.</x:v>
+        <x:v>Selhání ti rozbije provedení a další útoky nedokážeš dokončit.</x:v>
       </x:c>
       <x:c r="E118"/>
       <x:c r="F118">
@@ -2569,10 +2569,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C119" s="2" t="str">
-        <x:v>Ve svém příštím tahu nemůžeš provádět akce ani bonusové akce. Do konce svého příštího tahu máš −3 k AC.</x:v>
+        <x:v>Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="D119" s="2" t="str">
-        <x:v>Nepovedený útok tě zcela vyvede z míry a neschopnost navázat zhorší i obranu.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="E119"/>
       <x:c r="F119">
@@ -2587,10 +2587,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C120" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu mají všechny tvé záchranné hody nevýhodu a nemůžeš používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Do konce svého druhého následujícího tahu mají všechny tvé záchranné hody nevýhodu.</x:v>
       </x:c>
       <x:c r="D120" s="2" t="str">
-        <x:v>Bolestivý otřes ti rozvrátí pohotovost a schopnost včas odvracet další nebezpečí.</x:v>
+        <x:v>Otřes tě připraví o jistotu a dalším hrozbám odoláváš jen obtížně.</x:v>
       </x:c>
       <x:c r="E120"/>
       <x:c r="F120">
@@ -3196,10 +3196,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="2" t="str">
-        <x:v>Do konce svého příštího tahu nemůžeš používat reakce ani bonusové akce.</x:v>
+        <x:v>Do konce svého příštího tahu nemůžeš používat reakce.</x:v>
       </x:c>
       <x:c r="C38" s="2" t="str">
-        <x:v>Nezvládnutá obrana tě rozhodí a připraví o pohotové reakce i další manévry.</x:v>
+        <x:v>Nezvládnutá obrana tě zaměstná a nedokážeš pohotově reagovat.</x:v>
       </x:c>
       <x:c r="D38"/>
       <x:c r="E38">
@@ -3226,10 +3226,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B40" s="2" t="str">
-        <x:v>Ve svém příštím tahu nemůžeš použít akci Sprint ani Odpoutání.</x:v>
+        <x:v>Ve svém příštím tahu nemůžeš použít akci Sprint.</x:v>
       </x:c>
       <x:c r="C40" s="2" t="str">
-        <x:v>Ztratíš rytmus a nedokážeš se rychle přesunout ani bezpečně odpoutat.</x:v>
+        <x:v>Nezvládnutá obrana tě rozhodí a nedokážeš se rozběhnout naplno.</x:v>
       </x:c>
       <x:c r="D40"/>
       <x:c r="E40">
@@ -3286,10 +3286,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B44" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Ve svém příštím tahu nemůžeš používat akci ani bonusovou akci.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="C44" s="2" t="str">
-        <x:v>Zničující selhání obrany tě bolestivě ochromí a nezvládneš žádnou další akci.</x:v>
+        <x:v>Bolest ti naruší soustředění natolik, že další plnohodnotnou akci nezvládneš.</x:v>
       </x:c>
       <x:c r="D44"/>
       <x:c r="E44">
@@ -3346,10 +3346,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B48" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Do konce svého příštího tahu nemůžeš používat reakce ani bonusové akce.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Do konce svého příštího tahu nemůžeš používat reakce.</x:v>
       </x:c>
       <x:c r="C48" s="2" t="str">
-        <x:v>Selhání obrany tě bolestivě vyřadí z rytmu a znemožní pohotové jednání.</x:v>
+        <x:v>Bolest tě zaměstná natolik, že na dění kolem nedokážeš pohotově reagovat.</x:v>
       </x:c>
       <x:c r="D48"/>
       <x:c r="E48">
@@ -3376,10 +3376,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B50" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do začátku svého příštího tahu mají útoky proti tobě výhodu a ve svém příštím tahu nemůžeš útočit.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Do začátku svého příštího tahu mají útoky proti tobě výhodu.</x:v>
       </x:c>
       <x:c r="C50" s="2" t="str">
-        <x:v>Bolestivě se odkryješ a nezbude ti jistota ani na vlastní útok.</x:v>
+        <x:v>Bolest ti rozbije obranu a nechá tě vystaveného dalším útokům.</x:v>
       </x:c>
       <x:c r="D50"/>
       <x:c r="E50">
@@ -3406,10 +3406,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B52" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu nemůžeš provádět akci Sprint ani Odpoutání.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu nemůžeš provádět akci Sprint.</x:v>
       </x:c>
       <x:c r="C52" s="2" t="str">
-        <x:v>Bolestivě ztratíš kontrolu nad pohybem a nezvládneš rychlé ani bezpečné odpoutání.</x:v>
+        <x:v>Bolest naruší tvůj pohyb a nedokážeš se rozběhnout naplno.</x:v>
       </x:c>
       <x:c r="D52"/>
       <x:c r="E52">
@@ -3421,10 +3421,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B53" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do začátku svého druhého následujícího tahu máš −3 k AC a nemůžeš používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Do začátku svého druhého následujícího tahu máš −3 k AC.</x:v>
       </x:c>
       <x:c r="C53" s="2" t="str">
-        <x:v>Bolest ti rozbije krytí i pohotovost a další hrozby nestíháš zachytit.</x:v>
+        <x:v>Bolest ti rozbije obranu a nedokážeš se pořádně krýt.</x:v>
       </x:c>
       <x:c r="D53"/>
       <x:c r="E53">
@@ -3436,10 +3436,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B54" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Ve svém příštím tahu nemůžeš provést akci Útok ani seslat kouzlo.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="C54" s="2" t="str">
-        <x:v>Ničivá bolest ti znemožní další soustředěný útok i jakékoliv seslání kouzla.</x:v>
+        <x:v>Otřes tě rozhodí natolik, že nedokážeš provést další plnohodnotnou akci.</x:v>
       </x:c>
       <x:c r="D54"/>
       <x:c r="E54">
@@ -3466,10 +3466,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B56" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Ve svém příštím tahu nemůžeš používat akci a do konce tohoto tahu nemůžeš používat reakce.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Ve svém příštím tahu nemůžeš provádět akce.</x:v>
       </x:c>
       <x:c r="C56" s="2" t="str">
-        <x:v>Prudce se přetížíš a bolest tě připraví o jednání i pohotovou reakci.</x:v>
+        <x:v>Bolest ti naruší soustředění natolik, že další plnohodnotnou akci nezvládneš.</x:v>
       </x:c>
       <x:c r="D56"/>
       <x:c r="E56">
@@ -3496,10 +3496,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B58" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu mají tvé záchranné hody na Sílu a Obratnost nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu mají tvé záchranné hody nevýhodu.</x:v>
       </x:c>
       <x:c r="C58" s="2" t="str">
-        <x:v>Bolestivě si přetížíš tělo a nedokážeš dobře vzdorovat ani včas uhnout.</x:v>
+        <x:v>Bolest tě připraví o jistotu a dalším hrozbám odoláváš jen obtížně.</x:v>
       </x:c>
       <x:c r="D58"/>
       <x:c r="E58">
@@ -3511,10 +3511,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B59" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu nemůžeš používat bonusové akce ani reakce.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu nemůžeš používat bonusové akce.</x:v>
       </x:c>
       <x:c r="C59" s="2" t="str">
-        <x:v>Těžce narušíš vlastní rytmus a bolest ti znemožní pohotové doplňující jednání.</x:v>
+        <x:v>Bolest tě zaměstná natolik, že další manévr navíc nezvládneš.</x:v>
       </x:c>
       <x:c r="D59"/>
       <x:c r="E59">
@@ -3541,10 +3541,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B61" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu nemůžeš používat reakce a můžeš v každém tahu využít nejvýše polovinu své rychlosti (zaokrouhli dolů na celé stopy).</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Do konce svého druhého následujícího tahu můžeš v každém tahu využít nejvýše polovinu své rychlosti (zaokrouhli dolů na celé stopy).</x:v>
       </x:c>
       <x:c r="C61" s="2" t="str">
-        <x:v>Bolestivě ztratíš koordinaci a nezvládneš pohotově reagovat ani se rychle přesouvat.</x:v>
+        <x:v>Po nezvládnuté obraně se pohybuješ opatrně a každý přesun ti trvá déle.</x:v>
       </x:c>
       <x:c r="D61"/>
       <x:c r="E61">
@@ -3836,10 +3836,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="2" t="str">
-        <x:v>Příští ověření Síly má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření Síly má postih −2.</x:v>
       </x:c>
       <x:c r="E13" s="2" t="str">
-        <x:v>Provedení obětuješ velkému záběru a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Provedení obětuješ velkému záběru a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F13"/>
       <x:c r="G13">
@@ -3983,10 +3983,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D20" s="2" t="str">
-        <x:v>Příští dvě ověření Síly mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření Síly mají postih −1.</x:v>
       </x:c>
       <x:c r="E20" s="2" t="str">
-        <x:v>Přidáš důraz ve špatnou chvíli a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš důraz ve špatnou chvíli a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F20"/>
       <x:c r="G20">
@@ -4130,10 +4130,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D27" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Síly má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření Síly mají postih −3.</x:v>
       </x:c>
       <x:c r="E27" s="2" t="str">
-        <x:v>Pokusíš se všechno přetlačit a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Pokusíš se všechno přetlačit a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F27"/>
       <x:c r="G27">
@@ -4151,10 +4151,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D28" s="2" t="str">
-        <x:v>Příští ověření Síly má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření Síly mají postih −2.</x:v>
       </x:c>
       <x:c r="E28" s="2" t="str">
-        <x:v>Vlastní záběr špatně odhadneš a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Vlastní záběr špatně odhadneš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F28"/>
       <x:c r="G28">
@@ -4382,10 +4382,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D39" s="2" t="str">
-        <x:v>Příští tři ověření Síly mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření Síly mají postih −3.</x:v>
       </x:c>
       <x:c r="E39" s="2" t="str">
-        <x:v>Snadný výkon zbytečně vyhrotíš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Snadný výkon zbytečně vyhrotíš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F39"/>
       <x:c r="G39">
@@ -4403,10 +4403,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D40" s="2" t="str">
-        <x:v>Příští dvě ověření Síly mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření Síly mají postih −3.</x:v>
       </x:c>
       <x:c r="E40" s="2" t="str">
-        <x:v>Přidáš důraz ve špatnou chvíli a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš důraz ve špatnou chvíli a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F40"/>
       <x:c r="G40">
@@ -4487,10 +4487,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D44" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření Síly automaticky selže. Následující dvě ověření Síly mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření Síly automaticky selže.</x:v>
       </x:c>
       <x:c r="E44" s="2" t="str">
-        <x:v>Sílu předvedeš zbytečně okázale a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Sílu předvedeš zbytečně okázale a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F44"/>
       <x:c r="G44">
@@ -4550,10 +4550,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D47" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −5.</x:v>
       </x:c>
       <x:c r="E47" s="2" t="str">
-        <x:v>Pokusíš se všechno přetlačit a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Pokusíš se všechno přetlačit a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F47"/>
       <x:c r="G47">
@@ -4571,10 +4571,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D48" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −3.</x:v>
       </x:c>
       <x:c r="E48" s="2" t="str">
-        <x:v>Vlastní záběr špatně odhadneš a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Vlastní záběr špatně odhadneš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F48"/>
       <x:c r="G48">
@@ -4613,10 +4613,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D50" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští hod na iniciativu a příští ověření Síly mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští dvě ověření Síly mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E50" s="2" t="str">
-        <x:v>Přidáš sílu místo rozvahy a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Přidáš sílu místo rozvahy a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F50"/>
       <x:c r="G50">
@@ -4655,10 +4655,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D52" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E52" s="2" t="str">
-        <x:v>Přeceníš účinek hrubé síly a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Přeceníš účinek hrubé síly a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F52"/>
       <x:c r="G52">
@@ -4697,10 +4697,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D54" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E54" s="2" t="str">
-        <x:v>Zbytečně se předem vyčerpáš a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Zbytečně se předem vyčerpáš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F54"/>
       <x:c r="G54">
@@ -4718,10 +4718,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D55" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −5. Příští záchranný hod na Sílu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −5.</x:v>
       </x:c>
       <x:c r="E55" s="2" t="str">
-        <x:v>Odpor odhadneš příliš lehkovážně a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Odpor odhadneš příliš lehkovážně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F55"/>
       <x:c r="G55">
@@ -4739,10 +4739,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D56" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E56" s="2" t="str">
-        <x:v>Přepneš síly při napravování a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přepneš síly při napravování a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F56"/>
       <x:c r="G56">
@@ -4802,10 +4802,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D59" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −5.</x:v>
       </x:c>
       <x:c r="E59" s="2" t="str">
-        <x:v>Snadný výkon zbytečně vyhrotíš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Snadný výkon zbytečně vyhrotíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F59"/>
       <x:c r="G59">
@@ -4823,10 +4823,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D60" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E60" s="2" t="str">
-        <x:v>Přidáš důraz ve špatnou chvíli a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš důraz ve špatnou chvíli a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F60"/>
       <x:c r="G60">
@@ -4844,10 +4844,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D61" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu. Příští dvě ověření Síly mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Síly mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E61" s="2" t="str">
-        <x:v>Tlačíš na výkon příliš a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Tlačíš na výkon příliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F61"/>
       <x:c r="G61">
@@ -5096,10 +5096,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D73" s="2" t="str">
-        <x:v>Příští ověření dovednosti Athletics má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Athletics má postih −2.</x:v>
       </x:c>
       <x:c r="E73" s="2" t="str">
-        <x:v>Ztratíš správný rytmus záběru a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Ztratíš správný rytmus záběru a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F73"/>
       <x:c r="G73">
@@ -5243,10 +5243,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D80" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Athletics mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Athletics mají postih −1.</x:v>
       </x:c>
       <x:c r="E80" s="2" t="str">
-        <x:v>Přetáhneš potřebný záběr a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přetáhneš potřebný záběr a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F80"/>
       <x:c r="G80">
@@ -5390,10 +5390,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D87" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Athletics má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Athletics mají postih −3.</x:v>
       </x:c>
       <x:c r="E87" s="2" t="str">
-        <x:v>Záběr uspěcháš před srovnáním a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Záběr uspěcháš před srovnáním a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F87"/>
       <x:c r="G87">
@@ -5411,10 +5411,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D88" s="2" t="str">
-        <x:v>Příští ověření dovednosti Athletics má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Athletics mají postih −2.</x:v>
       </x:c>
       <x:c r="E88" s="2" t="str">
-        <x:v>Rozvrhneš si námahu špatně a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Rozvrhneš si námahu špatně a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F88"/>
       <x:c r="G88">
@@ -5642,10 +5642,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D99" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Athletics mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Athletics mají postih −3.</x:v>
       </x:c>
       <x:c r="E99" s="2" t="str">
-        <x:v>Zbytečně usiluješ o efektní výkon a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Zbytečně usiluješ o efektní výkon a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F99"/>
       <x:c r="G99">
@@ -5663,10 +5663,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D100" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Athletics mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Athletics mají postih −3.</x:v>
       </x:c>
       <x:c r="E100" s="2" t="str">
-        <x:v>Přetáhneš potřebný záběr a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přetáhneš potřebný záběr a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F100"/>
       <x:c r="G100">
@@ -5747,10 +5747,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D104" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření dovednosti Athletics automaticky selže. Následující dvě ověření dovednosti Athletics mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření dovednosti Athletics automaticky selže.</x:v>
       </x:c>
       <x:c r="E104" s="2" t="str">
-        <x:v>Přeceníš zásobu vlastních sil a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Přeceníš zásobu vlastních sil a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F104"/>
       <x:c r="G104">
@@ -5810,10 +5810,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D107" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají postih −5.</x:v>
       </x:c>
       <x:c r="E107" s="2" t="str">
-        <x:v>Záběr uspěcháš před srovnáním a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Záběr uspěcháš před srovnáním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F107"/>
       <x:c r="G107">
@@ -5831,10 +5831,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D108" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají postih −3.</x:v>
       </x:c>
       <x:c r="E108" s="2" t="str">
-        <x:v>Rozvrhneš si námahu špatně a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Rozvrhneš si námahu špatně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F108"/>
       <x:c r="G108">
@@ -5873,10 +5873,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D110" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští hod na iniciativu a příští ověření Síly mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští dvě ověření dovednosti Athletics mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E110" s="2" t="str">
-        <x:v>Přidáš tempo bez rozmyslu a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Přidáš tempo bez rozmyslu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F110"/>
       <x:c r="G110">
@@ -5915,10 +5915,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D112" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E112" s="2" t="str">
-        <x:v>Odhad výkonu nahradíš nadšením a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Odhad výkonu nahradíš nadšením a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F112"/>
       <x:c r="G112">
@@ -5957,10 +5957,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D114" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E114" s="2" t="str">
-        <x:v>Vlastní rezervu odhadneš velkoryse a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Vlastní rezervu odhadneš velkoryse a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F114"/>
       <x:c r="G114">
@@ -5978,10 +5978,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D115" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají postih −5. Příští záchranný hod na Sílu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají postih −5.</x:v>
       </x:c>
       <x:c r="E115" s="2" t="str">
-        <x:v>Přidáš sílu místo techniky a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přidáš sílu místo techniky a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F115"/>
       <x:c r="G115">
@@ -5999,10 +5999,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D116" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E116" s="2" t="str">
-        <x:v>Snažíš se chybu přetlačit a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Snažíš se chybu přetlačit a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F116"/>
       <x:c r="G116">
@@ -6062,10 +6062,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D119" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Síly mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají postih −5.</x:v>
       </x:c>
       <x:c r="E119" s="2" t="str">
-        <x:v>Zbytečně usiluješ o efektní výkon a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Zbytečně usiluješ o efektní výkon a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F119"/>
       <x:c r="G119">
@@ -6083,10 +6083,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D120" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E120" s="2" t="str">
-        <x:v>Přetáhneš potřebný záběr a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přetáhneš potřebný záběr a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F120"/>
       <x:c r="G120">
@@ -6104,10 +6104,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D121" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu. Příští dvě ověření Síly mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Athletics mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E121" s="2" t="str">
-        <x:v>Přeskočíš důležitou část přípravy a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Přeskočíš důležitou část přípravy a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F121"/>
       <x:c r="G121">
@@ -6356,10 +6356,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D133" s="2" t="str">
-        <x:v>Příští ověření Obratnosti má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření Obratnosti má postih −2.</x:v>
       </x:c>
       <x:c r="E133" s="2" t="str">
-        <x:v>Jemnost nahradíš prudkým provedením a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Jemnost nahradíš prudkým provedením a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F133"/>
       <x:c r="G133">
@@ -6503,10 +6503,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D140" s="2" t="str">
-        <x:v>Příští dvě ověření Obratnosti mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření Obratnosti mají postih −1.</x:v>
       </x:c>
       <x:c r="E140" s="2" t="str">
-        <x:v>Okázale opravuješ špatné načasování a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Okázale opravuješ špatné načasování a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F140"/>
       <x:c r="G140">
@@ -6650,10 +6650,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D147" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Obratnosti má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření Obratnosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E147" s="2" t="str">
-        <x:v>Vlastní pohyb zbytečně komplikuješ a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Vlastní pohyb zbytečně komplikuješ a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F147"/>
       <x:c r="G147">
@@ -6671,10 +6671,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D148" s="2" t="str">
-        <x:v>Příští ověření Obratnosti má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření Obratnosti mají postih −2.</x:v>
       </x:c>
       <x:c r="E148" s="2" t="str">
-        <x:v>Opravu začneš příliš brzy a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Opravu začneš příliš brzy a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F148"/>
       <x:c r="G148">
@@ -6902,10 +6902,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D159" s="2" t="str">
-        <x:v>Příští tři ověření Obratnosti mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření Obratnosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E159" s="2" t="str">
-        <x:v>Pokusíš se chybu předehnat a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Pokusíš se chybu předehnat a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F159"/>
       <x:c r="G159">
@@ -6923,10 +6923,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D160" s="2" t="str">
-        <x:v>Příští dvě ověření Obratnosti mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření Obratnosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E160" s="2" t="str">
-        <x:v>Okázale opravuješ špatné načasování a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Okázale opravuješ špatné načasování a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F160"/>
       <x:c r="G160">
@@ -7007,10 +7007,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D164" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření Obratnosti automaticky selže. Následující dvě ověření Obratnosti mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření Obratnosti automaticky selže.</x:v>
       </x:c>
       <x:c r="E164" s="2" t="str">
-        <x:v>Provedení zbytečně uspěcháš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Provedení zbytečně uspěcháš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F164"/>
       <x:c r="G164">
@@ -7070,10 +7070,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D167" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −5.</x:v>
       </x:c>
       <x:c r="E167" s="2" t="str">
-        <x:v>Vlastní pohyb zbytečně komplikuješ a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Vlastní pohyb zbytečně komplikuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F167"/>
       <x:c r="G167">
@@ -7091,10 +7091,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D168" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E168" s="2" t="str">
-        <x:v>Opravu začneš příliš brzy a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Opravu začneš příliš brzy a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F168"/>
       <x:c r="G168">
@@ -7133,10 +7133,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D170" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští hod na iniciativu a příští ověření Obratnosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští dvě ověření Obratnosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E170" s="2" t="str">
-        <x:v>Přidáš rychlost místo přesnosti a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Přidáš rychlost místo přesnosti a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F170"/>
       <x:c r="G170">
@@ -7175,10 +7175,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D172" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E172" s="2" t="str">
-        <x:v>Přehlédneš drobnou chybu provedení a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Přehlédneš drobnou chybu provedení a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F172"/>
       <x:c r="G172">
@@ -7217,10 +7217,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D174" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E174" s="2" t="str">
-        <x:v>Opravu načasuješ ještě hůř a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Opravu načasuješ ještě hůř a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F174"/>
       <x:c r="G174">
@@ -7238,10 +7238,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D175" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −5. Příští záchranný hod na Obratnost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −5.</x:v>
       </x:c>
       <x:c r="E175" s="2" t="str">
-        <x:v>Přeceníš jistotu vlastního pohybu a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš jistotu vlastního pohybu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F175"/>
       <x:c r="G175">
@@ -7259,10 +7259,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D176" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E176" s="2" t="str">
-        <x:v>Přesnost hlídáš až křečovitě a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přesnost hlídáš až křečovitě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F176"/>
       <x:c r="G176">
@@ -7322,10 +7322,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D179" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −5.</x:v>
       </x:c>
       <x:c r="E179" s="2" t="str">
-        <x:v>Pokusíš se chybu předehnat a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Pokusíš se chybu předehnat a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F179"/>
       <x:c r="G179">
@@ -7343,10 +7343,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D180" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E180" s="2" t="str">
-        <x:v>Okázale opravuješ špatné načasování a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Okázale opravuješ špatné načasování a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F180"/>
       <x:c r="G180">
@@ -7364,10 +7364,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D181" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu. Příští dvě ověření Obratnosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Obratnosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E181" s="2" t="str">
-        <x:v>Rychlé provedení zbytečně přepálíš a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Rychlé provedení zbytečně přepálíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F181"/>
       <x:c r="G181">
@@ -7616,10 +7616,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D193" s="2" t="str">
-        <x:v>Příští ověření dovednosti Acrobatics má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Acrobatics má postih −2.</x:v>
       </x:c>
       <x:c r="E193" s="2" t="str">
-        <x:v>Složitým provedením ztratíš jistotu a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Složitým provedením ztratíš jistotu a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F193"/>
       <x:c r="G193">
@@ -7763,10 +7763,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D200" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Acrobatics mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Acrobatics mají postih −1.</x:v>
       </x:c>
       <x:c r="E200" s="2" t="str">
-        <x:v>Správný rytmus překryješ horlivostí a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Správný rytmus překryješ horlivostí a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F200"/>
       <x:c r="G200">
@@ -7910,10 +7910,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D207" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Acrobatics má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Acrobatics mají postih −3.</x:v>
       </x:c>
       <x:c r="E207" s="2" t="str">
-        <x:v>Rovnováhu hlídáš až křečovitě a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Rovnováhu hlídáš až křečovitě a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F207"/>
       <x:c r="G207">
@@ -7931,10 +7931,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D208" s="2" t="str">
-        <x:v>Příští ověření dovednosti Acrobatics má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Acrobatics mají postih −2.</x:v>
       </x:c>
       <x:c r="E208" s="2" t="str">
-        <x:v>Srovnání uspěcháš před odhadem a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Srovnání uspěcháš před odhadem a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F208"/>
       <x:c r="G208">
@@ -8162,10 +8162,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D219" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Acrobatics mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Acrobatics mají postih −3.</x:v>
       </x:c>
       <x:c r="E219" s="2" t="str">
-        <x:v>Snažíš se chybu přehrát a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Snažíš se chybu přehrát a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F219"/>
       <x:c r="G219">
@@ -8183,10 +8183,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D220" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Acrobatics mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Acrobatics mají postih −3.</x:v>
       </x:c>
       <x:c r="E220" s="2" t="str">
-        <x:v>Správný rytmus překryješ horlivostí a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Správný rytmus překryješ horlivostí a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F220"/>
       <x:c r="G220">
@@ -8267,10 +8267,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D224" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření dovednosti Acrobatics automaticky selže. Následující dvě ověření dovednosti Acrobatics mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření dovednosti Acrobatics automaticky selže.</x:v>
       </x:c>
       <x:c r="E224" s="2" t="str">
-        <x:v>Pokus pojmeš příliš pružně a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Pokus pojmeš příliš pružně a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F224"/>
       <x:c r="G224">
@@ -8330,10 +8330,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D227" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají postih −5.</x:v>
       </x:c>
       <x:c r="E227" s="2" t="str">
-        <x:v>Rovnováhu hlídáš až křečovitě a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Rovnováhu hlídáš až křečovitě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F227"/>
       <x:c r="G227">
@@ -8351,10 +8351,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D228" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají postih −3.</x:v>
       </x:c>
       <x:c r="E228" s="2" t="str">
-        <x:v>Srovnání uspěcháš před odhadem a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Srovnání uspěcháš před odhadem a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F228"/>
       <x:c r="G228">
@@ -8393,10 +8393,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D230" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští hod na iniciativu a příští ověření Obratnosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští dvě ověření dovednosti Acrobatics mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E230" s="2" t="str">
-        <x:v>Pokusíš se předvést lehkost a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Pokusíš se předvést lehkost a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F230"/>
       <x:c r="G230">
@@ -8435,10 +8435,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D232" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E232" s="2" t="str">
-        <x:v>Vlastní stabilitu odhadneš velkoryse a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Vlastní stabilitu odhadneš velkoryse a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F232"/>
       <x:c r="G232">
@@ -8477,10 +8477,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D234" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E234" s="2" t="str">
-        <x:v>Přeženeš opravu drobného zaváhání a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Přeženeš opravu drobného zaváhání a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F234"/>
       <x:c r="G234">
@@ -8498,10 +8498,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D235" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají postih −5. Příští záchranný hod na Obratnost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají postih −5.</x:v>
       </x:c>
       <x:c r="E235" s="2" t="str">
-        <x:v>Nesladíš pohyb s načasováním a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Nesladíš pohyb s načasováním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F235"/>
       <x:c r="G235">
@@ -8519,10 +8519,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D236" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E236" s="2" t="str">
-        <x:v>Přidáš ladnost na úkor jistoty a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš ladnost na úkor jistoty a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F236"/>
       <x:c r="G236">
@@ -8582,10 +8582,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D239" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají postih −5.</x:v>
       </x:c>
       <x:c r="E239" s="2" t="str">
-        <x:v>Snažíš se chybu přehrát a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Snažíš se chybu přehrát a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F239"/>
       <x:c r="G239">
@@ -8603,10 +8603,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D240" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E240" s="2" t="str">
-        <x:v>Správný rytmus překryješ horlivostí a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Správný rytmus překryješ horlivostí a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F240"/>
       <x:c r="G240">
@@ -8624,10 +8624,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D241" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu. Příští dvě ověření Obratnosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Acrobatics mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E241" s="2" t="str">
-        <x:v>Plynulé provedení zbytečně narušíš a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Plynulé provedení zbytečně narušíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F241"/>
       <x:c r="G241">
@@ -8876,10 +8876,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D253" s="2" t="str">
-        <x:v>Příští ověření dovednosti Sleight of Hand má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Sleight of Hand má postih −2.</x:v>
       </x:c>
       <x:c r="E253" s="2" t="str">
-        <x:v>Provedení sevřeš přehnanou pečlivostí a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Provedení sevřeš přehnanou pečlivostí a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F253"/>
       <x:c r="G253">
@@ -9023,10 +9023,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D260" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Sleight of Hand mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Sleight of Hand mají postih −1.</x:v>
       </x:c>
       <x:c r="E260" s="2" t="str">
-        <x:v>Pokus zpestříš nepotřebným pohybem a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Pokus zpestříš nepotřebným pohybem a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F260"/>
       <x:c r="G260">
@@ -9170,10 +9170,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D267" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Sleight of Hand má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Sleight of Hand mají postih −3.</x:v>
       </x:c>
       <x:c r="E267" s="2" t="str">
-        <x:v>Opravu drobnosti příliš zvýrazníš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Opravu drobnosti příliš zvýrazníš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F267"/>
       <x:c r="G267">
@@ -9191,10 +9191,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D268" s="2" t="str">
-        <x:v>Příští ověření dovednosti Sleight of Hand má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Sleight of Hand mají postih −2.</x:v>
       </x:c>
       <x:c r="E268" s="2" t="str">
-        <x:v>Sled pohybů zbytečně komplikuješ a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Sled pohybů zbytečně komplikuješ a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F268"/>
       <x:c r="G268">
@@ -9422,10 +9422,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D279" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Sleight of Hand mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Sleight of Hand mají postih −3.</x:v>
       </x:c>
       <x:c r="E279" s="2" t="str">
-        <x:v>Předvedeš zbytečně nápadnou opravu a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Předvedeš zbytečně nápadnou opravu a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F279"/>
       <x:c r="G279">
@@ -9443,10 +9443,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D280" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Sleight of Hand mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Sleight of Hand mají postih −3.</x:v>
       </x:c>
       <x:c r="E280" s="2" t="str">
-        <x:v>Pokus zpestříš nepotřebným pohybem a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Pokus zpestříš nepotřebným pohybem a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F280"/>
       <x:c r="G280">
@@ -9527,10 +9527,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D284" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření dovednosti Sleight of Hand automaticky selže. Následující dvě ověření dovednosti Sleight of Hand mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření dovednosti Sleight of Hand automaticky selže.</x:v>
       </x:c>
       <x:c r="E284" s="2" t="str">
-        <x:v>Drobný pohyb zbytečně přeženeš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Drobný pohyb zbytečně přeženeš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F284"/>
       <x:c r="G284">
@@ -9590,10 +9590,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D287" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají postih −5.</x:v>
       </x:c>
       <x:c r="E287" s="2" t="str">
-        <x:v>Opravu drobnosti příliš zvýrazníš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Opravu drobnosti příliš zvýrazníš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F287"/>
       <x:c r="G287">
@@ -9611,10 +9611,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D288" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají postih −3.</x:v>
       </x:c>
       <x:c r="E288" s="2" t="str">
-        <x:v>Sled pohybů zbytečně komplikuješ a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Sled pohybů zbytečně komplikuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F288"/>
       <x:c r="G288">
@@ -9653,10 +9653,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D290" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští hod na iniciativu a příští ověření Obratnosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští dvě ověření dovednosti Sleight of Hand mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E290" s="2" t="str">
-        <x:v>Pokusíš se předběhnout přesnost a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Pokusíš se předběhnout přesnost a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F290"/>
       <x:c r="G290">
@@ -9695,10 +9695,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D292" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E292" s="2" t="str">
-        <x:v>Malý detail přehlédneš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Malý detail přehlédneš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F292"/>
       <x:c r="G292">
@@ -9737,10 +9737,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D294" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E294" s="2" t="str">
-        <x:v>Zbytečně opravuješ správnou část a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Zbytečně opravuješ správnou část a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F294"/>
       <x:c r="G294">
@@ -9758,10 +9758,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D295" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají postih −5. Příští záchranný hod na Obratnost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají postih −5.</x:v>
       </x:c>
       <x:c r="E295" s="2" t="str">
-        <x:v>Soustředění nahradíš naučenou rutinou a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Soustředění nahradíš naučenou rutinou a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F295"/>
       <x:c r="G295">
@@ -9779,10 +9779,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D296" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E296" s="2" t="str">
-        <x:v>Jemné načasování zbytečně rozhodíš a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jemné načasování zbytečně rozhodíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F296"/>
       <x:c r="G296">
@@ -9842,10 +9842,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D299" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají postih −5.</x:v>
       </x:c>
       <x:c r="E299" s="2" t="str">
-        <x:v>Předvedeš zbytečně nápadnou opravu a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Předvedeš zbytečně nápadnou opravu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F299"/>
       <x:c r="G299">
@@ -9863,10 +9863,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D300" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E300" s="2" t="str">
-        <x:v>Pokus zpestříš nepotřebným pohybem a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Pokus zpestříš nepotřebným pohybem a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F300"/>
       <x:c r="G300">
@@ -9884,10 +9884,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D301" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu. Příští dvě ověření Obratnosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Sleight of Hand mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E301" s="2" t="str">
-        <x:v>Jemný postup ukončíš zbrkle a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Jemný postup ukončíš zbrkle a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F301"/>
       <x:c r="G301">
@@ -10136,10 +10136,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D313" s="2" t="str">
-        <x:v>Příští ověření dovednosti Stealth má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Stealth má postih −2.</x:v>
       </x:c>
       <x:c r="E313" s="2" t="str">
-        <x:v>Ztratíš přirozený rytmus skrývání a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Ztratíš přirozený rytmus skrývání a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F313"/>
       <x:c r="G313">
@@ -10283,10 +10283,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D320" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Stealth mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Stealth mají postih −1.</x:v>
       </x:c>
       <x:c r="E320" s="2" t="str">
-        <x:v>Křečovitě opravuješ své tempo a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Křečovitě opravuješ své tempo a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F320"/>
       <x:c r="G320">
@@ -10430,10 +10430,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D327" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Stealth má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Stealth mají postih −3.</x:v>
       </x:c>
       <x:c r="E327" s="2" t="str">
-        <x:v>Opravu načasování zbytečně zvýrazníš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Opravu načasování zbytečně zvýrazníš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F327"/>
       <x:c r="G327">
@@ -10451,10 +10451,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D328" s="2" t="str">
-        <x:v>Příští ověření dovednosti Stealth má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Stealth mají postih −2.</x:v>
       </x:c>
       <x:c r="E328" s="2" t="str">
-        <x:v>Zvolíš přehnaně složitý postup a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zvolíš přehnaně složitý postup a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F328"/>
       <x:c r="G328">
@@ -10682,10 +10682,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D339" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Stealth mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Stealth mají postih −3.</x:v>
       </x:c>
       <x:c r="E339" s="2" t="str">
-        <x:v>Vlastní jistotu hlídáš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Vlastní jistotu hlídáš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F339"/>
       <x:c r="G339">
@@ -10703,10 +10703,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D340" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Stealth mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Stealth mají postih −3.</x:v>
       </x:c>
       <x:c r="E340" s="2" t="str">
-        <x:v>Křečovitě opravuješ své tempo a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Křečovitě opravuješ své tempo a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F340"/>
       <x:c r="G340">
@@ -10787,10 +10787,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D344" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření dovednosti Stealth automaticky selže. Následující dvě ověření dovednosti Stealth mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření dovednosti Stealth automaticky selže.</x:v>
       </x:c>
       <x:c r="E344" s="2" t="str">
-        <x:v>Soustředíš se na nenápadnost křečovitě a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Soustředíš se na nenápadnost křečovitě a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F344"/>
       <x:c r="G344">
@@ -10850,10 +10850,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D347" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají postih −5.</x:v>
       </x:c>
       <x:c r="E347" s="2" t="str">
-        <x:v>Opravu načasování zbytečně zvýrazníš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Opravu načasování zbytečně zvýrazníš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F347"/>
       <x:c r="G347">
@@ -10871,10 +10871,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D348" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají postih −3.</x:v>
       </x:c>
       <x:c r="E348" s="2" t="str">
-        <x:v>Zvolíš přehnaně složitý postup a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Zvolíš přehnaně složitý postup a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F348"/>
       <x:c r="G348">
@@ -10913,10 +10913,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D350" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští hod na iniciativu a příští ověření Obratnosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští dvě ověření dovednosti Stealth mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E350" s="2" t="str">
-        <x:v>Přeceníš jistotu svého tempa a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Přeceníš jistotu svého tempa a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F350"/>
       <x:c r="G350">
@@ -10955,10 +10955,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D352" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E352" s="2" t="str">
-        <x:v>Podstatný detail překryješ opatrností a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Podstatný detail překryješ opatrností a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F352"/>
       <x:c r="G352">
@@ -10997,10 +10997,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D354" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E354" s="2" t="str">
-        <x:v>Pokusíš se nenápadnost uspěchat a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Pokusíš se nenápadnost uspěchat a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F354"/>
       <x:c r="G354">
@@ -11018,10 +11018,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D355" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají postih −5. Příští záchranný hod na Obratnost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají postih −5.</x:v>
       </x:c>
       <x:c r="E355" s="2" t="str">
-        <x:v>Přípravu nahradíš sebejistým odhadem a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přípravu nahradíš sebejistým odhadem a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F355"/>
       <x:c r="G355">
@@ -11039,10 +11039,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D356" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E356" s="2" t="str">
-        <x:v>Přehnaně hlídáš každé zaváhání a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přehnaně hlídáš každé zaváhání a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F356"/>
       <x:c r="G356">
@@ -11102,10 +11102,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D359" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Obratnosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají postih −5.</x:v>
       </x:c>
       <x:c r="E359" s="2" t="str">
-        <x:v>Vlastní jistotu hlídáš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Vlastní jistotu hlídáš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F359"/>
       <x:c r="G359">
@@ -11123,10 +11123,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D360" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E360" s="2" t="str">
-        <x:v>Křečovitě opravuješ své tempo a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Křečovitě opravuješ své tempo a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F360"/>
       <x:c r="G360">
@@ -11144,10 +11144,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D361" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu. Příští dvě ověření Obratnosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření dovednosti Stealth mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E361" s="2" t="str">
-        <x:v>Snadné provedení překombinuješ opatrností a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Snadné provedení překombinuješ opatrností a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F361"/>
       <x:c r="G361">
@@ -11396,10 +11396,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D373" s="2" t="str">
-        <x:v>Příští ověření Inteligence má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření Inteligence má postih −2.</x:v>
       </x:c>
       <x:c r="E373" s="2" t="str">
-        <x:v>Spleteš si příčinu s následkem a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Spleteš si příčinu s následkem a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F373"/>
       <x:c r="G373">
@@ -11543,10 +11543,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D380" s="2" t="str">
-        <x:v>Příští dvě ověření Inteligence mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření Inteligence mají postih −1.</x:v>
       </x:c>
       <x:c r="E380" s="2" t="str">
-        <x:v>Přidáš zbytečnou myšlenkovou okliku a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš zbytečnou myšlenkovou okliku a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F380"/>
       <x:c r="G380">
@@ -11690,10 +11690,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D387" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Inteligence má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření Inteligence mají postih −3.</x:v>
       </x:c>
       <x:c r="E387" s="2" t="str">
-        <x:v>Souvislost si zbytečně domyslíš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Souvislost si zbytečně domyslíš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F387"/>
       <x:c r="G387">
@@ -11711,10 +11711,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D388" s="2" t="str">
-        <x:v>Příští ověření Inteligence má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření Inteligence mají postih −2.</x:v>
       </x:c>
       <x:c r="E388" s="2" t="str">
-        <x:v>Rozbor zatížíš zbytečnou odbočkou a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Rozbor zatížíš zbytečnou odbočkou a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F388"/>
       <x:c r="G388">
@@ -11942,10 +11942,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D399" s="2" t="str">
-        <x:v>Příští tři ověření Inteligence mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření Inteligence mají postih −3.</x:v>
       </x:c>
       <x:c r="E399" s="2" t="str">
-        <x:v>Chytrým zkratkám uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Chytrým zkratkám uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F399"/>
       <x:c r="G399">
@@ -11963,10 +11963,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D400" s="2" t="str">
-        <x:v>Příští dvě ověření Inteligence mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření Inteligence mají postih −3.</x:v>
       </x:c>
       <x:c r="E400" s="2" t="str">
-        <x:v>Přidáš zbytečnou myšlenkovou okliku a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš zbytečnou myšlenkovou okliku a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F400"/>
       <x:c r="G400">
@@ -12047,10 +12047,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D404" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření Inteligence automaticky selže. Následující dvě ověření Inteligence mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření Inteligence automaticky selže.</x:v>
       </x:c>
       <x:c r="E404" s="2" t="str">
-        <x:v>Závěr si pochválíš předčasně a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Závěr si pochválíš předčasně a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F404"/>
       <x:c r="G404">
@@ -12110,10 +12110,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D407" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −5.</x:v>
       </x:c>
       <x:c r="E407" s="2" t="str">
-        <x:v>Souvislost si zbytečně domyslíš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Souvislost si zbytečně domyslíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F407"/>
       <x:c r="G407">
@@ -12131,10 +12131,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D408" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −3.</x:v>
       </x:c>
       <x:c r="E408" s="2" t="str">
-        <x:v>Rozbor zatížíš zbytečnou odbočkou a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Rozbor zatížíš zbytečnou odbočkou a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F408"/>
       <x:c r="G408">
@@ -12173,10 +12173,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D410" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Inteligence mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření Inteligence mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E410" s="2" t="str">
-        <x:v>Odhad vydáváš za jistotu a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Odhad vydáváš za jistotu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F410"/>
       <x:c r="G410">
@@ -12215,10 +12215,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D412" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E412" s="2" t="str">
-        <x:v>Důležitý detail přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Důležitý detail přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F412"/>
       <x:c r="G412">
@@ -12257,10 +12257,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D414" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E414" s="2" t="str">
-        <x:v>Zbytečně rozebereš správnou část a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Zbytečně rozebereš správnou část a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F414"/>
       <x:c r="G414">
@@ -12278,10 +12278,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D415" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −5. Příští záchranný hod na Inteligenci má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −5.</x:v>
       </x:c>
       <x:c r="E415" s="2" t="str">
-        <x:v>Přeceníš přesnost vlastního úsudku a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš přesnost vlastního úsudku a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F415"/>
       <x:c r="G415">
@@ -12299,10 +12299,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D416" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E416" s="2" t="str">
-        <x:v>Jistotu hledáš v komplikacích a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jistotu hledáš v komplikacích a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F416"/>
       <x:c r="G416">
@@ -12362,10 +12362,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D419" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −5.</x:v>
       </x:c>
       <x:c r="E419" s="2" t="str">
-        <x:v>Chytrým zkratkám uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Chytrým zkratkám uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F419"/>
       <x:c r="G419">
@@ -12383,10 +12383,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D420" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E420" s="2" t="str">
-        <x:v>Přidáš zbytečnou myšlenkovou okliku a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš zbytečnou myšlenkovou okliku a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F420"/>
       <x:c r="G420">
@@ -12404,10 +12404,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D421" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu. Příští dvě ověření Inteligence mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Inteligence mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E421" s="2" t="str">
-        <x:v>Vlastní rozbor dovedeš do zmatku a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Vlastní rozbor dovedeš do zmatku a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F421"/>
       <x:c r="G421">
@@ -12656,10 +12656,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D433" s="2" t="str">
-        <x:v>Příští ověření dovednosti Arcana má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Arcana má postih −2.</x:v>
       </x:c>
       <x:c r="E433" s="2" t="str">
-        <x:v>Spleteš si dvě magické poučky a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Spleteš si dvě magické poučky a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F433"/>
       <x:c r="G433">
@@ -12803,10 +12803,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D440" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Arcana mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Arcana mají postih −1.</x:v>
       </x:c>
       <x:c r="E440" s="2" t="str">
-        <x:v>Přidáš magii zbytečnou složitost a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš magii zbytečnou složitost a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F440"/>
       <x:c r="G440">
@@ -12950,10 +12950,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D447" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Arcana má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Arcana mají postih −3.</x:v>
       </x:c>
       <x:c r="E447" s="2" t="str">
-        <x:v>Magickou souvislost si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Magickou souvislost si domyslíš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F447"/>
       <x:c r="G447">
@@ -12971,10 +12971,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D448" s="2" t="str">
-        <x:v>Příští ověření dovednosti Arcana má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Arcana mají postih −2.</x:v>
       </x:c>
       <x:c r="E448" s="2" t="str">
-        <x:v>Rozbor zatížíš nepotřebnou teorií a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Rozbor zatížíš nepotřebnou teorií a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F448"/>
       <x:c r="G448">
@@ -13202,10 +13202,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D459" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Arcana mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Arcana mají postih −3.</x:v>
       </x:c>
       <x:c r="E459" s="2" t="str">
-        <x:v>Učenému dojmu uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Učenému dojmu uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F459"/>
       <x:c r="G459">
@@ -13223,10 +13223,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D460" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Arcana mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Arcana mají postih −3.</x:v>
       </x:c>
       <x:c r="E460" s="2" t="str">
-        <x:v>Přidáš magii zbytečnou složitost a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš magii zbytečnou složitost a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F460"/>
       <x:c r="G460">
@@ -13307,10 +13307,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D464" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Arcana automaticky selže. Následující dvě ověření dovednosti Arcana mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Arcana automaticky selže.</x:v>
       </x:c>
       <x:c r="E464" s="2" t="str">
-        <x:v>Známou poučku příliš zobecníš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Známou poučku příliš zobecníš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F464"/>
       <x:c r="G464">
@@ -13370,10 +13370,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D467" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají postih −5.</x:v>
       </x:c>
       <x:c r="E467" s="2" t="str">
-        <x:v>Magickou souvislost si domyslíš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Magickou souvislost si domyslíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F467"/>
       <x:c r="G467">
@@ -13391,10 +13391,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D468" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají postih −3.</x:v>
       </x:c>
       <x:c r="E468" s="2" t="str">
-        <x:v>Rozbor zatížíš nepotřebnou teorií a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Rozbor zatížíš nepotřebnou teorií a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F468"/>
       <x:c r="G468">
@@ -13433,10 +13433,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D470" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Inteligence mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Arcana mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E470" s="2" t="str">
-        <x:v>Povědomý princip přijmeš bez ověření a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Povědomý princip přijmeš bez ověření a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F470"/>
       <x:c r="G470">
@@ -13475,10 +13475,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D472" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E472" s="2" t="str">
-        <x:v>Klíčovou odlišnost přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Klíčovou odlišnost přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F472"/>
       <x:c r="G472">
@@ -13517,10 +13517,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D474" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E474" s="2" t="str">
-        <x:v>Správnou znalost opravíš k horšímu a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správnou znalost opravíš k horšímu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F474"/>
       <x:c r="G474">
@@ -13538,10 +13538,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D475" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají postih −5. Příští záchranný hod na Inteligenci má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají postih −5.</x:v>
       </x:c>
       <x:c r="E475" s="2" t="str">
-        <x:v>Spolehneš se na neúplnou vzpomínku a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Spolehneš se na neúplnou vzpomínku a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F475"/>
       <x:c r="G475">
@@ -13559,10 +13559,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D476" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E476" s="2" t="str">
-        <x:v>Magický princip zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Magický princip zbytečně překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F476"/>
       <x:c r="G476">
@@ -13622,10 +13622,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D479" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Arcana mají postih −5.</x:v>
       </x:c>
       <x:c r="E479" s="2" t="str">
-        <x:v>Učenému dojmu uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Učenému dojmu uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F479"/>
       <x:c r="G479">
@@ -13643,10 +13643,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D480" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E480" s="2" t="str">
-        <x:v>Přidáš magii zbytečnou složitost a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš magii zbytečnou složitost a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F480"/>
       <x:c r="G480">
@@ -13664,10 +13664,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D481" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu. Příští dvě ověření Inteligence mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Arcana mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E481" s="2" t="str">
-        <x:v>Vlastní výklad zamotáš odbočkami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Vlastní výklad zamotáš odbočkami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F481"/>
       <x:c r="G481">
@@ -13916,10 +13916,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D493" s="2" t="str">
-        <x:v>Příští ověření dovednosti History má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti History má postih −2.</x:v>
       </x:c>
       <x:c r="E493" s="2" t="str">
-        <x:v>Zaměníš pořadí známých událostí a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš pořadí známých událostí a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F493"/>
       <x:c r="G493">
@@ -14063,10 +14063,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D500" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti History mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti History mají postih −1.</x:v>
       </x:c>
       <x:c r="E500" s="2" t="str">
-        <x:v>Zbytečně rozvětvíš vlastní výklad a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Zbytečně rozvětvíš vlastní výklad a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F500"/>
       <x:c r="G500">
@@ -14210,10 +14210,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D507" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti History má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti History mají postih −3.</x:v>
       </x:c>
       <x:c r="E507" s="2" t="str">
-        <x:v>Chybějící souvislost si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Chybějící souvislost si domyslíš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F507"/>
       <x:c r="G507">
@@ -14231,10 +14231,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D508" s="2" t="str">
-        <x:v>Příští ověření dovednosti History má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti History mají postih −2.</x:v>
       </x:c>
       <x:c r="E508" s="2" t="str">
-        <x:v>Výklad zatížíš zbytečnou odbočkou a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Výklad zatížíš zbytečnou odbočkou a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F508"/>
       <x:c r="G508">
@@ -14462,10 +14462,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D519" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti History mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti History mají postih −3.</x:v>
       </x:c>
       <x:c r="E519" s="2" t="str">
-        <x:v>Zvučné poučce uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Zvučné poučce uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F519"/>
       <x:c r="G519">
@@ -14483,10 +14483,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D520" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti History mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti History mají postih −3.</x:v>
       </x:c>
       <x:c r="E520" s="2" t="str">
-        <x:v>Zbytečně rozvětvíš vlastní výklad a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Zbytečně rozvětvíš vlastní výklad a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F520"/>
       <x:c r="G520">
@@ -14567,10 +14567,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D524" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti History automaticky selže. Následující dvě ověření dovednosti History mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti History automaticky selže.</x:v>
       </x:c>
       <x:c r="E524" s="2" t="str">
-        <x:v>Známý příběh příliš zobecníš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Známý příběh příliš zobecníš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F524"/>
       <x:c r="G524">
@@ -14630,10 +14630,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D527" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají postih −5.</x:v>
       </x:c>
       <x:c r="E527" s="2" t="str">
-        <x:v>Chybějící souvislost si domyslíš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Chybějící souvislost si domyslíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F527"/>
       <x:c r="G527">
@@ -14651,10 +14651,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D528" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají postih −3.</x:v>
       </x:c>
       <x:c r="E528" s="2" t="str">
-        <x:v>Výklad zatížíš zbytečnou odbočkou a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Výklad zatížíš zbytečnou odbočkou a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F528"/>
       <x:c r="G528">
@@ -14693,10 +14693,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D530" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Inteligence mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti History mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E530" s="2" t="str">
-        <x:v>Vzpomínku přijmeš bez ověření a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Vzpomínku přijmeš bez ověření a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F530"/>
       <x:c r="G530">
@@ -14735,10 +14735,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D532" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E532" s="2" t="str">
-        <x:v>Podstatný rozdíl přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Podstatný rozdíl přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F532"/>
       <x:c r="G532">
@@ -14777,10 +14777,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D534" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E534" s="2" t="str">
-        <x:v>Správnou vzpomínku překryješ dohadem a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správnou vzpomínku překryješ dohadem a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F534"/>
       <x:c r="G534">
@@ -14798,10 +14798,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D535" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají postih −5. Příští záchranný hod na Inteligenci má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají postih −5.</x:v>
       </x:c>
       <x:c r="E535" s="2" t="str">
-        <x:v>Přeceníš přesnost vlastní paměti a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš přesnost vlastní paměti a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F535"/>
       <x:c r="G535">
@@ -14819,10 +14819,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D536" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E536" s="2" t="str">
-        <x:v>Jednoduchou souvislost překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jednoduchou souvislost překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F536"/>
       <x:c r="G536">
@@ -14882,10 +14882,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D539" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti History mají postih −5.</x:v>
       </x:c>
       <x:c r="E539" s="2" t="str">
-        <x:v>Zvučné poučce uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Zvučné poučce uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F539"/>
       <x:c r="G539">
@@ -14903,10 +14903,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D540" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E540" s="2" t="str">
-        <x:v>Zbytečně rozvětvíš vlastní výklad a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Zbytečně rozvětvíš vlastní výklad a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F540"/>
       <x:c r="G540">
@@ -14924,10 +14924,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D541" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu. Příští dvě ověření Inteligence mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti History mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E541" s="2" t="str">
-        <x:v>Minulost si zamotáš opravami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Minulost si zamotáš opravami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F541"/>
       <x:c r="G541">
@@ -15176,10 +15176,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D553" s="2" t="str">
-        <x:v>Příští ověření dovednosti Investigation má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Investigation má postih −2.</x:v>
       </x:c>
       <x:c r="E553" s="2" t="str">
-        <x:v>Zaměníš následek za příčinu a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš následek za příčinu a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F553"/>
       <x:c r="G553">
@@ -15323,10 +15323,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D560" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Investigation mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Investigation mají postih −1.</x:v>
       </x:c>
       <x:c r="E560" s="2" t="str">
-        <x:v>Přidáš zbytečnou vyšetřovací okliku a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš zbytečnou vyšetřovací okliku a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F560"/>
       <x:c r="G560">
@@ -15470,10 +15470,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D567" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Investigation má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Investigation mají postih −3.</x:v>
       </x:c>
       <x:c r="E567" s="2" t="str">
-        <x:v>Chybějící článek si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Chybějící článek si domyslíš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F567"/>
       <x:c r="G567">
@@ -15491,10 +15491,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D568" s="2" t="str">
-        <x:v>Příští ověření dovednosti Investigation má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Investigation mají postih −2.</x:v>
       </x:c>
       <x:c r="E568" s="2" t="str">
-        <x:v>Rozbor zatížíš zbytečnou stopou a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Rozbor zatížíš zbytečnou stopou a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F568"/>
       <x:c r="G568">
@@ -15722,10 +15722,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D579" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Investigation mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Investigation mají postih −3.</x:v>
       </x:c>
       <x:c r="E579" s="2" t="str">
-        <x:v>Elegantnímu vysvětlení uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Elegantnímu vysvětlení uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F579"/>
       <x:c r="G579">
@@ -15743,10 +15743,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D580" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Investigation mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Investigation mají postih −3.</x:v>
       </x:c>
       <x:c r="E580" s="2" t="str">
-        <x:v>Přidáš zbytečnou vyšetřovací okliku a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš zbytečnou vyšetřovací okliku a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F580"/>
       <x:c r="G580">
@@ -15827,10 +15827,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D584" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Investigation automaticky selže. Následující dvě ověření dovednosti Investigation mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Investigation automaticky selže.</x:v>
       </x:c>
       <x:c r="E584" s="2" t="str">
-        <x:v>Jednu souvislost příliš zobecníš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Jednu souvislost příliš zobecníš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F584"/>
       <x:c r="G584">
@@ -15890,10 +15890,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D587" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají postih −5.</x:v>
       </x:c>
       <x:c r="E587" s="2" t="str">
-        <x:v>Chybějící článek si domyslíš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Chybějící článek si domyslíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F587"/>
       <x:c r="G587">
@@ -15911,10 +15911,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D588" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají postih −3.</x:v>
       </x:c>
       <x:c r="E588" s="2" t="str">
-        <x:v>Rozbor zatížíš zbytečnou stopou a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Rozbor zatížíš zbytečnou stopou a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F588"/>
       <x:c r="G588">
@@ -15953,10 +15953,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D590" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Inteligence mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Investigation mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E590" s="2" t="str">
-        <x:v>První vysvětlení přijmeš ochotně a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>První vysvětlení přijmeš ochotně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F590"/>
       <x:c r="G590">
@@ -15995,10 +15995,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D592" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E592" s="2" t="str">
-        <x:v>Zásadní nesrovnalost přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Zásadní nesrovnalost přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F592"/>
       <x:c r="G592">
@@ -16037,10 +16037,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D594" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E594" s="2" t="str">
-        <x:v>Správný závěr překryješ opravou a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správný závěr překryješ opravou a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F594"/>
       <x:c r="G594">
@@ -16058,10 +16058,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D595" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají postih −5. Příští záchranný hod na Inteligenci má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají postih −5.</x:v>
       </x:c>
       <x:c r="E595" s="2" t="str">
-        <x:v>Přeceníš spolehlivost vlastního odhadu a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš spolehlivost vlastního odhadu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F595"/>
       <x:c r="G595">
@@ -16079,10 +16079,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D596" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E596" s="2" t="str">
-        <x:v>Pátrání zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Pátrání zbytečně překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F596"/>
       <x:c r="G596">
@@ -16142,10 +16142,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D599" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Investigation mají postih −5.</x:v>
       </x:c>
       <x:c r="E599" s="2" t="str">
-        <x:v>Elegantnímu vysvětlení uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Elegantnímu vysvětlení uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F599"/>
       <x:c r="G599">
@@ -16163,10 +16163,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D600" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E600" s="2" t="str">
-        <x:v>Přidáš zbytečnou vyšetřovací okliku a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš zbytečnou vyšetřovací okliku a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F600"/>
       <x:c r="G600">
@@ -16184,10 +16184,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D601" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu. Příští dvě ověření Inteligence mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Investigation mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E601" s="2" t="str">
-        <x:v>Vlastní pátrání zamotáš domněnkami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Vlastní pátrání zamotáš domněnkami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F601"/>
       <x:c r="G601">
@@ -16436,10 +16436,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D613" s="2" t="str">
-        <x:v>Příští ověření dovednosti Nature má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Nature má postih −2.</x:v>
       </x:c>
       <x:c r="E613" s="2" t="str">
-        <x:v>Zaměníš dvě přírodní zákonitosti a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš dvě přírodní zákonitosti a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F613"/>
       <x:c r="G613">
@@ -16583,10 +16583,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D620" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Nature mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Nature mají postih −1.</x:v>
       </x:c>
       <x:c r="E620" s="2" t="str">
-        <x:v>Přírodu zbytečně vysvětluješ oklikou a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přírodu zbytečně vysvětluješ oklikou a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F620"/>
       <x:c r="G620">
@@ -16730,10 +16730,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D627" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Nature má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Nature mají postih −3.</x:v>
       </x:c>
       <x:c r="E627" s="2" t="str">
-        <x:v>Přírodní souvislost si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Přírodní souvislost si domyslíš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F627"/>
       <x:c r="G627">
@@ -16751,10 +16751,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D628" s="2" t="str">
-        <x:v>Příští ověření dovednosti Nature má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Nature mají postih −2.</x:v>
       </x:c>
       <x:c r="E628" s="2" t="str">
-        <x:v>Výklad zatížíš zbytečnou výjimkou a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Výklad zatížíš zbytečnou výjimkou a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F628"/>
       <x:c r="G628">
@@ -16982,10 +16982,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D639" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Nature mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Nature mají postih −3.</x:v>
       </x:c>
       <x:c r="E639" s="2" t="str">
-        <x:v>Povědomé poučce uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Povědomé poučce uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F639"/>
       <x:c r="G639">
@@ -17003,10 +17003,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D640" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Nature mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Nature mají postih −3.</x:v>
       </x:c>
       <x:c r="E640" s="2" t="str">
-        <x:v>Přírodu zbytečně vysvětluješ oklikou a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přírodu zbytečně vysvětluješ oklikou a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F640"/>
       <x:c r="G640">
@@ -17087,10 +17087,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D644" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Nature automaticky selže. Následující dvě ověření dovednosti Nature mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Nature automaticky selže.</x:v>
       </x:c>
       <x:c r="E644" s="2" t="str">
-        <x:v>Podobnost povýšíš na jistotu a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Podobnost povýšíš na jistotu a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F644"/>
       <x:c r="G644">
@@ -17150,10 +17150,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D647" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají postih −5.</x:v>
       </x:c>
       <x:c r="E647" s="2" t="str">
-        <x:v>Přírodní souvislost si domyslíš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Přírodní souvislost si domyslíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F647"/>
       <x:c r="G647">
@@ -17171,10 +17171,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D648" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají postih −3.</x:v>
       </x:c>
       <x:c r="E648" s="2" t="str">
-        <x:v>Výklad zatížíš zbytečnou výjimkou a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Výklad zatížíš zbytečnou výjimkou a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F648"/>
       <x:c r="G648">
@@ -17213,10 +17213,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D650" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Inteligence mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Nature mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E650" s="2" t="str">
-        <x:v>Povědomý znak přijmeš bez ověření a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Povědomý znak přijmeš bez ověření a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F650"/>
       <x:c r="G650">
@@ -17255,10 +17255,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D652" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E652" s="2" t="str">
-        <x:v>Klíčový rozdíl přejdeš samolibě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Klíčový rozdíl přejdeš samolibě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F652"/>
       <x:c r="G652">
@@ -17297,10 +17297,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D654" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E654" s="2" t="str">
-        <x:v>Správnou znalost překryješ dohadem a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správnou znalost překryješ dohadem a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F654"/>
       <x:c r="G654">
@@ -17318,10 +17318,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D655" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají postih −5. Příští záchranný hod na Inteligenci má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají postih −5.</x:v>
       </x:c>
       <x:c r="E655" s="2" t="str">
-        <x:v>Přeceníš přesnost známého pravidla a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš přesnost známého pravidla a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F655"/>
       <x:c r="G655">
@@ -17339,10 +17339,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D656" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E656" s="2" t="str">
-        <x:v>Jednoduchý princip zbytečně rozebereš a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jednoduchý princip zbytečně rozebereš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F656"/>
       <x:c r="G656">
@@ -17402,10 +17402,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D659" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Nature mají postih −5.</x:v>
       </x:c>
       <x:c r="E659" s="2" t="str">
-        <x:v>Povědomé poučce uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Povědomé poučce uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F659"/>
       <x:c r="G659">
@@ -17423,10 +17423,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D660" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E660" s="2" t="str">
-        <x:v>Přírodu zbytečně vysvětluješ oklikou a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přírodu zbytečně vysvětluješ oklikou a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F660"/>
       <x:c r="G660">
@@ -17444,10 +17444,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D661" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu. Příští dvě ověření Inteligence mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Nature mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E661" s="2" t="str">
-        <x:v>Známé souvislosti si zamotáš a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Známé souvislosti si zamotáš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F661"/>
       <x:c r="G661">
@@ -17696,10 +17696,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D673" s="2" t="str">
-        <x:v>Příští ověření dovednosti Religion má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Religion má postih −2.</x:v>
       </x:c>
       <x:c r="E673" s="2" t="str">
-        <x:v>Zaměníš dvě známá učení a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš dvě známá učení a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F673"/>
       <x:c r="G673">
@@ -17843,10 +17843,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D680" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Religion mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Religion mají postih −1.</x:v>
       </x:c>
       <x:c r="E680" s="2" t="str">
-        <x:v>Přidáš zbytečnou věroučnou okliku a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš zbytečnou věroučnou okliku a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F680"/>
       <x:c r="G680">
@@ -17990,10 +17990,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D687" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Religion má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Religion mají postih −3.</x:v>
       </x:c>
       <x:c r="E687" s="2" t="str">
-        <x:v>Náboženskou souvislost si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Náboženskou souvislost si domyslíš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F687"/>
       <x:c r="G687">
@@ -18011,10 +18011,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D688" s="2" t="str">
-        <x:v>Příští ověření dovednosti Religion má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Religion mají postih −2.</x:v>
       </x:c>
       <x:c r="E688" s="2" t="str">
-        <x:v>Rozbor zatížíš učenou odbočkou a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Rozbor zatížíš učenou odbočkou a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F688"/>
       <x:c r="G688">
@@ -18242,10 +18242,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D699" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Religion mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Religion mají postih −3.</x:v>
       </x:c>
       <x:c r="E699" s="2" t="str">
-        <x:v>Slavnostnímu dojmu uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Slavnostnímu dojmu uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F699"/>
       <x:c r="G699">
@@ -18263,10 +18263,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D700" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Religion mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Religion mají postih −3.</x:v>
       </x:c>
       <x:c r="E700" s="2" t="str">
-        <x:v>Přidáš zbytečnou věroučnou okliku a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš zbytečnou věroučnou okliku a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F700"/>
       <x:c r="G700">
@@ -18347,10 +18347,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D704" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Religion automaticky selže. Následující dvě ověření dovednosti Religion mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Religion automaticky selže.</x:v>
       </x:c>
       <x:c r="E704" s="2" t="str">
-        <x:v>Jednu tradici příliš zobecníš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Jednu tradici příliš zobecníš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F704"/>
       <x:c r="G704">
@@ -18410,10 +18410,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D707" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají postih −5.</x:v>
       </x:c>
       <x:c r="E707" s="2" t="str">
-        <x:v>Náboženskou souvislost si domyslíš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Náboženskou souvislost si domyslíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F707"/>
       <x:c r="G707">
@@ -18431,10 +18431,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D708" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají postih −3.</x:v>
       </x:c>
       <x:c r="E708" s="2" t="str">
-        <x:v>Rozbor zatížíš učenou odbočkou a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Rozbor zatížíš učenou odbočkou a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F708"/>
       <x:c r="G708">
@@ -18473,10 +18473,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D710" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Inteligence mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Religion mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E710" s="2" t="str">
-        <x:v>Povědomý význam přijmeš bez ověření a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Povědomý význam přijmeš bez ověření a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F710"/>
       <x:c r="G710">
@@ -18515,10 +18515,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D712" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E712" s="2" t="str">
-        <x:v>Důležitou výjimku přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Důležitou výjimku přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F712"/>
       <x:c r="G712">
@@ -18557,10 +18557,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D714" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E714" s="2" t="str">
-        <x:v>Správnou vzpomínku překryješ výkladem a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správnou vzpomínku překryješ výkladem a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F714"/>
       <x:c r="G714">
@@ -18578,10 +18578,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D715" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají postih −5. Příští záchranný hod na Inteligenci má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají postih −5.</x:v>
       </x:c>
       <x:c r="E715" s="2" t="str">
-        <x:v>Přeceníš přesnost vlastní znalosti a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš přesnost vlastní znalosti a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F715"/>
       <x:c r="G715">
@@ -18599,10 +18599,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D716" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E716" s="2" t="str">
-        <x:v>Jednoduchou poučku překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jednoduchou poučku překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F716"/>
       <x:c r="G716">
@@ -18662,10 +18662,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D719" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Inteligence mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Religion mají postih −5.</x:v>
       </x:c>
       <x:c r="E719" s="2" t="str">
-        <x:v>Slavnostnímu dojmu uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Slavnostnímu dojmu uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F719"/>
       <x:c r="G719">
@@ -18683,10 +18683,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D720" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E720" s="2" t="str">
-        <x:v>Přidáš zbytečnou věroučnou okliku a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš zbytečnou věroučnou okliku a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F720"/>
       <x:c r="G720">
@@ -18704,10 +18704,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D721" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu. Příští dvě ověření Inteligence mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Religion mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E721" s="2" t="str">
-        <x:v>Vlastní znalosti zamotáš opravami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Vlastní znalosti zamotáš opravami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F721"/>
       <x:c r="G721">
@@ -18956,10 +18956,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D733" s="2" t="str">
-        <x:v>Příští ověření Moudrosti má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření Moudrosti má postih −2.</x:v>
       </x:c>
       <x:c r="E733" s="2" t="str">
-        <x:v>Zaměníš přání za skutečný odhad a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš přání za skutečný odhad a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F733"/>
       <x:c r="G733">
@@ -19103,10 +19103,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D740" s="2" t="str">
-        <x:v>Příští dvě ověření Moudrosti mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření Moudrosti mají postih −1.</x:v>
       </x:c>
       <x:c r="E740" s="2" t="str">
-        <x:v>Přidáš zbytečnou rozhodovací okliku a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš zbytečnou rozhodovací okliku a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F740"/>
       <x:c r="G740">
@@ -19250,10 +19250,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D747" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Moudrosti má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření Moudrosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E747" s="2" t="str">
-        <x:v>Chybějící jistotu nahradíš domněnkou a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Chybějící jistotu nahradíš domněnkou a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F747"/>
       <x:c r="G747">
@@ -19271,10 +19271,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D748" s="2" t="str">
-        <x:v>Příští ověření Moudrosti má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření Moudrosti mají postih −2.</x:v>
       </x:c>
       <x:c r="E748" s="2" t="str">
-        <x:v>Rozhodování zatížíš zbytečnou pochybností a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Rozhodování zatížíš zbytečnou pochybností a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F748"/>
       <x:c r="G748">
@@ -19502,10 +19502,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D759" s="2" t="str">
-        <x:v>Příští tři ověření Moudrosti mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření Moudrosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E759" s="2" t="str">
-        <x:v>Dojmu rozvahy uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Dojmu rozvahy uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F759"/>
       <x:c r="G759">
@@ -19523,10 +19523,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D760" s="2" t="str">
-        <x:v>Příští dvě ověření Moudrosti mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření Moudrosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E760" s="2" t="str">
-        <x:v>Přidáš zbytečnou rozhodovací okliku a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš zbytečnou rozhodovací okliku a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F760"/>
       <x:c r="G760">
@@ -19607,10 +19607,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D764" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření Moudrosti automaticky selže. Následující dvě ověření Moudrosti mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření Moudrosti automaticky selže.</x:v>
       </x:c>
       <x:c r="E764" s="2" t="str">
-        <x:v>Jednu zkušenost příliš zobecníš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Jednu zkušenost příliš zobecníš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F764"/>
       <x:c r="G764">
@@ -19670,10 +19670,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D767" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −5.</x:v>
       </x:c>
       <x:c r="E767" s="2" t="str">
-        <x:v>Chybějící jistotu nahradíš domněnkou a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Chybějící jistotu nahradíš domněnkou a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F767"/>
       <x:c r="G767">
@@ -19691,10 +19691,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D768" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E768" s="2" t="str">
-        <x:v>Rozhodování zatížíš zbytečnou pochybností a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Rozhodování zatížíš zbytečnou pochybností a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F768"/>
       <x:c r="G768">
@@ -19733,10 +19733,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D770" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Moudrosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření Moudrosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E770" s="2" t="str">
-        <x:v>Prvnímu pocitu uvěříš ochotně a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Prvnímu pocitu uvěříš ochotně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F770"/>
       <x:c r="G770">
@@ -19775,10 +19775,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D772" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E772" s="2" t="str">
-        <x:v>Varovný náznak přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Varovný náznak přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F772"/>
       <x:c r="G772">
@@ -19817,10 +19817,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D774" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E774" s="2" t="str">
-        <x:v>Správný pocit překryješ pochybností a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správný pocit překryješ pochybností a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F774"/>
       <x:c r="G774">
@@ -19838,10 +19838,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D775" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −5. Příští záchranný hod na Moudrost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −5.</x:v>
       </x:c>
       <x:c r="E775" s="2" t="str">
-        <x:v>Přeceníš spolehlivost vlastní intuice a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš spolehlivost vlastní intuice a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F775"/>
       <x:c r="G775">
@@ -19859,10 +19859,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D776" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E776" s="2" t="str">
-        <x:v>Prostý úsudek zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Prostý úsudek zbytečně překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F776"/>
       <x:c r="G776">
@@ -19922,10 +19922,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D779" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −5.</x:v>
       </x:c>
       <x:c r="E779" s="2" t="str">
-        <x:v>Dojmu rozvahy uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Dojmu rozvahy uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F779"/>
       <x:c r="G779">
@@ -19943,10 +19943,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D780" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E780" s="2" t="str">
-        <x:v>Přidáš zbytečnou rozhodovací okliku a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš zbytečnou rozhodovací okliku a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F780"/>
       <x:c r="G780">
@@ -19964,10 +19964,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D781" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu. Příští dvě ověření Moudrosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Moudrosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E781" s="2" t="str">
-        <x:v>Vlastní odhad zamotáš opravami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Vlastní odhad zamotáš opravami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F781"/>
       <x:c r="G781">
@@ -20216,10 +20216,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D793" s="2" t="str">
-        <x:v>Příští ověření dovednosti Animal Handling má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Animal Handling má postih −2.</x:v>
       </x:c>
       <x:c r="E793" s="2" t="str">
-        <x:v>Zaměníš očekávání za pochopení a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš očekávání za pochopení a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F793"/>
       <x:c r="G793">
@@ -20363,10 +20363,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D800" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Animal Handling mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Animal Handling mají postih −1.</x:v>
       </x:c>
       <x:c r="E800" s="2" t="str">
-        <x:v>Zbytečně zkomplikuješ vlastní přístup a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Zbytečně zkomplikuješ vlastní přístup a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F800"/>
       <x:c r="G800">
@@ -20510,10 +20510,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D807" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Animal Handling má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Animal Handling mají postih −3.</x:v>
       </x:c>
       <x:c r="E807" s="2" t="str">
-        <x:v>Chování si doplníš domněnkou a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Chování si doplníš domněnkou a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F807"/>
       <x:c r="G807">
@@ -20531,10 +20531,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D808" s="2" t="str">
-        <x:v>Příští ověření dovednosti Animal Handling má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Animal Handling mají postih −2.</x:v>
       </x:c>
       <x:c r="E808" s="2" t="str">
-        <x:v>Přístup zatížíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Přístup zatížíš zbytečným váháním a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F808"/>
       <x:c r="G808">
@@ -20762,10 +20762,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D819" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Animal Handling mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Animal Handling mají postih −3.</x:v>
       </x:c>
       <x:c r="E819" s="2" t="str">
-        <x:v>Představě kontroly uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Představě kontroly uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F819"/>
       <x:c r="G819">
@@ -20783,10 +20783,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D820" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Animal Handling mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Animal Handling mají postih −3.</x:v>
       </x:c>
       <x:c r="E820" s="2" t="str">
-        <x:v>Zbytečně zkomplikuješ vlastní přístup a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Zbytečně zkomplikuješ vlastní přístup a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F820"/>
       <x:c r="G820">
@@ -20867,10 +20867,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D824" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Animal Handling automaticky selže. Následující dvě ověření dovednosti Animal Handling mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Animal Handling automaticky selže.</x:v>
       </x:c>
       <x:c r="E824" s="2" t="str">
-        <x:v>Jeden náznak příliš zobecníš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Jeden náznak příliš zobecníš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F824"/>
       <x:c r="G824">
@@ -20930,10 +20930,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D827" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají postih −5.</x:v>
       </x:c>
       <x:c r="E827" s="2" t="str">
-        <x:v>Chování si doplníš domněnkou a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Chování si doplníš domněnkou a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F827"/>
       <x:c r="G827">
@@ -20951,10 +20951,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D828" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají postih −3.</x:v>
       </x:c>
       <x:c r="E828" s="2" t="str">
-        <x:v>Přístup zatížíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Přístup zatížíš zbytečným váháním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F828"/>
       <x:c r="G828">
@@ -20993,10 +20993,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D830" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Moudrosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Animal Handling mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E830" s="2" t="str">
-        <x:v>Povědomé reakci uvěříš ochotně a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Povědomé reakci uvěříš ochotně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F830"/>
       <x:c r="G830">
@@ -21035,10 +21035,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D832" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E832" s="2" t="str">
-        <x:v>Jemný signál přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Jemný signál přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F832"/>
       <x:c r="G832">
@@ -21077,10 +21077,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D834" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E834" s="2" t="str">
-        <x:v>Správný přístup opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správný přístup opravíš přehnaně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F834"/>
       <x:c r="G834">
@@ -21098,10 +21098,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D835" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají postih −5. Příští záchranný hod na Moudrost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají postih −5.</x:v>
       </x:c>
       <x:c r="E835" s="2" t="str">
-        <x:v>Přeceníš jistotu svého odhadu a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš jistotu svého odhadu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F835"/>
       <x:c r="G835">
@@ -21119,10 +21119,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D836" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E836" s="2" t="str">
-        <x:v>Jednoduché chování zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jednoduché chování zbytečně překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F836"/>
       <x:c r="G836">
@@ -21182,10 +21182,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D839" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají postih −5.</x:v>
       </x:c>
       <x:c r="E839" s="2" t="str">
-        <x:v>Představě kontroly uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Představě kontroly uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F839"/>
       <x:c r="G839">
@@ -21203,10 +21203,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D840" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E840" s="2" t="str">
-        <x:v>Zbytečně zkomplikuješ vlastní přístup a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Zbytečně zkomplikuješ vlastní přístup a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F840"/>
       <x:c r="G840">
@@ -21224,10 +21224,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D841" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu. Příští dvě ověření Moudrosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Animal Handling mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E841" s="2" t="str">
-        <x:v>Přirozené jednání zamotáš opravami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Přirozené jednání zamotáš opravami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F841"/>
       <x:c r="G841">
@@ -21476,10 +21476,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D853" s="2" t="str">
-        <x:v>Příští ověření dovednosti Insight má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Insight má postih −2.</x:v>
       </x:c>
       <x:c r="E853" s="2" t="str">
-        <x:v>Zaměníš obavu za skutečný úmysl a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš obavu za skutečný úmysl a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F853"/>
       <x:c r="G853">
@@ -21623,10 +21623,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D860" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Insight mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Insight mají postih −1.</x:v>
       </x:c>
       <x:c r="E860" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v úsudku a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš zbytečnou okliku v úsudku a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F860"/>
       <x:c r="G860">
@@ -21770,10 +21770,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D867" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Insight má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Insight mají postih −3.</x:v>
       </x:c>
       <x:c r="E867" s="2" t="str">
-        <x:v>Cizí úmysl si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Cizí úmysl si domyslíš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F867"/>
       <x:c r="G867">
@@ -21791,10 +21791,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D868" s="2" t="str">
-        <x:v>Příští ověření dovednosti Insight má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Insight mají postih −2.</x:v>
       </x:c>
       <x:c r="E868" s="2" t="str">
-        <x:v>Odhad zatížíš zbytečnou pochybností a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Odhad zatížíš zbytečnou pochybností a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F868"/>
       <x:c r="G868">
@@ -22022,10 +22022,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D879" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Insight mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Insight mají postih −3.</x:v>
       </x:c>
       <x:c r="E879" s="2" t="str">
-        <x:v>Vlastní prozíravosti uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Vlastní prozíravosti uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F879"/>
       <x:c r="G879">
@@ -22043,10 +22043,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D880" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Insight mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Insight mají postih −3.</x:v>
       </x:c>
       <x:c r="E880" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v úsudku a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš zbytečnou okliku v úsudku a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F880"/>
       <x:c r="G880">
@@ -22127,10 +22127,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D884" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Insight automaticky selže. Následující dvě ověření dovednosti Insight mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Insight automaticky selže.</x:v>
       </x:c>
       <x:c r="E884" s="2" t="str">
-        <x:v>Jeden náznak vyložíš velkoryse a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Jeden náznak vyložíš velkoryse a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F884"/>
       <x:c r="G884">
@@ -22190,10 +22190,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D887" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají postih −5.</x:v>
       </x:c>
       <x:c r="E887" s="2" t="str">
-        <x:v>Cizí úmysl si domyslíš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Cizí úmysl si domyslíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F887"/>
       <x:c r="G887">
@@ -22211,10 +22211,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D888" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají postih −3.</x:v>
       </x:c>
       <x:c r="E888" s="2" t="str">
-        <x:v>Odhad zatížíš zbytečnou pochybností a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Odhad zatížíš zbytečnou pochybností a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F888"/>
       <x:c r="G888">
@@ -22253,10 +22253,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D890" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Moudrosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Insight mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E890" s="2" t="str">
-        <x:v>Povědomému dojmu uvěříš bez ověření a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Povědomému dojmu uvěříš bez ověření a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F890"/>
       <x:c r="G890">
@@ -22295,10 +22295,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D892" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E892" s="2" t="str">
-        <x:v>Podstatnou nesrovnalost přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Podstatnou nesrovnalost přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F892"/>
       <x:c r="G892">
@@ -22337,10 +22337,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D894" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E894" s="2" t="str">
-        <x:v>Správný dojem překryješ podezřením a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správný dojem překryješ podezřením a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F894"/>
       <x:c r="G894">
@@ -22358,10 +22358,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D895" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají postih −5. Příští záchranný hod na Moudrost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají postih −5.</x:v>
       </x:c>
       <x:c r="E895" s="2" t="str">
-        <x:v>Přeceníš přesnost vlastního vhledu a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš přesnost vlastního vhledu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F895"/>
       <x:c r="G895">
@@ -22379,10 +22379,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D896" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E896" s="2" t="str">
-        <x:v>Prosté jednání zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Prosté jednání zbytečně překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F896"/>
       <x:c r="G896">
@@ -22442,10 +22442,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D899" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Insight mají postih −5.</x:v>
       </x:c>
       <x:c r="E899" s="2" t="str">
-        <x:v>Vlastní prozíravosti uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Vlastní prozíravosti uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F899"/>
       <x:c r="G899">
@@ -22463,10 +22463,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D900" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E900" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v úsudku a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš zbytečnou okliku v úsudku a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F900"/>
       <x:c r="G900">
@@ -22484,10 +22484,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D901" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu. Příští dvě ověření Moudrosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Insight mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E901" s="2" t="str">
-        <x:v>Cizí jednání zamotáš výkladem a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Cizí jednání zamotáš výkladem a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F901"/>
       <x:c r="G901">
@@ -22736,10 +22736,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D913" s="2" t="str">
-        <x:v>Příští ověření dovednosti Medicine má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Medicine má postih −2.</x:v>
       </x:c>
       <x:c r="E913" s="2" t="str">
-        <x:v>Zaměníš podobnost za vysvětlení a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš podobnost za vysvětlení a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F913"/>
       <x:c r="G913">
@@ -22883,10 +22883,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D920" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Medicine mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Medicine mají postih −1.</x:v>
       </x:c>
       <x:c r="E920" s="2" t="str">
-        <x:v>Přidáš zbytečnou diagnostickou okliku a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš zbytečnou diagnostickou okliku a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F920"/>
       <x:c r="G920">
@@ -23030,10 +23030,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D927" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Medicine má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Medicine mají postih −3.</x:v>
       </x:c>
       <x:c r="E927" s="2" t="str">
-        <x:v>Chybějící poznatek si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Chybějící poznatek si domyslíš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F927"/>
       <x:c r="G927">
@@ -23051,10 +23051,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D928" s="2" t="str">
-        <x:v>Příští ověření dovednosti Medicine má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Medicine mají postih −2.</x:v>
       </x:c>
       <x:c r="E928" s="2" t="str">
-        <x:v>Postup zatížíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Postup zatížíš zbytečným váháním a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F928"/>
       <x:c r="G928">
@@ -23282,10 +23282,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D939" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Medicine mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Medicine mají postih −3.</x:v>
       </x:c>
       <x:c r="E939" s="2" t="str">
-        <x:v>Dojmu odbornosti uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Dojmu odbornosti uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F939"/>
       <x:c r="G939">
@@ -23303,10 +23303,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D940" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Medicine mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Medicine mají postih −3.</x:v>
       </x:c>
       <x:c r="E940" s="2" t="str">
-        <x:v>Přidáš zbytečnou diagnostickou okliku a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš zbytečnou diagnostickou okliku a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F940"/>
       <x:c r="G940">
@@ -23387,10 +23387,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D944" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Medicine automaticky selže. Následující dvě ověření dovednosti Medicine mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Medicine automaticky selže.</x:v>
       </x:c>
       <x:c r="E944" s="2" t="str">
-        <x:v>Známý příznak příliš zobecníš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Známý příznak příliš zobecníš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F944"/>
       <x:c r="G944">
@@ -23450,10 +23450,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D947" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají postih −5.</x:v>
       </x:c>
       <x:c r="E947" s="2" t="str">
-        <x:v>Chybějící poznatek si domyslíš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Chybějící poznatek si domyslíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F947"/>
       <x:c r="G947">
@@ -23471,10 +23471,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D948" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají postih −3.</x:v>
       </x:c>
       <x:c r="E948" s="2" t="str">
-        <x:v>Postup zatížíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Postup zatížíš zbytečným váháním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F948"/>
       <x:c r="G948">
@@ -23513,10 +23513,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D950" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Moudrosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Medicine mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E950" s="2" t="str">
-        <x:v>Povědomému projevu uvěříš ochotně a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Povědomému projevu uvěříš ochotně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F950"/>
       <x:c r="G950">
@@ -23555,10 +23555,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D952" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E952" s="2" t="str">
-        <x:v>Důležitou odlišnost přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Důležitou odlišnost přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F952"/>
       <x:c r="G952">
@@ -23597,10 +23597,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D954" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E954" s="2" t="str">
-        <x:v>Správný postup opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správný postup opravíš přehnaně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F954"/>
       <x:c r="G954">
@@ -23618,10 +23618,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D955" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají postih −5. Příští záchranný hod na Moudrost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají postih −5.</x:v>
       </x:c>
       <x:c r="E955" s="2" t="str">
-        <x:v>Přeceníš vlastní diagnostickou jistotu a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš vlastní diagnostickou jistotu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F955"/>
       <x:c r="G955">
@@ -23639,10 +23639,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D956" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E956" s="2" t="str">
-        <x:v>Jednoduché posouzení překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jednoduché posouzení překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F956"/>
       <x:c r="G956">
@@ -23702,10 +23702,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D959" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Medicine mají postih −5.</x:v>
       </x:c>
       <x:c r="E959" s="2" t="str">
-        <x:v>Dojmu odbornosti uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Dojmu odbornosti uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F959"/>
       <x:c r="G959">
@@ -23723,10 +23723,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D960" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E960" s="2" t="str">
-        <x:v>Přidáš zbytečnou diagnostickou okliku a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš zbytečnou diagnostickou okliku a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F960"/>
       <x:c r="G960">
@@ -23744,10 +23744,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D961" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu. Příští dvě ověření Moudrosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Medicine mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E961" s="2" t="str">
-        <x:v>Zdravotní souvislosti si zamotáš a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Zdravotní souvislosti si zamotáš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F961"/>
       <x:c r="G961">
@@ -23996,10 +23996,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D973" s="2" t="str">
-        <x:v>Příští ověření dovednosti Perception má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Perception má postih −2.</x:v>
       </x:c>
       <x:c r="E973" s="2" t="str">
-        <x:v>Zaměníš očekávání za skutečný vjem a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš očekávání za skutečný vjem a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F973"/>
       <x:c r="G973">
@@ -24143,10 +24143,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D980" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Perception mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Perception mají postih −1.</x:v>
       </x:c>
       <x:c r="E980" s="2" t="str">
-        <x:v>Zbytečně si roztříštíš vlastní pozornost a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Zbytečně si roztříštíš vlastní pozornost a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F980"/>
       <x:c r="G980">
@@ -24290,10 +24290,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D987" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Perception má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Perception mají postih −3.</x:v>
       </x:c>
       <x:c r="E987" s="2" t="str">
-        <x:v>Chybějící detail si domyslíš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Chybějící detail si domyslíš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F987"/>
       <x:c r="G987" t="n">
@@ -24311,10 +24311,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D988" s="2" t="str">
-        <x:v>Příští ověření dovednosti Perception má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Perception mají postih −2.</x:v>
       </x:c>
       <x:c r="E988" s="2" t="str">
-        <x:v>Pozorování zatížíš zbytečnou pochybností a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Pozorování zatížíš zbytečnou pochybností a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F988"/>
       <x:c r="G988" t="n">
@@ -24542,10 +24542,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D999" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Perception mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Perception mají postih −3.</x:v>
       </x:c>
       <x:c r="E999" s="2" t="str">
-        <x:v>Vlastní ostražitosti uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Vlastní ostražitosti uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F999"/>
       <x:c r="G999" t="n">
@@ -24563,10 +24563,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D1000" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Perception mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Perception mají postih −3.</x:v>
       </x:c>
       <x:c r="E1000" s="2" t="str">
-        <x:v>Zbytečně si roztříštíš vlastní pozornost a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Zbytečně si roztříštíš vlastní pozornost a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1000"/>
       <x:c r="G1000" t="n">
@@ -24647,10 +24647,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1004" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Perception automaticky selže. Následující dvě ověření dovednosti Perception mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Perception automaticky selže.</x:v>
       </x:c>
       <x:c r="E1004" s="2" t="str">
-        <x:v>Jednomu vjemu přidáš váhu a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Jednomu vjemu přidáš váhu a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F1004"/>
       <x:c r="G1004">
@@ -24710,10 +24710,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1007" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají postih −5.</x:v>
       </x:c>
       <x:c r="E1007" s="2" t="str">
-        <x:v>Chybějící detail si domyslíš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Chybějící detail si domyslíš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1007"/>
       <x:c r="G1007">
@@ -24731,10 +24731,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1008" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají postih −3.</x:v>
       </x:c>
       <x:c r="E1008" s="2" t="str">
-        <x:v>Pozorování zatížíš zbytečnou pochybností a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Pozorování zatížíš zbytečnou pochybností a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1008"/>
       <x:c r="G1008">
@@ -24773,10 +24773,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1010" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Moudrosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Perception mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1010" s="2" t="str">
-        <x:v>Prvnímu vjemu uvěříš bez ověření a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Prvnímu vjemu uvěříš bez ověření a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1010"/>
       <x:c r="G1010">
@@ -24857,10 +24857,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1014" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Perception mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Perception mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1014" s="2" t="str">
-        <x:v>Správný postřeh překryješ dohadem a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správný postřeh překryješ dohadem a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1014"/>
       <x:c r="G1014">
@@ -24878,10 +24878,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1015" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají postih −5. Příští záchranný hod na Moudrost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají postih −5.</x:v>
       </x:c>
       <x:c r="E1015" s="2" t="str">
-        <x:v>Přeceníš rozsah vlastní pozornosti a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš rozsah vlastní pozornosti a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1015"/>
       <x:c r="G1015">
@@ -24899,10 +24899,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1016" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1016" s="2" t="str">
-        <x:v>Soustředění zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Soustředění zbytečně překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1016"/>
       <x:c r="G1016">
@@ -24962,10 +24962,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1019" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Perception mají postih −5.</x:v>
       </x:c>
       <x:c r="E1019" s="2" t="str">
-        <x:v>Vlastní ostražitosti uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Vlastní ostražitosti uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1019"/>
       <x:c r="G1019">
@@ -24983,10 +24983,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1020" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1020" s="2" t="str">
-        <x:v>Zbytečně si roztříštíš vlastní pozornost a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Zbytečně si roztříštíš vlastní pozornost a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F1020"/>
       <x:c r="G1020">
@@ -25004,10 +25004,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1021" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Perception mají nevýhodu. Příští dvě ověření Moudrosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Perception mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1021" s="2" t="str">
-        <x:v>Vjemy si zamotáš neustálým opravováním a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Vjemy si zamotáš neustálým opravováním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1021"/>
       <x:c r="G1021">
@@ -25256,10 +25256,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1033" s="2" t="str">
-        <x:v>Příští ověření dovednosti Survival má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Survival má postih −2.</x:v>
       </x:c>
       <x:c r="E1033" s="2" t="str">
-        <x:v>Zaměníš zkušenost za platné pravidlo a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš zkušenost za platné pravidlo a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1033"/>
       <x:c r="G1033">
@@ -25403,10 +25403,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1040" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Survival mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Survival mají postih −1.</x:v>
       </x:c>
       <x:c r="E1040" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v postupu a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš zbytečnou okliku v postupu a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F1040"/>
       <x:c r="G1040">
@@ -25550,10 +25550,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1047" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Survival má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Survival mají postih −3.</x:v>
       </x:c>
       <x:c r="E1047" s="2" t="str">
-        <x:v>Chybějící souvislost doplníš odhadem a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Chybějící souvislost doplníš odhadem a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1047"/>
       <x:c r="G1047">
@@ -25571,10 +25571,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1048" s="2" t="str">
-        <x:v>Příští ověření dovednosti Survival má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Survival mají postih −2.</x:v>
       </x:c>
       <x:c r="E1048" s="2" t="str">
-        <x:v>Přípravu zatížíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Přípravu zatížíš zbytečným váháním a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1048"/>
       <x:c r="G1048">
@@ -25802,10 +25802,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1059" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Survival mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Survival mají postih −3.</x:v>
       </x:c>
       <x:c r="E1059" s="2" t="str">
-        <x:v>Vlastní připravenosti uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Vlastní připravenosti uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1059"/>
       <x:c r="G1059">
@@ -25823,10 +25823,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1060" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Survival mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Survival mají postih −3.</x:v>
       </x:c>
       <x:c r="E1060" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v postupu a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš zbytečnou okliku v postupu a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1060"/>
       <x:c r="G1060">
@@ -25907,10 +25907,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1064" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Survival automaticky selže. Následující dvě ověření dovednosti Survival mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Survival automaticky selže.</x:v>
       </x:c>
       <x:c r="E1064" s="2" t="str">
-        <x:v>Jednu zákonitost příliš zobecníš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Jednu zákonitost příliš zobecníš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F1064"/>
       <x:c r="G1064">
@@ -25970,10 +25970,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1067" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají postih −5.</x:v>
       </x:c>
       <x:c r="E1067" s="2" t="str">
-        <x:v>Chybějící souvislost doplníš odhadem a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Chybějící souvislost doplníš odhadem a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1067"/>
       <x:c r="G1067">
@@ -25991,10 +25991,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1068" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají postih −3.</x:v>
       </x:c>
       <x:c r="E1068" s="2" t="str">
-        <x:v>Přípravu zatížíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Přípravu zatížíš zbytečným váháním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1068"/>
       <x:c r="G1068">
@@ -26033,10 +26033,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1070" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Moudrosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Survival mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1070" s="2" t="str">
-        <x:v>Povědomé podmínky přijmeš bez ověření a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Povědomé podmínky přijmeš bez ověření a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1070"/>
       <x:c r="G1070">
@@ -26075,10 +26075,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1072" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1072" s="2" t="str">
-        <x:v>Důležitý náznak přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Důležitý náznak přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1072"/>
       <x:c r="G1072">
@@ -26117,10 +26117,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1074" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1074" s="2" t="str">
-        <x:v>Správný odhad opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Správný odhad opravíš přehnaně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1074"/>
       <x:c r="G1074">
@@ -26138,10 +26138,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1075" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají postih −5. Příští záchranný hod na Moudrost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají postih −5.</x:v>
       </x:c>
       <x:c r="E1075" s="2" t="str">
-        <x:v>Přeceníš spolehlivost vlastní zkušenosti a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš spolehlivost vlastní zkušenosti a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1075"/>
       <x:c r="G1075">
@@ -26159,10 +26159,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1076" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1076" s="2" t="str">
-        <x:v>Jednoduché řešení překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jednoduché řešení překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1076"/>
       <x:c r="G1076">
@@ -26222,10 +26222,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1079" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Moudrosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Survival mají postih −5.</x:v>
       </x:c>
       <x:c r="E1079" s="2" t="str">
-        <x:v>Vlastní připravenosti uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Vlastní připravenosti uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1079"/>
       <x:c r="G1079">
@@ -26243,10 +26243,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1080" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1080" s="2" t="str">
-        <x:v>Přidáš zbytečnou okliku v postupu a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš zbytečnou okliku v postupu a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F1080"/>
       <x:c r="G1080">
@@ -26264,10 +26264,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1081" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu. Příští dvě ověření Moudrosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Survival mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1081" s="2" t="str">
-        <x:v>Podmínky si zamotáš přehnaným rozborem a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Podmínky si zamotáš přehnaným rozborem a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1081"/>
       <x:c r="G1081">
@@ -26516,10 +26516,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1093" s="2" t="str">
-        <x:v>Příští ověření Charismatu má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření Charismatu má postih −2.</x:v>
       </x:c>
       <x:c r="E1093" s="2" t="str">
-        <x:v>Zaměníš důraz za přirozenost a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš důraz za přirozenost a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1093"/>
       <x:c r="G1093">
@@ -26663,10 +26663,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1100" s="2" t="str">
-        <x:v>Příští dvě ověření Charismatu mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření Charismatu mají postih −1.</x:v>
       </x:c>
       <x:c r="E1100" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu projevu a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš nepotřebnou změnu projevu a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F1100"/>
       <x:c r="G1100">
@@ -26810,10 +26810,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1107" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Charismatu má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření Charismatu mají postih −3.</x:v>
       </x:c>
       <x:c r="E1107" s="2" t="str">
-        <x:v>Vlastní vystupování zbytečně přeženeš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Vlastní vystupování zbytečně přeženeš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1107"/>
       <x:c r="G1107">
@@ -26831,10 +26831,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1108" s="2" t="str">
-        <x:v>Příští ověření Charismatu má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření Charismatu mají postih −2.</x:v>
       </x:c>
       <x:c r="E1108" s="2" t="str">
-        <x:v>Projev zatížíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Projev zatížíš zbytečným váháním a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1108"/>
       <x:c r="G1108">
@@ -27062,10 +27062,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1119" s="2" t="str">
-        <x:v>Příští tři ověření Charismatu mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření Charismatu mají postih −3.</x:v>
       </x:c>
       <x:c r="E1119" s="2" t="str">
-        <x:v>Vlastnímu kouzlu uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Vlastnímu kouzlu uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1119"/>
       <x:c r="G1119">
@@ -27083,10 +27083,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1120" s="2" t="str">
-        <x:v>Příští dvě ověření Charismatu mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření Charismatu mají postih −3.</x:v>
       </x:c>
       <x:c r="E1120" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu projevu a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš nepotřebnou změnu projevu a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1120"/>
       <x:c r="G1120">
@@ -27167,10 +27167,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1124" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření Charismatu automaticky selže. Následující dvě ověření Charismatu mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření Charismatu automaticky selže.</x:v>
       </x:c>
       <x:c r="E1124" s="2" t="str">
-        <x:v>Důraz přidáš ve špatnou chvíli a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Důraz přidáš ve špatnou chvíli a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F1124"/>
       <x:c r="G1124">
@@ -27230,10 +27230,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1127" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −5.</x:v>
       </x:c>
       <x:c r="E1127" s="2" t="str">
-        <x:v>Vlastní vystupování zbytečně přeženeš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Vlastní vystupování zbytečně přeženeš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1127"/>
       <x:c r="G1127">
@@ -27251,10 +27251,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1128" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −3.</x:v>
       </x:c>
       <x:c r="E1128" s="2" t="str">
-        <x:v>Projev zatížíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Projev zatížíš zbytečným váháním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1128"/>
       <x:c r="G1128">
@@ -27293,10 +27293,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1130" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Charismatu mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření Charismatu mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1130" s="2" t="str">
-        <x:v>Úspěch svého dojmu odhadneš předčasně a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Úspěch svého dojmu odhadneš předčasně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1130"/>
       <x:c r="G1130">
@@ -27335,10 +27335,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1132" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1132" s="2" t="str">
-        <x:v>Jemnost projevu přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Jemnost projevu přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1132"/>
       <x:c r="G1132">
@@ -27377,10 +27377,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1134" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1134" s="2" t="str">
-        <x:v>Přirozený dojem opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Přirozený dojem opravíš přehnaně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1134"/>
       <x:c r="G1134">
@@ -27398,10 +27398,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1135" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −5. Příští záchranný hod na Charisma má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −5.</x:v>
       </x:c>
       <x:c r="E1135" s="2" t="str">
-        <x:v>Přeceníš přesvědčivost vlastního vystupování a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš přesvědčivost vlastního vystupování a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1135"/>
       <x:c r="G1135">
@@ -27419,10 +27419,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1136" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1136" s="2" t="str">
-        <x:v>Prosté vystupování zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Prosté vystupování zbytečně překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1136"/>
       <x:c r="G1136">
@@ -27482,10 +27482,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1139" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −5.</x:v>
       </x:c>
       <x:c r="E1139" s="2" t="str">
-        <x:v>Vlastnímu kouzlu uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Vlastnímu kouzlu uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1139"/>
       <x:c r="G1139">
@@ -27503,10 +27503,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1140" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1140" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu projevu a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš nepotřebnou změnu projevu a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F1140"/>
       <x:c r="G1140">
@@ -27524,10 +27524,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1141" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu. Příští dvě ověření Charismatu mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření Charismatu mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1141" s="2" t="str">
-        <x:v>Vystupování si zamotáš opravami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Vystupování si zamotáš opravami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1141"/>
       <x:c r="G1141">
@@ -27776,10 +27776,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1153" s="2" t="str">
-        <x:v>Příští ověření dovednosti Deception má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Deception má postih −2.</x:v>
       </x:c>
       <x:c r="E1153" s="2" t="str">
-        <x:v>Zaměníš přehánění za přesvědčivost a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš přehánění za přesvědčivost a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1153"/>
       <x:c r="G1153">
@@ -27923,10 +27923,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1160" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Deception mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Deception mají postih −1.</x:v>
       </x:c>
       <x:c r="E1160" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu verze a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš zbytečnou změnu verze a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F1160"/>
       <x:c r="G1160">
@@ -28070,10 +28070,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1167" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Deception má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Deception mají postih −3.</x:v>
       </x:c>
       <x:c r="E1167" s="2" t="str">
-        <x:v>Maskování pravdy zbytečně přeženeš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Maskování pravdy zbytečně přeženeš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1167"/>
       <x:c r="G1167">
@@ -28091,10 +28091,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1168" s="2" t="str">
-        <x:v>Příští ověření dovednosti Deception má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Deception mají postih −2.</x:v>
       </x:c>
       <x:c r="E1168" s="2" t="str">
-        <x:v>Krytí zatížíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Krytí zatížíš zbytečným váháním a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1168"/>
       <x:c r="G1168">
@@ -28322,10 +28322,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1179" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Deception mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Deception mají postih −3.</x:v>
       </x:c>
       <x:c r="E1179" s="2" t="str">
-        <x:v>Vlastnímu předstírání uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Vlastnímu předstírání uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1179"/>
       <x:c r="G1179">
@@ -28343,10 +28343,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1180" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Deception mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Deception mají postih −3.</x:v>
       </x:c>
       <x:c r="E1180" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu verze a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš zbytečnou změnu verze a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1180"/>
       <x:c r="G1180">
@@ -28427,10 +28427,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1184" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Deception automaticky selže. Následující dvě ověření dovednosti Deception mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Deception automaticky selže.</x:v>
       </x:c>
       <x:c r="E1184" s="2" t="str">
-        <x:v>Drobné vysvětlení příliš rozvineš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Drobné vysvětlení příliš rozvineš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F1184"/>
       <x:c r="G1184">
@@ -28490,10 +28490,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1187" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají postih −5.</x:v>
       </x:c>
       <x:c r="E1187" s="2" t="str">
-        <x:v>Maskování pravdy zbytečně přeženeš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Maskování pravdy zbytečně přeženeš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1187"/>
       <x:c r="G1187">
@@ -28511,10 +28511,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1188" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají postih −3.</x:v>
       </x:c>
       <x:c r="E1188" s="2" t="str">
-        <x:v>Krytí zatížíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Krytí zatížíš zbytečným váháním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1188"/>
       <x:c r="G1188">
@@ -28553,10 +28553,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1190" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Charismatu mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Deception mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1190" s="2" t="str">
-        <x:v>Věrohodnost pokusu oceníš předčasně a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Věrohodnost pokusu oceníš předčasně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1190"/>
       <x:c r="G1190">
@@ -28595,10 +28595,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1192" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1192" s="2" t="str">
-        <x:v>Podstatný nesoulad přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Podstatný nesoulad přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1192"/>
       <x:c r="G1192">
@@ -28637,10 +28637,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1194" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1194" s="2" t="str">
-        <x:v>Uváděnou verzi opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Uváděnou verzi opravíš přehnaně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1194"/>
       <x:c r="G1194">
@@ -28658,10 +28658,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1195" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají postih −5. Příští záchranný hod na Charisma má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají postih −5.</x:v>
       </x:c>
       <x:c r="E1195" s="2" t="str">
-        <x:v>Přeceníš přirozenost svého předstírání a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš přirozenost svého předstírání a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1195"/>
       <x:c r="G1195">
@@ -28679,10 +28679,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1196" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1196" s="2" t="str">
-        <x:v>Jednoduché krytí zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jednoduché krytí zbytečně překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1196"/>
       <x:c r="G1196">
@@ -28742,10 +28742,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1199" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Deception mají postih −5.</x:v>
       </x:c>
       <x:c r="E1199" s="2" t="str">
-        <x:v>Vlastnímu předstírání uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Vlastnímu předstírání uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1199"/>
       <x:c r="G1199">
@@ -28763,10 +28763,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1200" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1200" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu verze a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš zbytečnou změnu verze a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F1200"/>
       <x:c r="G1200">
@@ -28784,10 +28784,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1201" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu. Příští dvě ověření Charismatu mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Deception mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1201" s="2" t="str">
-        <x:v>Důvěryhodnost si narušíš opravami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Důvěryhodnost si narušíš opravami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1201"/>
       <x:c r="G1201">
@@ -29036,10 +29036,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1213" s="2" t="str">
-        <x:v>Příští ověření dovednosti Intimidation má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Intimidation má postih −2.</x:v>
       </x:c>
       <x:c r="E1213" s="2" t="str">
-        <x:v>Zaměníš naléhavost za autoritu a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš naléhavost za autoritu a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1213"/>
       <x:c r="G1213">
@@ -29183,10 +29183,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1220" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Intimidation mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Intimidation mají postih −1.</x:v>
       </x:c>
       <x:c r="E1220" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu důrazu a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš zbytečnou změnu důrazu a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F1220"/>
       <x:c r="G1220">
@@ -29330,10 +29330,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1227" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Intimidation má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Intimidation mají postih −3.</x:v>
       </x:c>
       <x:c r="E1227" s="2" t="str">
-        <x:v>Výhrůžný dojem zbytečně přeženeš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Výhrůžný dojem zbytečně přeženeš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1227"/>
       <x:c r="G1227">
@@ -29351,10 +29351,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1228" s="2" t="str">
-        <x:v>Příští ověření dovednosti Intimidation má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Intimidation mají postih −2.</x:v>
       </x:c>
       <x:c r="E1228" s="2" t="str">
-        <x:v>Rozhodnost narušíš vlastním váháním a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Rozhodnost narušíš vlastním váháním a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1228"/>
       <x:c r="G1228">
@@ -29582,10 +29582,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1239" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Intimidation mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Intimidation mají postih −3.</x:v>
       </x:c>
       <x:c r="E1239" s="2" t="str">
-        <x:v>Vlastní převaze uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Vlastní převaze uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1239"/>
       <x:c r="G1239">
@@ -29603,10 +29603,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1240" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Intimidation mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Intimidation mají postih −3.</x:v>
       </x:c>
       <x:c r="E1240" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu důrazu a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš zbytečnou změnu důrazu a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1240"/>
       <x:c r="G1240">
@@ -29687,10 +29687,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1244" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Intimidation automaticky selže. Následující dvě ověření dovednosti Intimidation mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Intimidation automaticky selže.</x:v>
       </x:c>
       <x:c r="E1244" s="2" t="str">
-        <x:v>Nátlak vyženeš zbytečně vysoko a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Nátlak vyženeš zbytečně vysoko a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F1244"/>
       <x:c r="G1244">
@@ -29750,10 +29750,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1247" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají postih −5.</x:v>
       </x:c>
       <x:c r="E1247" s="2" t="str">
-        <x:v>Výhrůžný dojem zbytečně přeženeš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Výhrůžný dojem zbytečně přeženeš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1247"/>
       <x:c r="G1247">
@@ -29771,10 +29771,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1248" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají postih −3.</x:v>
       </x:c>
       <x:c r="E1248" s="2" t="str">
-        <x:v>Rozhodnost narušíš vlastním váháním a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Rozhodnost narušíš vlastním váháním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1248"/>
       <x:c r="G1248">
@@ -29813,10 +29813,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1250" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Charismatu mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Intimidation mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1250" s="2" t="str">
-        <x:v>Účinek svého nátlaku oceníš předčasně a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Účinek svého nátlaku oceníš předčasně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1250"/>
       <x:c r="G1250">
@@ -29855,10 +29855,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1252" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1252" s="2" t="str">
-        <x:v>Vlastní zaváhání přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Vlastní zaváhání přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1252"/>
       <x:c r="G1252">
@@ -29897,10 +29897,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1254" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1254" s="2" t="str">
-        <x:v>Přirozený důraz opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Přirozený důraz opravíš přehnaně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1254"/>
       <x:c r="G1254">
@@ -29918,10 +29918,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1255" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají postih −5. Příští záchranný hod na Charisma má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají postih −5.</x:v>
       </x:c>
       <x:c r="E1255" s="2" t="str">
-        <x:v>Přeceníš přesvědčivost své tvrdosti a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš přesvědčivost své tvrdosti a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1255"/>
       <x:c r="G1255">
@@ -29939,10 +29939,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1256" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1256" s="2" t="str">
-        <x:v>Jednoduchý nátlak překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jednoduchý nátlak překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1256"/>
       <x:c r="G1256">
@@ -30002,10 +30002,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1259" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají postih −5.</x:v>
       </x:c>
       <x:c r="E1259" s="2" t="str">
-        <x:v>Vlastní převaze uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Vlastní převaze uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1259"/>
       <x:c r="G1259">
@@ -30023,10 +30023,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1260" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1260" s="2" t="str">
-        <x:v>Přidáš zbytečnou změnu důrazu a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš zbytečnou změnu důrazu a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F1260"/>
       <x:c r="G1260">
@@ -30044,10 +30044,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1261" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu. Příští dvě ověření Charismatu mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Intimidation mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1261" s="2" t="str">
-        <x:v>Autoritu si narušíš opravami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Autoritu si narušíš opravami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1261"/>
       <x:c r="G1261">
@@ -30296,10 +30296,10 @@
         <x:v>Sranda</x:v>
       </x:c>
       <x:c r="D1273" s="2" t="str">
-        <x:v>Příští ověření dovednosti Performance má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Performance má postih −2.</x:v>
       </x:c>
       <x:c r="E1273" s="2" t="str">
-        <x:v>Zaměníš složitost za působivost a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš složitost za působivost a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1273"/>
       <x:c r="G1273" t="n">
@@ -30443,10 +30443,10 @@
         <x:v>Sranda</x:v>
       </x:c>
       <x:c r="D1280" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Performance mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Performance mají postih −1.</x:v>
       </x:c>
       <x:c r="E1280" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu tempa a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš nepotřebnou změnu tempa a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F1280"/>
       <x:c r="G1280" t="n">
@@ -30590,10 +30590,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1287" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Performance má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Performance mají postih −3.</x:v>
       </x:c>
       <x:c r="E1287" s="2" t="str">
-        <x:v>Podání svého výkonu přeženeš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Podání svého výkonu přeženeš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1287"/>
       <x:c r="G1287">
@@ -30611,10 +30611,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1288" s="2" t="str">
-        <x:v>Příští ověření dovednosti Performance má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Performance mají postih −2.</x:v>
       </x:c>
       <x:c r="E1288" s="2" t="str">
-        <x:v>Provedení narušíš zbytečným váháním a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Provedení narušíš zbytečným váháním a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1288"/>
       <x:c r="G1288">
@@ -30842,10 +30842,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1299" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Performance mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Performance mají postih −3.</x:v>
       </x:c>
       <x:c r="E1299" s="2" t="str">
-        <x:v>Vlastnímu talentu uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Vlastnímu talentu uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1299"/>
       <x:c r="G1299">
@@ -30863,10 +30863,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1300" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Performance mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Performance mají postih −3.</x:v>
       </x:c>
       <x:c r="E1300" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu tempa a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš nepotřebnou změnu tempa a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1300"/>
       <x:c r="G1300">
@@ -30947,10 +30947,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1304" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Performance automaticky selže. Následující dvě ověření dovednosti Performance mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Performance automaticky selže.</x:v>
       </x:c>
       <x:c r="E1304" s="2" t="str">
-        <x:v>Efekt vyženeš nad možnosti a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Efekt vyženeš nad možnosti a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F1304"/>
       <x:c r="G1304">
@@ -31010,10 +31010,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1307" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají postih −5.</x:v>
       </x:c>
       <x:c r="E1307" s="2" t="str">
-        <x:v>Podání svého výkonu přeženeš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Podání svého výkonu přeženeš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1307"/>
       <x:c r="G1307">
@@ -31031,10 +31031,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1308" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají postih −3.</x:v>
       </x:c>
       <x:c r="E1308" s="2" t="str">
-        <x:v>Provedení narušíš zbytečným váháním a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Provedení narušíš zbytečným váháním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1308"/>
       <x:c r="G1308">
@@ -31073,10 +31073,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1310" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Charismatu mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Performance mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1310" s="2" t="str">
-        <x:v>Úspěch výkonu odhadneš předčasně a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Úspěch výkonu odhadneš předčasně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1310"/>
       <x:c r="G1310">
@@ -31115,10 +31115,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1312" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1312" s="2" t="str">
-        <x:v>Drobnou nepřesnost přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Drobnou nepřesnost přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1312"/>
       <x:c r="G1312">
@@ -31157,10 +31157,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1314" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1314" s="2" t="str">
-        <x:v>Přirozený výkon opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Přirozený výkon opravíš přehnaně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1314"/>
       <x:c r="G1314">
@@ -31178,10 +31178,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1315" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají postih −5. Příští záchranný hod na Charisma má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají postih −5.</x:v>
       </x:c>
       <x:c r="E1315" s="2" t="str">
-        <x:v>Přeceníš jistotu svého podání a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš jistotu svého podání a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1315"/>
       <x:c r="G1315">
@@ -31199,10 +31199,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1316" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1316" s="2" t="str">
-        <x:v>Jednoduché provedení zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Jednoduché provedení zbytečně překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1316"/>
       <x:c r="G1316">
@@ -31262,10 +31262,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1319" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Performance mají postih −5.</x:v>
       </x:c>
       <x:c r="E1319" s="2" t="str">
-        <x:v>Vlastnímu talentu uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Vlastnímu talentu uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1319"/>
       <x:c r="G1319">
@@ -31283,10 +31283,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1320" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1320" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu tempa a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš nepotřebnou změnu tempa a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F1320"/>
       <x:c r="G1320">
@@ -31304,10 +31304,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1321" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu. Příští dvě ověření Charismatu mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Performance mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1321" s="2" t="str">
-        <x:v>Celý výkon zamotáš opravami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Celý výkon zamotáš opravami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1321"/>
       <x:c r="G1321">
@@ -31556,10 +31556,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1333" s="2" t="str">
-        <x:v>Příští ověření dovednosti Persuasion má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření dovednosti Persuasion má postih −2.</x:v>
       </x:c>
       <x:c r="E1333" s="2" t="str">
-        <x:v>Zaměníš opakování za přesvědčivost a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš opakování za přesvědčivost a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1333"/>
       <x:c r="G1333">
@@ -31703,10 +31703,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1340" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Persuasion mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření dovednosti Persuasion mají postih −1.</x:v>
       </x:c>
       <x:c r="E1340" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu přístupu a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš nepotřebnou změnu přístupu a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F1340"/>
       <x:c r="G1340">
@@ -31850,10 +31850,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D1347" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření dovednosti Persuasion má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Persuasion mají postih −3.</x:v>
       </x:c>
       <x:c r="E1347" s="2" t="str">
-        <x:v>Snaze přesvědčit příliš podlehneš a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Snaze přesvědčit příliš podlehneš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1347"/>
       <x:c r="G1347" t="n">
@@ -31871,10 +31871,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D1348" s="2" t="str">
-        <x:v>Příští ověření dovednosti Persuasion má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření dovednosti Persuasion mají postih −2.</x:v>
       </x:c>
       <x:c r="E1348" s="2" t="str">
-        <x:v>Vlastní postup zatížíš váháním a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Vlastní postup zatížíš váháním a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1348"/>
       <x:c r="G1348" t="n">
@@ -32102,10 +32102,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D1359" s="2" t="str">
-        <x:v>Příští tři ověření dovednosti Persuasion mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření dovednosti Persuasion mají postih −3.</x:v>
       </x:c>
       <x:c r="E1359" s="2" t="str">
-        <x:v>Vlastnímu vlivu uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Vlastnímu vlivu uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1359"/>
       <x:c r="G1359" t="n">
@@ -32123,10 +32123,10 @@
         <x:v>Vážný</x:v>
       </x:c>
       <x:c r="D1360" s="2" t="str">
-        <x:v>Příští dvě ověření dovednosti Persuasion mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření dovednosti Persuasion mají postih −3.</x:v>
       </x:c>
       <x:c r="E1360" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu přístupu a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš nepotřebnou změnu přístupu a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1360"/>
       <x:c r="G1360" t="n">
@@ -32207,10 +32207,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1364" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Persuasion automaticky selže. Následující dvě ověření dovednosti Persuasion mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští ověření dovednosti Persuasion automaticky selže.</x:v>
       </x:c>
       <x:c r="E1364" s="2" t="str">
-        <x:v>Důvod zbytečně přikrášlíš a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Důvod zbytečně přikrášlíš a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F1364"/>
       <x:c r="G1364">
@@ -32270,10 +32270,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1367" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají postih −5.</x:v>
       </x:c>
       <x:c r="E1367" s="2" t="str">
-        <x:v>Snaze přesvědčit příliš podlehneš a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Snaze přesvědčit příliš podlehneš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1367"/>
       <x:c r="G1367">
@@ -32291,10 +32291,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1368" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají postih −3.</x:v>
       </x:c>
       <x:c r="E1368" s="2" t="str">
-        <x:v>Vlastní postup zatížíš váháním a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Vlastní postup zatížíš váháním a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1368"/>
       <x:c r="G1368">
@@ -32333,10 +32333,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1370" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští hod na iniciativu a příští ověření Charismatu mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští dvě ověření dovednosti Persuasion mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1370" s="2" t="str">
-        <x:v>Účinek svého přístupu oceníš předčasně a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Účinek svého přístupu oceníš předčasně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1370"/>
       <x:c r="G1370">
@@ -32375,10 +32375,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1372" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1372" s="2" t="str">
-        <x:v>Podstatnou slabinu přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Podstatnou slabinu přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1372"/>
       <x:c r="G1372">
@@ -32417,10 +32417,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1374" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1374" s="2" t="str">
-        <x:v>Srozumitelný důvod opravíš přehnaně a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Srozumitelný důvod opravíš přehnaně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1374"/>
       <x:c r="G1374">
@@ -32438,10 +32438,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1375" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají postih −5. Příští záchranný hod na Charisma má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají postih −5.</x:v>
       </x:c>
       <x:c r="E1375" s="2" t="str">
-        <x:v>Přeceníš sílu vlastního dojmu a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš sílu vlastního dojmu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1375"/>
       <x:c r="G1375">
@@ -32459,10 +32459,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1376" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1376" s="2" t="str">
-        <x:v>Prosté zdůvodnění zbytečně překombinuješ a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Prosté zdůvodnění zbytečně překombinuješ a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1376"/>
       <x:c r="G1376">
@@ -32522,10 +32522,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1379" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření Charismatu mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají postih −5.</x:v>
       </x:c>
       <x:c r="E1379" s="2" t="str">
-        <x:v>Vlastnímu vlivu uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Vlastnímu vlivu uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1379"/>
       <x:c r="G1379">
@@ -32543,10 +32543,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1380" s="2" t="str">
-        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 psychického poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1380" s="2" t="str">
-        <x:v>Přidáš nepotřebnou změnu přístupu a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš nepotřebnou změnu přístupu a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F1380"/>
       <x:c r="G1380">
@@ -32564,10 +32564,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1381" s="2" t="str">
-        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu. Příští dvě ověření Charismatu mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 psychického poškození. Příští tři ověření dovednosti Persuasion mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1381" s="2" t="str">
-        <x:v>Přesvědčování si zamotáš opravami a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Přesvědčování si zamotáš opravami a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1381"/>
       <x:c r="G1381">
@@ -32816,10 +32816,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1393" s="2" t="str">
-        <x:v>Příští ověření Odolnosti má postih −1. Příští záchranný hod má postih −1.</x:v>
+        <x:v>Příští ověření Odolnosti má postih −2.</x:v>
       </x:c>
       <x:c r="E1393" s="2" t="str">
-        <x:v>Zaměníš napětí za skutečnou výdrž a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Zaměníš napětí za skutečnou výdrž a další pokus zbytečně překombinuješ.</x:v>
       </x:c>
       <x:c r="F1393"/>
       <x:c r="G1393">
@@ -32963,10 +32963,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D1400" s="2" t="str">
-        <x:v>Příští dvě ověření Odolnosti mají postih −1. Příští hod na iniciativu má postih −1.</x:v>
+        <x:v>Příští dvě ověření Odolnosti mají postih −1.</x:v>
       </x:c>
       <x:c r="E1400" s="2" t="str">
-        <x:v>Přidáš námahu ve špatnou chvíli a opatrnost zpomalí další pokusy i reakce.</x:v>
+        <x:v>Přidáš námahu ve špatnou chvíli a další pokusy přehnaně hlídáš.</x:v>
       </x:c>
       <x:c r="F1400"/>
       <x:c r="G1400">
@@ -33110,10 +33110,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1407" s="2" t="str">
-        <x:v>Příští dvě ověření vlastností mají postih −1. Příští ověření Odolnosti má navíc postih −2.</x:v>
+        <x:v>Příští dvě ověření Odolnosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E1407" s="2" t="str">
-        <x:v>Pokusíš se všechno přestát silou a zmatek přeneseš i do dalších činností.</x:v>
+        <x:v>Pokusíš se všechno přestát silou a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1407"/>
       <x:c r="G1407">
@@ -33131,10 +33131,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1408" s="2" t="str">
-        <x:v>Příští ověření Odolnosti má postih −2. Příští záchranný hod má postih −2.</x:v>
+        <x:v>Příští dvě ověření Odolnosti mají postih −2.</x:v>
       </x:c>
       <x:c r="E1408" s="2" t="str">
-        <x:v>Námahu rozvrhneš příliš lehkovážně a nejistota ti naruší výkon i obranu.</x:v>
+        <x:v>Námahu rozvrhneš příliš lehkovážně a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1408"/>
       <x:c r="G1408">
@@ -33362,10 +33362,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1419" s="2" t="str">
-        <x:v>Příští tři ověření Odolnosti mají postih −2 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Příští tři ověření Odolnosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E1419" s="2" t="str">
-        <x:v>Vlastním rezervám uvěříš přespříliš a ze zmatku tě nedostane ani povzbuzení.</x:v>
+        <x:v>Vlastním rezervám uvěříš přespříliš a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1419"/>
       <x:c r="G1419">
@@ -33383,10 +33383,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D1420" s="2" t="str">
-        <x:v>Příští dvě ověření Odolnosti mají postih −3. Příští hod na iniciativu má postih −3.</x:v>
+        <x:v>Příští dvě ověření Odolnosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E1420" s="2" t="str">
-        <x:v>Přidáš námahu ve špatnou chvíli a zmatek ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přidáš námahu ve špatnou chvíli a ztratíš jistotu při dalších pokusech.</x:v>
       </x:c>
       <x:c r="F1420"/>
       <x:c r="G1420">
@@ -33467,10 +33467,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1424" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření Odolnosti automaticky selže. Následující dvě ověření Odolnosti mají postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští ověření Odolnosti automaticky selže.</x:v>
       </x:c>
       <x:c r="E1424" s="2" t="str">
-        <x:v>Varovné signály odbydeš hrdinstvím a bolest tě donutí další pokusy přerušit.</x:v>
+        <x:v>Varovné signály odbydeš hrdinstvím a bolest ti znemožní další pokus.</x:v>
       </x:c>
       <x:c r="F1424"/>
       <x:c r="G1424">
@@ -33530,10 +33530,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1427" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají postih −5. Příští dva záchranné hody mají postih −2.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají postih −5.</x:v>
       </x:c>
       <x:c r="E1427" s="2" t="str">
-        <x:v>Pokusíš se všechno přestát silou a bolest ti naruší výkon i obranu.</x:v>
+        <x:v>Pokusíš se všechno přestát silou a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1427"/>
       <x:c r="G1427">
@@ -33551,10 +33551,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1428" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají postih −3. Příští dva záchranné hody mají postih −3.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají postih −3.</x:v>
       </x:c>
       <x:c r="E1428" s="2" t="str">
-        <x:v>Námahu rozvrhneš příliš lehkovážně a bolest ti ztíží výkon i obranu.</x:v>
+        <x:v>Námahu rozvrhneš příliš lehkovážně a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1428"/>
       <x:c r="G1428">
@@ -33593,10 +33593,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1430" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští hod na iniciativu a příští ověření Odolnosti mají nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští dvě ověření Odolnosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1430" s="2" t="str">
-        <x:v>Přeceníš rezervu vlastní výdrže a bolest tě připraví o včasnou pohotovost.</x:v>
+        <x:v>Přeceníš rezervu vlastní výdrže a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1430"/>
       <x:c r="G1430">
@@ -33635,10 +33635,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1432" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu. Stejný postih mají i příští tři ověření dovednosti Perception.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1432" s="2" t="str">
-        <x:v>Slabý signál přejdeš sebejistě a kvůli bolesti ztratíš přehled i jistotu.</x:v>
+        <x:v>Slabý signál přejdeš sebejistě a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1432"/>
       <x:c r="G1432">
@@ -33677,10 +33677,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1434" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu. Příští záchranný hod má postih −3.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1434" s="2" t="str">
-        <x:v>Drobnou slabost překryješ přepětím a prudká bolest naruší výkon i obranu.</x:v>
+        <x:v>Drobnou slabost překryješ přepětím a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1434"/>
       <x:c r="G1434">
@@ -33698,10 +33698,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1435" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají postih −5. Příští záchranný hod na Odolnost má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají postih −5.</x:v>
       </x:c>
       <x:c r="E1435" s="2" t="str">
-        <x:v>Přeceníš schopnost snášet zátěž a bolest ti rozbije jistotu i pohotovost.</x:v>
+        <x:v>Přeceníš schopnost snášet zátěž a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1435"/>
       <x:c r="G1435">
@@ -33719,10 +33719,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1436" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu. Příští hod na iniciativu má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1436" s="2" t="str">
-        <x:v>Přirozenou výdrž zbytečně přepínáš a otřes ti naruší výkon i pohotovost.</x:v>
+        <x:v>Přirozenou výdrž zbytečně přepínáš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1436"/>
       <x:c r="G1436">
@@ -33782,10 +33782,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1439" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají postih −3 a nemohou mít výhodu. Nevýhoda se uplatní běžně.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření Odolnosti mají postih −5.</x:v>
       </x:c>
       <x:c r="E1439" s="2" t="str">
-        <x:v>Vlastním rezervám uvěříš přespříliš a bolest přehluší i poslední zbytky jistoty.</x:v>
+        <x:v>Vlastním rezervám uvěříš přespříliš a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1439"/>
       <x:c r="G1439">
@@ -33803,10 +33803,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1440" s="2" t="str">
-        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu. Příští záchranný hod má nevýhodu.</x:v>
+        <x:v>Utrpíš 2d6 drtivého poškození. Příští tři ověření vlastností mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1440" s="2" t="str">
-        <x:v>Přidáš námahu ve špatnou chvíli a bolest ti rozbije soustředění i obranu.</x:v>
+        <x:v>Přidáš námahu ve špatnou chvíli a bolest ti naruší další činnosti.</x:v>
       </x:c>
       <x:c r="F1440"/>
       <x:c r="G1440">
@@ -33824,10 +33824,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D1441" s="2" t="str">
-        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu. Příští dvě ověření Odolnosti mají navíc postih −2.</x:v>
+        <x:v>Utrpíš 3d6 drtivého poškození. Příští tři ověření Odolnosti mají nevýhodu.</x:v>
       </x:c>
       <x:c r="E1441" s="2" t="str">
-        <x:v>Snaze nepovolit obětuješ rozvahu a prudká bolest ti dlouho rozbíjí další pokusy.</x:v>
+        <x:v>Snaze nepovolit obětuješ rozvahu a bolest ti ztíží další pokusy.</x:v>
       </x:c>
       <x:c r="F1441"/>
       <x:c r="G1441">
